--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/sisepuede_modeling/ssp_morocco/ssp_modeling/scenario_mapping/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4CF85F-1717-8E42-8429-E0807712519D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555CE780-5F1D-FA42-B598-C2460E7FB20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45060" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
     <sheet name="yaml" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">main!$A$1:$M$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$R$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$63</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="416">
   <si>
     <t>subsector</t>
   </si>
@@ -658,10 +659,22 @@
     <t>transformation_unit</t>
   </si>
   <si>
+    <t>egypt_mitigation_action</t>
+  </si>
+  <si>
+    <t>egypt_action_descirption</t>
+  </si>
+  <si>
+    <t>magnitude</t>
+  </si>
+  <si>
+    <t>magnitude_description</t>
+  </si>
+  <si>
+    <t>default_magnitude</t>
+  </si>
+  <si>
     <t>start_period</t>
-  </si>
-  <si>
-    <t>default_magnitude</t>
   </si>
   <si>
     <t>AFOLU</t>
@@ -1292,30 +1305,47 @@
     <t>Increasing recycling rates reduces waste-related emissions and aligns with the goal of promoting sustainable urban development.</t>
   </si>
   <si>
-    <t>egypt_mitigation_action</t>
-  </si>
-  <si>
-    <t>egypt_action_descirption</t>
-  </si>
-  <si>
-    <t>magnitude</t>
-  </si>
-  <si>
-    <t>magnitude_description</t>
-  </si>
-  <si>
-    <t>strategy_LEP</t>
+    <t>TX:ENFU:ADJ_EXPORTS</t>
+  </si>
+  <si>
+    <t>ENFU</t>
+  </si>
+  <si>
+    <t>Increase fuel exports</t>
+  </si>
+  <si>
+    <t>transformation_enfu_adj_exports.yaml</t>
+  </si>
+  <si>
+    <t>Esta impacta en waso</t>
+  </si>
+  <si>
+    <t>TX:FGTV:INC_GAS_RECOVERY</t>
+  </si>
+  <si>
+    <t>Gas Recovery</t>
+  </si>
+  <si>
+    <t>transformation_fgtv_inc_gas_recovery.yaml</t>
+  </si>
+  <si>
+    <t>strategy_NDC</t>
+  </si>
+  <si>
+    <t>strategy_LEDS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1356,12 +1386,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1375,7 +1399,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1387,8 +1411,20 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1440,6 +1476,19 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FFC6C6C6"/>
       </top>
@@ -1463,12 +1512,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1485,15 +1562,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1506,27 +1583,27 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1539,71 +1616,179 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1912,89 +2097,90 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="13.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.5" style="4" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="33.1640625" style="4" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="47.5" style="4" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="48.5" style="4" hidden="1" customWidth="1"/>
-    <col min="9" max="10" width="35" style="4" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="31.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.83203125" style="38" customWidth="1"/>
-    <col min="13" max="13" width="20.5" style="40" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5" style="42" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5" style="40" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5" style="34" customWidth="1"/>
+    <col min="4" max="4" width="32.1640625" style="34" customWidth="1"/>
+    <col min="5" max="5" width="44.1640625" style="34" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="88.33203125" style="34" hidden="1" customWidth="1"/>
+    <col min="7" max="10" width="13" style="34" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" style="35" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" style="36" customWidth="1"/>
+    <col min="13" max="13" width="25.6640625" style="37" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" style="37" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13.5" style="38" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5" style="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="4" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" s="4" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="56" t="s">
         <v>204</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>205</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="K1" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>206</v>
+      <c r="I1" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>211</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="N1" s="10"/>
+        <v>414</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>415</v>
+      </c>
       <c r="O1" s="10"/>
-      <c r="P1" s="11"/>
+      <c r="P1" s="10"/>
       <c r="Q1" s="11"/>
-    </row>
-    <row r="2" spans="1:17" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R1" s="11"/>
+    </row>
+    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>209</v>
+      <c r="E2" s="13" t="s">
+        <v>213</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
@@ -2003,179 +2189,201 @@
       <c r="K2" s="15">
         <v>0.45</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="16">
         <v>12</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="17"/>
+      <c r="N2" s="17">
         <v>1</v>
       </c>
-      <c r="N2" s="10"/>
       <c r="O2" s="10"/>
-      <c r="P2" s="11"/>
+      <c r="P2" s="10">
+        <f t="shared" ref="P2:P7" si="0">K2*M2</f>
+        <v>0</v>
+      </c>
       <c r="Q2" s="11"/>
-    </row>
-    <row r="3" spans="1:17" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R2" s="11"/>
+    </row>
+    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B3" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>212</v>
+      <c r="E3" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>216</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
-      <c r="K3" s="18">
+      <c r="K3" s="19">
         <v>0.5</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="16">
         <v>12</v>
       </c>
-      <c r="M3" s="16"/>
-      <c r="N3" s="10"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
       <c r="O3" s="10"/>
-      <c r="P3" s="11"/>
+      <c r="P3" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="Q3" s="11"/>
-    </row>
-    <row r="4" spans="1:17" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R3" s="11"/>
+    </row>
+    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B4" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>213</v>
+      <c r="E4" s="13" t="s">
+        <v>217</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
-      <c r="K4" s="18">
+      <c r="K4" s="19">
         <v>0.3</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="16">
         <v>12</v>
       </c>
-      <c r="M4" s="16"/>
-      <c r="N4" s="10"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
       <c r="O4" s="10"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-    </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P4" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="R4" s="11"/>
+    </row>
+    <row r="5" spans="1:18" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>215</v>
+      <c r="E5" s="13" t="s">
+        <v>219</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="12"/>
       <c r="J5" s="12"/>
       <c r="K5" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="L5" s="13">
+        <v>221</v>
+      </c>
+      <c r="L5" s="16">
         <v>12</v>
       </c>
-      <c r="M5" s="16"/>
-      <c r="N5" s="10"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
       <c r="O5" s="10"/>
-      <c r="P5" s="11"/>
+      <c r="P5" s="10" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="Q5" s="11"/>
-    </row>
-    <row r="6" spans="1:17" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R5" s="11"/>
+    </row>
+    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B6" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>218</v>
+      <c r="E6" s="13" t="s">
+        <v>222</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="K6" s="18">
+        <v>225</v>
+      </c>
+      <c r="K6" s="19">
         <v>0.2</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="16">
         <v>12</v>
       </c>
-      <c r="M6" s="16"/>
-      <c r="N6" s="10"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
       <c r="O6" s="10"/>
-      <c r="P6" s="11"/>
+      <c r="P6" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="Q6" s="11"/>
-    </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R6" s="11"/>
+    </row>
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="B7" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>223</v>
+      <c r="E7" s="59" t="s">
+        <v>227</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -2184,272 +2392,311 @@
       <c r="K7" s="23">
         <v>50</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="16">
         <v>12</v>
       </c>
-      <c r="M7" s="46">
+      <c r="M7" s="17"/>
+      <c r="N7" s="79">
         <v>1</v>
       </c>
-      <c r="N7" s="10"/>
       <c r="O7" s="10"/>
-      <c r="P7" s="11"/>
+      <c r="P7" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="Q7" s="11"/>
-    </row>
-    <row r="8" spans="1:17" s="4" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R7" s="11"/>
+    </row>
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B8" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>225</v>
+      <c r="E8" s="13" t="s">
+        <v>229</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="L8" s="13">
-        <v>12</v>
-      </c>
-      <c r="M8" s="46">
+        <v>233</v>
+      </c>
+      <c r="L8" s="16">
+        <v>10</v>
+      </c>
+      <c r="M8" s="79">
         <v>1</v>
       </c>
-      <c r="N8" s="10"/>
+      <c r="N8" s="79">
+        <v>1</v>
+      </c>
       <c r="O8" s="10"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-    </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P8" s="10">
+        <f>0.6*M8</f>
+        <v>0.6</v>
+      </c>
+      <c r="Q8" s="10">
+        <f>0.6*N8</f>
+        <v>0.6</v>
+      </c>
+      <c r="R8" s="11"/>
+    </row>
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B9" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>230</v>
+      <c r="E9" s="13" t="s">
+        <v>234</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="K9" s="18">
+        <v>237</v>
+      </c>
+      <c r="K9" s="19">
         <v>0.95</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="16">
         <v>12</v>
       </c>
-      <c r="M9" s="46">
+      <c r="M9" s="17"/>
+      <c r="N9" s="79">
         <v>1</v>
       </c>
-      <c r="N9" s="10"/>
       <c r="O9" s="10"/>
-      <c r="P9" s="11"/>
+      <c r="P9" s="10">
+        <f t="shared" ref="P9:P15" si="1">K9*M9</f>
+        <v>0</v>
+      </c>
       <c r="Q9" s="11"/>
-    </row>
-    <row r="10" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R9" s="11"/>
+    </row>
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B10" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>234</v>
+      <c r="E10" s="13" t="s">
+        <v>238</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="K10" s="18">
+        <v>241</v>
+      </c>
+      <c r="K10" s="19">
         <v>0.95</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="16">
         <v>12</v>
       </c>
-      <c r="M10" s="46">
+      <c r="M10" s="79">
         <v>1</v>
       </c>
-      <c r="N10" s="10"/>
+      <c r="N10" s="79">
+        <v>1</v>
+      </c>
       <c r="O10" s="10"/>
-      <c r="P10" s="11"/>
+      <c r="P10" s="10">
+        <f t="shared" si="1"/>
+        <v>0.95</v>
+      </c>
       <c r="Q10" s="11"/>
-    </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R10" s="11"/>
+    </row>
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>238</v>
-      </c>
+      <c r="C11" s="62" t="s">
+        <v>411</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="E11" s="13"/>
       <c r="F11" s="12" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
-      <c r="K11" s="18">
-        <v>0.8</v>
-      </c>
-      <c r="L11" s="13">
-        <v>12</v>
-      </c>
-      <c r="M11" s="46">
-        <v>1</v>
-      </c>
-      <c r="N11" s="10"/>
+      <c r="K11" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="L11" s="16">
+        <v>10</v>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
       <c r="O11" s="10"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-    </row>
-    <row r="12" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="10">
+        <f>K11*N11</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="11"/>
+    </row>
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B12" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>241</v>
+      <c r="C12" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-      <c r="K12" s="18">
+      <c r="K12" s="19">
         <v>0.8</v>
       </c>
-      <c r="L12" s="13">
-        <v>12</v>
-      </c>
-      <c r="M12" s="46">
+      <c r="L12" s="16">
+        <v>10</v>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="79">
         <v>1</v>
       </c>
-      <c r="N12" s="10"/>
       <c r="O12" s="10"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-    </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10">
+        <f>K12*N12</f>
+        <v>0.8</v>
+      </c>
+      <c r="R12" s="11"/>
+    </row>
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>243</v>
+        <v>226</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>245</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
-      <c r="I13" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="K13" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="L13" s="13">
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="19">
+        <v>0.8</v>
+      </c>
+      <c r="L13" s="16">
         <v>12</v>
       </c>
-      <c r="M13" s="46">
+      <c r="M13" s="78"/>
+      <c r="N13" s="79">
         <v>1</v>
       </c>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-    </row>
-    <row r="14" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O13" s="10" t="e">
+        <f>K13*#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P13" s="66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="66">
+        <f>K13*N13</f>
+        <v>0.8</v>
+      </c>
+      <c r="R13" s="11"/>
+    </row>
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B14" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="12" t="s">
+      <c r="C14" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="60" t="s">
         <v>246</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="25" t="s">
         <v>247</v>
       </c>
       <c r="G14" s="12"/>
@@ -2461,33 +2708,40 @@
         <v>249</v>
       </c>
       <c r="K14" s="20">
-        <v>0.4</v>
-      </c>
-      <c r="L14" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="L14" s="16">
         <v>12</v>
       </c>
-      <c r="M14" s="46">
+      <c r="M14" s="17"/>
+      <c r="N14" s="79">
         <v>1</v>
       </c>
-      <c r="N14" s="10"/>
       <c r="O14" s="10"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-    </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="10">
+        <f>K14*N14</f>
+        <v>0.3</v>
+      </c>
+      <c r="R14" s="11"/>
+    </row>
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="12" t="s">
+      <c r="C15" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>250</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -2495,121 +2749,136 @@
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="18" t="s">
+      <c r="I15" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="L15" s="13">
+      <c r="J15" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="K15" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="L15" s="16">
         <v>12</v>
       </c>
-      <c r="M15" s="46">
+      <c r="M15" s="17"/>
+      <c r="N15" s="79">
         <v>1</v>
       </c>
-      <c r="N15" s="10"/>
       <c r="O15" s="10"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-    </row>
-    <row r="16" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="10">
+        <f>K15*N15</f>
+        <v>0.4</v>
+      </c>
+      <c r="R15" s="11"/>
+    </row>
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>253</v>
+        <v>226</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>254</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
-      <c r="I16" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="J16" s="12" t="s">
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="K16" s="15">
+      <c r="L16" s="16">
+        <v>12</v>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="79">
+        <v>1</v>
+      </c>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+    </row>
+    <row r="17" spans="1:18" s="64" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="K17" s="15">
         <v>0.5</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L17" s="80">
         <v>12</v>
       </c>
-      <c r="M16" s="46">
+      <c r="M17" s="81"/>
+      <c r="N17" s="82">
         <v>1</v>
       </c>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-    </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>258</v>
-      </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="K17" s="18">
-        <v>0.3</v>
-      </c>
-      <c r="L17" s="13">
-        <v>12</v>
-      </c>
-      <c r="M17" s="46">
-        <v>1</v>
-      </c>
-      <c r="N17" s="10"/>
       <c r="O17" s="10"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-    </row>
-    <row r="18" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P17" s="10">
+        <f t="shared" ref="P17:P41" si="2">K17*M17</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="10">
+        <f>K17*N17</f>
+        <v>0.5</v>
+      </c>
+      <c r="R17" s="63"/>
+    </row>
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="12" t="s">
+      <c r="C18" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="59" t="s">
         <v>261</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="25" t="s">
         <v>262</v>
       </c>
       <c r="G18" s="12"/>
@@ -2620,34 +2889,38 @@
       <c r="J18" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="K18" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="L18" s="13">
+      <c r="K18" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="L18" s="16">
         <v>12</v>
       </c>
-      <c r="M18" s="46">
+      <c r="M18" s="17"/>
+      <c r="N18" s="79">
         <v>1</v>
       </c>
-      <c r="N18" s="10"/>
       <c r="O18" s="10"/>
-      <c r="P18" s="11"/>
+      <c r="P18" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q18" s="11"/>
-    </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R18" s="11"/>
+    </row>
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="12" t="s">
+      <c r="C19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>265</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -2655,40 +2928,48 @@
       </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
+      <c r="I19" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>268</v>
+      </c>
       <c r="K19" s="15">
         <v>0.1</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="16">
         <v>12</v>
       </c>
-      <c r="M19" s="46">
+      <c r="M19" s="17"/>
+      <c r="N19" s="79">
         <v>1</v>
       </c>
-      <c r="N19" s="10"/>
       <c r="O19" s="10"/>
-      <c r="P19" s="11"/>
+      <c r="P19" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q19" s="11"/>
-    </row>
-    <row r="20" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R19" s="11"/>
+    </row>
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>267</v>
+      <c r="C20" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>269</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
@@ -2697,35 +2978,39 @@
       <c r="K20" s="15">
         <v>0.1</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="16">
         <v>12</v>
       </c>
-      <c r="M20" s="46">
+      <c r="M20" s="17"/>
+      <c r="N20" s="79">
         <v>1</v>
       </c>
-      <c r="N20" s="10"/>
       <c r="O20" s="10"/>
-      <c r="P20" s="11"/>
+      <c r="P20" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q20" s="11"/>
-    </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R20" s="11"/>
+    </row>
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>269</v>
+      <c r="C21" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>271</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
@@ -2734,195 +3019,217 @@
       <c r="K21" s="15">
         <v>0.1</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="16">
         <v>12</v>
       </c>
-      <c r="M21" s="46">
+      <c r="M21" s="17"/>
+      <c r="N21" s="79">
         <v>1</v>
       </c>
-      <c r="N21" s="10"/>
       <c r="O21" s="10"/>
-      <c r="P21" s="11"/>
+      <c r="P21" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q21" s="11"/>
-    </row>
-    <row r="22" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R21" s="11"/>
+    </row>
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>272</v>
+        <v>51</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>274</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
-      <c r="I22" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="J22" s="26" t="s">
-        <v>274</v>
-      </c>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
       <c r="K22" s="15">
-        <v>0.999</v>
-      </c>
-      <c r="L22" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="L22" s="16">
         <v>12</v>
       </c>
-      <c r="M22" s="46">
+      <c r="M22" s="17"/>
+      <c r="N22" s="79">
         <v>1</v>
       </c>
-      <c r="N22" s="10"/>
       <c r="O22" s="10"/>
-      <c r="P22" s="11"/>
+      <c r="P22" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q22" s="11"/>
-    </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R22" s="11"/>
+    </row>
+    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B23" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="12" t="s">
+      <c r="C23" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="59" t="s">
         <v>275</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="25" t="s">
         <v>276</v>
       </c>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="J23" s="27" t="s">
+      <c r="J23" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="K23" s="18">
-        <v>0.95</v>
-      </c>
-      <c r="L23" s="13">
-        <v>12</v>
-      </c>
-      <c r="M23" s="46">
+      <c r="K23" s="15">
+        <v>0.999</v>
+      </c>
+      <c r="L23" s="16">
+        <v>10</v>
+      </c>
+      <c r="M23" s="17"/>
+      <c r="N23" s="79">
         <v>1</v>
       </c>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-    </row>
-    <row r="24" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O23" s="66"/>
+      <c r="P23" s="66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="67">
+        <f>K23*N23</f>
+        <v>0.999</v>
+      </c>
+      <c r="R23" s="11"/>
+    </row>
+    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B24" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="22" t="s">
+      <c r="C24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="12" t="s">
         <v>280</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
-      <c r="I24" s="26" t="s">
+      <c r="I24" s="12" t="s">
         <v>281</v>
       </c>
       <c r="J24" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="K24" s="15">
-        <v>0.2</v>
-      </c>
-      <c r="L24" s="13">
+      <c r="K24" s="19">
+        <v>0.95</v>
+      </c>
+      <c r="L24" s="16">
         <v>12</v>
       </c>
-      <c r="M24" s="46">
+      <c r="M24" s="17"/>
+      <c r="N24" s="79">
         <v>1</v>
       </c>
-      <c r="N24" s="10"/>
       <c r="O24" s="10"/>
-      <c r="P24" s="11"/>
+      <c r="P24" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q24" s="11"/>
-    </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R24" s="11"/>
+    </row>
+    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B25" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="12" t="s">
+      <c r="C25" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="59" t="s">
         <v>283</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="25" t="s">
         <v>284</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="K25" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="L25" s="13">
-        <v>12</v>
-      </c>
-      <c r="M25" s="46">
+      <c r="K25" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="L25" s="16">
+        <v>8</v>
+      </c>
+      <c r="M25" s="17"/>
+      <c r="N25" s="79">
         <v>1</v>
       </c>
-      <c r="N25" s="10"/>
       <c r="O25" s="10"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-    </row>
-    <row r="26" spans="1:17" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P25" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="67">
+        <f>K25*N25</f>
+        <v>0.2</v>
+      </c>
+      <c r="R25" s="11"/>
+    </row>
+    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>287</v>
       </c>
       <c r="F26" s="12" t="s">
@@ -2930,759 +3237,848 @@
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="18">
-        <v>0.9</v>
-      </c>
-      <c r="L26" s="13">
+      <c r="I26" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="K26" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="L26" s="16">
         <v>12</v>
       </c>
-      <c r="M26" s="46">
+      <c r="M26" s="17"/>
+      <c r="N26" s="79">
         <v>1</v>
       </c>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="30"/>
-    </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O26" s="10"/>
+      <c r="P26" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+    </row>
+    <row r="27" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B27" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>289</v>
+      <c r="C27" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>291</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="L27" s="13">
+      <c r="K27" s="19">
+        <v>0.9</v>
+      </c>
+      <c r="L27" s="16">
         <v>12</v>
       </c>
-      <c r="M27" s="46">
+      <c r="M27" s="17"/>
+      <c r="N27" s="79">
         <v>1</v>
       </c>
-      <c r="N27" s="10"/>
       <c r="O27" s="10"/>
-      <c r="P27" s="11"/>
+      <c r="P27" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q27" s="11"/>
-    </row>
-    <row r="28" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R27" s="28"/>
+    </row>
+    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B28" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>292</v>
+      <c r="C28" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>293</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
-      <c r="K28" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="L28" s="13">
+      <c r="K28" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="L28" s="16">
         <v>12</v>
       </c>
-      <c r="M28" s="46">
+      <c r="M28" s="17"/>
+      <c r="N28" s="79">
         <v>1</v>
       </c>
-      <c r="N28" s="10"/>
       <c r="O28" s="10"/>
-      <c r="P28" s="11"/>
+      <c r="P28" s="10" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="Q28" s="11"/>
-    </row>
-    <row r="29" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R28" s="11"/>
+    </row>
+    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B29" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="12" t="s">
+      <c r="C29" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="F29" s="12" t="s">
         <v>294</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>290</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="L29" s="13">
+      <c r="K29" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="L29" s="16">
         <v>12</v>
       </c>
-      <c r="M29" s="46">
+      <c r="M29" s="17"/>
+      <c r="N29" s="79">
         <v>1</v>
       </c>
-      <c r="N29" s="10"/>
       <c r="O29" s="10"/>
-      <c r="P29" s="11"/>
+      <c r="P29" s="10" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="Q29" s="11"/>
-    </row>
-    <row r="30" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R29" s="11"/>
+    </row>
+    <row r="30" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>296</v>
+        <v>212</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>298</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
-      <c r="K30" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="L30" s="13">
+      <c r="K30" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="L30" s="16">
         <v>12</v>
       </c>
-      <c r="M30" s="46">
+      <c r="M30" s="17"/>
+      <c r="N30" s="79">
         <v>1</v>
       </c>
-      <c r="N30" s="10"/>
       <c r="O30" s="10"/>
-      <c r="P30" s="11"/>
+      <c r="P30" s="10" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="Q30" s="11"/>
-    </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R30" s="11"/>
+    </row>
+    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B31" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>299</v>
+      <c r="C31" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>300</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
-      <c r="K31" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="L31" s="13">
+      <c r="K31" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="L31" s="16">
         <v>12</v>
       </c>
-      <c r="M31" s="46">
+      <c r="M31" s="17"/>
+      <c r="N31" s="79">
         <v>1</v>
       </c>
-      <c r="N31" s="10"/>
       <c r="O31" s="10"/>
-      <c r="P31" s="11"/>
+      <c r="P31" s="10" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="Q31" s="11"/>
-    </row>
-    <row r="32" spans="1:17" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R31" s="11"/>
+    </row>
+    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B32" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B32" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>301</v>
+      <c r="C32" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>303</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="K32" s="18">
-        <v>0.3</v>
-      </c>
-      <c r="L32" s="13">
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="L32" s="16">
         <v>12</v>
       </c>
-      <c r="M32" s="46">
+      <c r="M32" s="17"/>
+      <c r="N32" s="79">
         <v>1</v>
       </c>
-      <c r="N32" s="31"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="32"/>
-    </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O32" s="10"/>
+      <c r="P32" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+    </row>
+    <row r="33" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="74" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" s="69" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B33" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E33" s="12" t="s">
+      <c r="F33" s="12" t="s">
         <v>306</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>307</v>
       </c>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="L33" s="13">
+      <c r="I33" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="K33" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="L33" s="16">
         <v>12</v>
       </c>
-      <c r="M33" s="46">
+      <c r="M33" s="17"/>
+      <c r="N33" s="79">
         <v>1</v>
       </c>
-      <c r="N33" s="10"/>
       <c r="O33" s="10"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-    </row>
-    <row r="34" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P33" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="29"/>
+    </row>
+    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="B34" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>308</v>
+      <c r="C34" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>310</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
-      <c r="K34" s="18">
-        <v>0.9</v>
-      </c>
-      <c r="L34" s="13">
+      <c r="K34" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="L34" s="16">
         <v>12</v>
       </c>
-      <c r="M34" s="46">
+      <c r="M34" s="17"/>
+      <c r="N34" s="79">
         <v>1</v>
       </c>
-      <c r="N34" s="10"/>
       <c r="O34" s="10"/>
-      <c r="P34" s="11"/>
+      <c r="P34" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q34" s="11"/>
-    </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R34" s="11"/>
+    </row>
+    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>312</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="L35" s="13">
+      <c r="K35" s="19">
+        <v>0.9</v>
+      </c>
+      <c r="L35" s="16">
         <v>12</v>
       </c>
-      <c r="M35" s="46">
+      <c r="M35" s="17"/>
+      <c r="N35" s="79">
         <v>1</v>
       </c>
-      <c r="N35" s="10"/>
       <c r="O35" s="10"/>
-      <c r="P35" s="11"/>
+      <c r="P35" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q35" s="11"/>
-    </row>
-    <row r="36" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R35" s="11"/>
+    </row>
+    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B36" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>312</v>
+      <c r="C36" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>314</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
-      <c r="K36" s="18">
+      <c r="K36" s="20">
         <v>0.5</v>
       </c>
-      <c r="L36" s="13">
-        <v>12</v>
-      </c>
-      <c r="M36" s="46">
+      <c r="L36" s="16">
+        <v>10</v>
+      </c>
+      <c r="M36" s="17"/>
+      <c r="N36" s="79">
         <v>1</v>
       </c>
-      <c r="N36" s="10"/>
       <c r="O36" s="10"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11"/>
-    </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P36" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="10">
+        <f>K36*N36</f>
+        <v>0.5</v>
+      </c>
+      <c r="R36" s="11"/>
+    </row>
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B37" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>314</v>
+      <c r="C37" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>316</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
-      <c r="K37" s="20">
-        <v>0.95</v>
-      </c>
-      <c r="L37" s="13">
-        <v>12</v>
-      </c>
-      <c r="M37" s="46">
+      <c r="K37" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="L37" s="16">
+        <v>10</v>
+      </c>
+      <c r="M37" s="17"/>
+      <c r="N37" s="79">
         <v>1</v>
       </c>
-      <c r="N37" s="10"/>
       <c r="O37" s="10"/>
-      <c r="P37" s="11"/>
+      <c r="P37" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q37" s="11"/>
-    </row>
-    <row r="38" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R37" s="11"/>
+    </row>
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>316</v>
+        <v>226</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>318</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
-      <c r="K38" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="L38" s="13">
-        <v>12</v>
-      </c>
-      <c r="M38" s="46">
+      <c r="K38" s="20">
+        <v>0.95</v>
+      </c>
+      <c r="L38" s="16">
+        <v>10</v>
+      </c>
+      <c r="M38" s="17"/>
+      <c r="N38" s="79">
         <v>1</v>
       </c>
-      <c r="N38" s="10"/>
       <c r="O38" s="10"/>
-      <c r="P38" s="11"/>
+      <c r="P38" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q38" s="11"/>
-    </row>
-    <row r="39" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R38" s="11"/>
+    </row>
+    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B39" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>318</v>
+      <c r="C39" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>320</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
-      <c r="K39" s="18">
+      <c r="K39" s="19">
         <v>0.2</v>
       </c>
-      <c r="L39" s="13">
+      <c r="L39" s="16">
         <v>12</v>
       </c>
-      <c r="M39" s="46">
+      <c r="M39" s="17"/>
+      <c r="N39" s="79">
         <v>1</v>
       </c>
-      <c r="N39" s="10"/>
       <c r="O39" s="10"/>
-      <c r="P39" s="11"/>
+      <c r="P39" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q39" s="11"/>
-    </row>
-    <row r="40" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R39" s="11"/>
+    </row>
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>320</v>
+        <v>212</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>322</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="J40" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="K40" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="L40" s="13">
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="L40" s="16">
         <v>12</v>
       </c>
-      <c r="M40" s="46">
+      <c r="M40" s="17"/>
+      <c r="N40" s="79">
         <v>1</v>
       </c>
-      <c r="N40" s="10"/>
       <c r="O40" s="10"/>
-      <c r="P40" s="11"/>
+      <c r="P40" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="Q40" s="11"/>
-    </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R40" s="11"/>
+    </row>
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E41" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" s="13" t="s">
         <v>324</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>325</v>
       </c>
       <c r="G41" s="12"/>
-      <c r="H41" s="33"/>
+      <c r="H41" s="12"/>
       <c r="I41" s="12" t="s">
         <v>326</v>
       </c>
       <c r="J41" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="K41" s="18">
+      <c r="K41" s="19">
         <v>0.25</v>
       </c>
-      <c r="L41" s="13">
+      <c r="L41" s="16">
         <v>12</v>
       </c>
-      <c r="M41" s="46">
+      <c r="M41" s="17"/>
+      <c r="N41" s="79">
         <v>1</v>
       </c>
-      <c r="N41" s="10"/>
       <c r="O41" s="10"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-    </row>
-    <row r="42" spans="1:17" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P41" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="10">
+        <f>K41*N41</f>
+        <v>0.25</v>
+      </c>
+      <c r="R41" s="11"/>
+    </row>
+    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B42" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B42" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E42" s="12" t="s">
+      <c r="C42" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" s="13" t="s">
         <v>328</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>329</v>
       </c>
       <c r="G42" s="12"/>
-      <c r="H42" s="33"/>
+      <c r="H42" s="30"/>
       <c r="I42" s="12" t="s">
         <v>330</v>
       </c>
       <c r="J42" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="K42" s="18">
+      <c r="K42" s="19">
         <v>0.25</v>
       </c>
-      <c r="L42" s="13">
+      <c r="L42" s="16">
         <v>12</v>
       </c>
-      <c r="M42" s="46">
+      <c r="M42" s="17"/>
+      <c r="N42" s="79">
         <v>1</v>
       </c>
-      <c r="N42" s="10"/>
       <c r="O42" s="10"/>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="11"/>
-    </row>
-    <row r="43" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P42" s="10">
+        <f t="shared" ref="P42:P50" si="3">K42*N42</f>
+        <v>0.25</v>
+      </c>
+      <c r="Q42" s="10">
+        <f>K42*P42</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="R42" s="11"/>
+    </row>
+    <row r="43" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B43" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B43" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E43" s="12" t="s">
+      <c r="C43" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>332</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>333</v>
       </c>
       <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="18">
+      <c r="H43" s="30"/>
+      <c r="I43" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="K43" s="19">
         <v>0.25</v>
       </c>
-      <c r="L43" s="13">
+      <c r="L43" s="16">
         <v>12</v>
       </c>
-      <c r="M43" s="46">
+      <c r="M43" s="17"/>
+      <c r="N43" s="79">
         <v>1</v>
       </c>
-      <c r="N43" s="10"/>
       <c r="O43" s="10"/>
-      <c r="P43" s="11"/>
+      <c r="P43" s="10">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
       <c r="Q43" s="11"/>
-    </row>
-    <row r="44" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R43" s="11"/>
+    </row>
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B44" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B44" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>334</v>
+      <c r="C44" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>336</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="18">
-        <v>0.7</v>
-      </c>
-      <c r="L44" s="13">
+      <c r="K44" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="L44" s="16">
         <v>12</v>
       </c>
-      <c r="M44" s="46">
+      <c r="M44" s="17"/>
+      <c r="N44" s="79">
         <v>1</v>
       </c>
-      <c r="N44" s="10"/>
       <c r="O44" s="10"/>
-      <c r="P44" s="11"/>
+      <c r="P44" s="10">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
       <c r="Q44" s="11"/>
-    </row>
-    <row r="45" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R44" s="11"/>
+    </row>
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B45" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B45" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>336</v>
+      <c r="C45" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>338</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G45" s="12"/>
       <c r="H45" s="12"/>
-      <c r="I45" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="K45" s="18">
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="19">
         <v>0.7</v>
       </c>
-      <c r="L45" s="13">
+      <c r="L45" s="16">
         <v>12</v>
       </c>
-      <c r="M45" s="46">
+      <c r="M45" s="17"/>
+      <c r="N45" s="79">
         <v>1</v>
       </c>
-      <c r="N45" s="10"/>
       <c r="O45" s="10"/>
-      <c r="P45" s="11"/>
+      <c r="P45" s="10">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
       <c r="Q45" s="11"/>
-    </row>
-    <row r="46" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R45" s="11"/>
+    </row>
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B46" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B46" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E46" s="12" t="s">
+      <c r="C46" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E46" s="13" t="s">
         <v>340</v>
       </c>
       <c r="F46" s="12" t="s">
@@ -3696,34 +4092,38 @@
       <c r="J46" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="K46" s="20">
+      <c r="K46" s="19">
         <v>0.7</v>
       </c>
-      <c r="L46" s="13">
+      <c r="L46" s="16">
         <v>12</v>
       </c>
-      <c r="M46" s="46">
+      <c r="M46" s="17"/>
+      <c r="N46" s="79">
         <v>1</v>
       </c>
-      <c r="N46" s="10"/>
       <c r="O46" s="10"/>
-      <c r="P46" s="11"/>
+      <c r="P46" s="10">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
       <c r="Q46" s="11"/>
-    </row>
-    <row r="47" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R46" s="11"/>
+    </row>
+    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B47" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B47" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E47" s="12" t="s">
+      <c r="C47" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" s="13" t="s">
         <v>344</v>
       </c>
       <c r="F47" s="12" t="s">
@@ -3731,77 +4131,85 @@
       </c>
       <c r="G47" s="12"/>
       <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="L47" s="13">
+      <c r="I47" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="K47" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="L47" s="16">
         <v>12</v>
       </c>
-      <c r="M47" s="46">
+      <c r="M47" s="17"/>
+      <c r="N47" s="79">
         <v>1</v>
       </c>
-      <c r="N47" s="10"/>
       <c r="O47" s="10"/>
-      <c r="P47" s="11"/>
+      <c r="P47" s="10">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
       <c r="Q47" s="11"/>
-    </row>
-    <row r="48" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R47" s="11"/>
+    </row>
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B48" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B48" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>346</v>
+      <c r="C48" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>348</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
-      <c r="I48" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="J48" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="K48" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="L48" s="13">
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="L48" s="16">
         <v>12</v>
       </c>
-      <c r="M48" s="46">
+      <c r="M48" s="17"/>
+      <c r="N48" s="79">
         <v>1</v>
       </c>
-      <c r="N48" s="10"/>
       <c r="O48" s="10"/>
-      <c r="P48" s="11"/>
+      <c r="P48" s="10">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
       <c r="Q48" s="11"/>
-    </row>
-    <row r="49" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R48" s="11"/>
+    </row>
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B49" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="E49" s="12" t="s">
+      <c r="C49" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" s="13" t="s">
         <v>350</v>
       </c>
       <c r="F49" s="12" t="s">
@@ -3815,34 +4223,38 @@
       <c r="J49" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="K49" s="18">
-        <v>0.3</v>
-      </c>
-      <c r="L49" s="13">
+      <c r="K49" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="L49" s="16">
         <v>12</v>
       </c>
-      <c r="M49" s="46">
+      <c r="M49" s="17"/>
+      <c r="N49" s="79">
         <v>1</v>
       </c>
-      <c r="N49" s="10"/>
       <c r="O49" s="10"/>
-      <c r="P49" s="11"/>
+      <c r="P49" s="10">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
       <c r="Q49" s="11"/>
-    </row>
-    <row r="50" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R49" s="11"/>
+    </row>
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B50" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B50" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="E50" s="12" t="s">
+      <c r="C50" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>354</v>
       </c>
       <c r="F50" s="12" t="s">
@@ -3856,157 +4268,170 @@
       <c r="J50" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="K50" s="18" t="s">
+      <c r="K50" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="L50" s="16">
+        <v>12</v>
+      </c>
+      <c r="M50" s="17"/>
+      <c r="N50" s="79">
+        <v>1</v>
+      </c>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10">
+        <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="11"/>
+    </row>
+    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="L50" s="13">
-        <v>12</v>
-      </c>
-      <c r="M50" s="46">
-        <v>1</v>
-      </c>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="11"/>
-    </row>
-    <row r="51" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E51" s="12" t="s">
+      <c r="F51" s="12" t="s">
         <v>359</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>360</v>
       </c>
       <c r="G51" s="12"/>
       <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="18">
-        <v>0.85</v>
-      </c>
-      <c r="L51" s="13">
+      <c r="I51" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="K51" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="L51" s="16">
         <v>12</v>
       </c>
-      <c r="M51" s="46">
+      <c r="M51" s="17"/>
+      <c r="N51" s="79">
         <v>1</v>
       </c>
-      <c r="N51" s="10"/>
       <c r="O51" s="10"/>
-      <c r="P51" s="11"/>
+      <c r="P51" s="10"/>
       <c r="Q51" s="11"/>
-    </row>
-    <row r="52" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R51" s="11"/>
+    </row>
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="26" t="s">
+      <c r="B52" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>361</v>
+      <c r="C52" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>363</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
-      <c r="I52" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="J52" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="K52" s="18">
-        <v>0.9</v>
-      </c>
-      <c r="L52" s="13">
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="19">
+        <v>0.85</v>
+      </c>
+      <c r="L52" s="16">
         <v>12</v>
       </c>
-      <c r="M52" s="46">
+      <c r="M52" s="17"/>
+      <c r="N52" s="79">
         <v>1</v>
       </c>
-      <c r="N52" s="10"/>
       <c r="O52" s="10"/>
-      <c r="P52" s="11"/>
+      <c r="P52" s="10">
+        <f>K52*M52</f>
+        <v>0</v>
+      </c>
       <c r="Q52" s="11"/>
-    </row>
-    <row r="53" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R52" s="11"/>
+    </row>
+    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E53" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="B53" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E53" s="12" t="s">
+      <c r="F53" s="12" t="s">
         <v>366</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>367</v>
       </c>
       <c r="G53" s="12"/>
       <c r="H53" s="12"/>
       <c r="I53" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="J53" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="J53" s="12" t="s">
+      <c r="K53" s="19">
+        <v>0.9</v>
+      </c>
+      <c r="L53" s="16">
+        <v>12</v>
+      </c>
+      <c r="M53" s="17"/>
+      <c r="N53" s="79">
+        <v>1</v>
+      </c>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10">
+        <f>K53*M53</f>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+    </row>
+    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="K53" s="18" t="s">
+      <c r="B54" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E54" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="L53" s="13">
-        <v>12</v>
-      </c>
-      <c r="M53" s="46">
-        <v>1</v>
-      </c>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="11"/>
-      <c r="Q53" s="11"/>
-    </row>
-    <row r="54" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B54" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="E54" s="12" t="s">
+      <c r="F54" s="12" t="s">
         <v>371</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>367</v>
       </c>
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
@@ -4016,38 +4441,39 @@
       <c r="J54" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="K54" s="18" t="s">
+      <c r="K54" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="L54" s="13">
-        <v>12</v>
-      </c>
-      <c r="M54" s="46">
+      <c r="L54" s="16">
+        <v>10</v>
+      </c>
+      <c r="M54" s="17"/>
+      <c r="N54" s="79">
         <v>1</v>
       </c>
-      <c r="N54" s="10"/>
       <c r="O54" s="10"/>
-      <c r="P54" s="11"/>
+      <c r="P54" s="10"/>
       <c r="Q54" s="11"/>
-    </row>
-    <row r="55" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R54" s="11"/>
+    </row>
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B55" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="E55" s="12" t="s">
+      <c r="C55" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E55" s="13" t="s">
         <v>375</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G55" s="12"/>
       <c r="H55" s="12"/>
@@ -4057,75 +4483,77 @@
       <c r="J55" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="K55" s="18" t="s">
+      <c r="K55" s="19" t="s">
         <v>378</v>
       </c>
-      <c r="L55" s="13">
-        <v>12</v>
-      </c>
-      <c r="M55" s="46">
+      <c r="L55" s="16">
+        <v>10</v>
+      </c>
+      <c r="M55" s="17"/>
+      <c r="N55" s="79">
         <v>1</v>
       </c>
-      <c r="N55" s="10"/>
       <c r="O55" s="10"/>
-      <c r="P55" s="11"/>
+      <c r="P55" s="10"/>
       <c r="Q55" s="11"/>
-    </row>
-    <row r="56" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R55" s="11"/>
+    </row>
+    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B56" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E56" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E56" s="13" t="s">
         <v>379</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="J56" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="K56" s="19" t="s">
         <v>382</v>
       </c>
-      <c r="K56" s="18">
-        <v>0.3</v>
-      </c>
-      <c r="L56" s="13">
+      <c r="L56" s="16">
         <v>12</v>
       </c>
-      <c r="M56" s="46">
+      <c r="M56" s="17"/>
+      <c r="N56" s="79">
         <v>1</v>
       </c>
-      <c r="N56" s="10"/>
       <c r="O56" s="10"/>
-      <c r="P56" s="11"/>
+      <c r="P56" s="10"/>
       <c r="Q56" s="11"/>
-    </row>
-    <row r="57" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R56" s="11"/>
+    </row>
+    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B57" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="E57" s="12" t="s">
+      <c r="C57" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="D57" s="69" t="s">
+        <v>184</v>
+      </c>
+      <c r="E57" s="13" t="s">
         <v>383</v>
       </c>
       <c r="F57" s="12" t="s">
@@ -4133,116 +4561,129 @@
       </c>
       <c r="G57" s="12"/>
       <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="15" t="s">
+      <c r="I57" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="L57" s="13">
+      <c r="J57" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="K57" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="L57" s="16">
         <v>12</v>
       </c>
-      <c r="M57" s="46"/>
-      <c r="N57" s="10"/>
+      <c r="M57" s="17"/>
+      <c r="N57" s="79">
+        <v>1</v>
+      </c>
       <c r="O57" s="10"/>
-      <c r="P57" s="11"/>
+      <c r="P57" s="10">
+        <f>K57*M57</f>
+        <v>0</v>
+      </c>
       <c r="Q57" s="11"/>
-    </row>
-    <row r="58" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R57" s="11"/>
+    </row>
+    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B58" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="D58" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>386</v>
-      </c>
-      <c r="F58" s="22" t="s">
+      <c r="C58" s="74" t="s">
+        <v>186</v>
+      </c>
+      <c r="D58" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="E58" s="13" t="s">
         <v>387</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>388</v>
       </c>
       <c r="G58" s="12"/>
       <c r="H58" s="12"/>
-      <c r="I58" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="J58" s="12" t="s">
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="K58" s="15">
-        <v>0.85</v>
-      </c>
-      <c r="L58" s="13">
+      <c r="L58" s="16">
         <v>12</v>
       </c>
-      <c r="M58" s="46">
-        <v>1</v>
-      </c>
-      <c r="N58" s="10"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="79"/>
       <c r="O58" s="10"/>
-      <c r="P58" s="11"/>
+      <c r="P58" s="10"/>
       <c r="Q58" s="11"/>
-    </row>
-    <row r="59" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R58" s="11"/>
+    </row>
+    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B59" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E59" s="12" t="s">
+      <c r="C59" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="D59" s="71" t="s">
+        <v>167</v>
+      </c>
+      <c r="E59" s="59" t="s">
         <v>390</v>
       </c>
-      <c r="F59" s="12" t="s">
+      <c r="F59" s="22" t="s">
         <v>391</v>
       </c>
       <c r="G59" s="12"/>
       <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
+      <c r="I59" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>393</v>
+      </c>
       <c r="K59" s="15">
         <v>0.85</v>
       </c>
-      <c r="L59" s="13">
+      <c r="L59" s="16">
         <v>12</v>
       </c>
-      <c r="M59" s="46">
+      <c r="M59" s="17"/>
+      <c r="N59" s="79">
         <v>1</v>
       </c>
-      <c r="N59" s="10"/>
       <c r="O59" s="10"/>
-      <c r="P59" s="11"/>
+      <c r="P59" s="10">
+        <f t="shared" ref="P59:P64" si="4">K59*M59</f>
+        <v>0</v>
+      </c>
       <c r="Q59" s="11"/>
-    </row>
-    <row r="60" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R59" s="11"/>
+    </row>
+    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B60" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="B60" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>392</v>
+      <c r="C60" s="74" t="s">
+        <v>191</v>
+      </c>
+      <c r="D60" s="69" t="s">
+        <v>192</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>394</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G60" s="12"/>
       <c r="H60" s="12"/>
@@ -4251,159 +4692,283 @@
       <c r="K60" s="15">
         <v>0.85</v>
       </c>
-      <c r="L60" s="13">
+      <c r="L60" s="16">
         <v>12</v>
       </c>
-      <c r="M60" s="46">
+      <c r="M60" s="17"/>
+      <c r="N60" s="79">
         <v>1</v>
       </c>
-      <c r="N60" s="10"/>
       <c r="O60" s="10"/>
-      <c r="P60" s="11"/>
+      <c r="P60" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="Q60" s="11"/>
-    </row>
-    <row r="61" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R60" s="11"/>
+    </row>
+    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B61" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="B61" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>394</v>
+      <c r="C61" s="74" t="s">
+        <v>194</v>
+      </c>
+      <c r="D61" s="69" t="s">
+        <v>195</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>396</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
-      <c r="I61" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="J61" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="K61" s="34">
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="L61" s="16">
+        <v>12</v>
+      </c>
+      <c r="M61" s="17"/>
+      <c r="N61" s="79">
         <v>1</v>
       </c>
-      <c r="L61" s="13">
+      <c r="O61" s="10"/>
+      <c r="P61" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q61" s="11"/>
+      <c r="R61" s="11"/>
+    </row>
+    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="40" t="s">
+        <v>369</v>
+      </c>
+      <c r="B62" s="61" t="s">
+        <v>182</v>
+      </c>
+      <c r="C62" s="76" t="s">
+        <v>197</v>
+      </c>
+      <c r="D62" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="E62" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="F62" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="G62" s="40"/>
+      <c r="H62" s="40"/>
+      <c r="I62" s="40" t="s">
+        <v>400</v>
+      </c>
+      <c r="J62" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="K62" s="41">
+        <v>1</v>
+      </c>
+      <c r="L62" s="42">
         <v>12</v>
       </c>
-      <c r="M61" s="46">
+      <c r="M62" s="43"/>
+      <c r="N62" s="79">
         <v>1</v>
       </c>
-      <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="11"/>
-      <c r="Q61" s="11"/>
-    </row>
-    <row r="62" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="B62" s="26" t="s">
+      <c r="O62" s="10"/>
+      <c r="P62" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q62" s="11"/>
+      <c r="R62" s="11"/>
+    </row>
+    <row r="63" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="44" t="s">
+        <v>369</v>
+      </c>
+      <c r="B63" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C63" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D63" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="E62" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="J62" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="K62" s="18">
+      <c r="E63" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="F63" s="44" t="s">
+        <v>403</v>
+      </c>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="44" t="s">
+        <v>404</v>
+      </c>
+      <c r="J63" s="44" t="s">
+        <v>405</v>
+      </c>
+      <c r="K63" s="46">
         <v>0.95</v>
       </c>
-      <c r="L62" s="13">
+      <c r="L63" s="47">
         <v>12</v>
       </c>
-      <c r="M62" s="46">
+      <c r="M63" s="48"/>
+      <c r="N63" s="79">
         <v>1</v>
       </c>
-      <c r="N62" s="10"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="11"/>
-      <c r="Q62" s="11"/>
-    </row>
-    <row r="63" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="19"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
-      <c r="K63" s="36"/>
-      <c r="L63" s="35"/>
-      <c r="M63" s="29"/>
-      <c r="N63" s="31"/>
-      <c r="O63" s="31"/>
-      <c r="P63" s="29"/>
-      <c r="Q63" s="30"/>
-    </row>
-    <row r="64" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="19"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="36"/>
-      <c r="L64" s="35"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="31"/>
-      <c r="O64" s="31"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="30"/>
-    </row>
-    <row r="65" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="19"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
-      <c r="K65" s="36"/>
-      <c r="L65" s="35"/>
-      <c r="M65" s="29"/>
-      <c r="N65" s="37"/>
-      <c r="O65" s="31"/>
-      <c r="P65" s="29"/>
-      <c r="Q65" s="28"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q63" s="11"/>
+      <c r="R63" s="11"/>
+    </row>
+    <row r="64" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="B64" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="C64" s="45" t="s">
+        <v>406</v>
+      </c>
+      <c r="D64" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="E64" s="45"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
+      <c r="H64" s="45"/>
+      <c r="I64" s="45"/>
+      <c r="J64" s="45"/>
+      <c r="K64" s="51">
+        <v>1.5</v>
+      </c>
+      <c r="L64" s="52">
+        <v>12</v>
+      </c>
+      <c r="M64" s="49"/>
+      <c r="N64" s="17"/>
+      <c r="O64" s="50"/>
+      <c r="P64" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q64" s="11"/>
+      <c r="R64" s="28"/>
+    </row>
+    <row r="65" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="31"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31"/>
+      <c r="H65" s="31"/>
+      <c r="I65" s="31"/>
+      <c r="J65" s="31"/>
+      <c r="K65" s="10"/>
+      <c r="L65" s="32"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="11"/>
+      <c r="O65" s="33"/>
+      <c r="P65" s="33"/>
+      <c r="Q65" s="11"/>
+      <c r="R65" s="27"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M1:M1048576">
+  <autoFilter ref="A1:R65" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="M1">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M10">
     <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M64:N1048576 M2:M7 M11:M63 M9">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N10 N12:N63">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N11">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M8">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4423,7 +4988,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" style="3" bestFit="1" customWidth="1"/>
@@ -4577,13 +5142,13 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>411</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>412</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4591,27 +5156,27 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4619,13 +5184,13 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4633,27 +5198,27 @@
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4661,13 +5226,13 @@
         <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4675,13 +5240,13 @@
         <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4689,13 +5254,13 @@
         <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4703,13 +5268,13 @@
         <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4717,27 +5282,27 @@
         <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4745,13 +5310,13 @@
         <v>70</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4759,13 +5324,13 @@
         <v>70</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4773,27 +5338,27 @@
         <v>70</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4801,13 +5366,13 @@
         <v>83</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4815,13 +5380,13 @@
         <v>83</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4829,27 +5394,27 @@
         <v>83</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4857,13 +5422,13 @@
         <v>96</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4871,27 +5436,27 @@
         <v>96</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4899,27 +5464,27 @@
         <v>106</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4927,13 +5492,13 @@
         <v>113</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4941,27 +5506,27 @@
         <v>113</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4969,41 +5534,41 @@
         <v>123</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5011,13 +5576,13 @@
         <v>134</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5025,13 +5590,13 @@
         <v>134</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5039,13 +5604,13 @@
         <v>134</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5053,13 +5618,13 @@
         <v>134</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5067,13 +5632,13 @@
         <v>134</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5081,13 +5646,13 @@
         <v>134</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5095,13 +5660,13 @@
         <v>134</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5109,13 +5674,13 @@
         <v>134</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5123,27 +5688,27 @@
         <v>134</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5151,27 +5716,27 @@
         <v>165</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5179,13 +5744,13 @@
         <v>172</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5193,27 +5758,27 @@
         <v>172</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5221,13 +5786,13 @@
         <v>182</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5235,13 +5800,13 @@
         <v>182</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5249,13 +5814,13 @@
         <v>182</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5263,41 +5828,493 @@
         <v>182</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C61" s="53" t="s">
         <v>195</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D61" s="53" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
+    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="54" t="s">
         <v>182</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B62" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C62" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D62" s="54" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
+    <row r="63" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="54" t="s">
         <v>182</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B63" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C63" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D63" s="54" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="55" t="s">
+        <v>407</v>
+      </c>
+      <c r="B64" s="55" t="s">
+        <v>406</v>
+      </c>
+      <c r="C64" s="55" t="s">
+        <v>408</v>
+      </c>
+      <c r="D64" s="55" t="s">
+        <v>409</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904C1827-1506-7D43-8DF8-A60638971741}">
+  <dimension ref="I8:J53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="8" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f>+I8+2015</f>
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="9" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <f t="shared" ref="J9:J53" si="0">+I9+2015</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="10" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="11" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="12" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I12">
+        <v>4</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="13" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="14" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I14">
+        <v>6</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="15" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I15">
+        <v>7</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="16" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I16" s="68">
+        <v>8</v>
+      </c>
+      <c r="J16" s="68">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="17" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I17">
+        <v>9</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="18" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I18" s="68">
+        <v>10</v>
+      </c>
+      <c r="J18" s="68">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="19" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I19">
+        <v>11</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="20" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I20">
+        <v>12</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="21" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I21">
+        <v>13</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="22" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I22">
+        <v>14</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="23" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I23">
+        <v>15</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="24" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I24">
+        <v>16</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="0"/>
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="25" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I25">
+        <v>17</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="0"/>
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="26" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I26">
+        <v>18</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="0"/>
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="27" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I27">
+        <v>19</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="0"/>
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="28" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I28" s="68">
+        <v>20</v>
+      </c>
+      <c r="J28" s="68">
+        <f t="shared" si="0"/>
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="29" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I29">
+        <v>21</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="0"/>
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="30" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I30">
+        <v>22</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="0"/>
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="31" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I31">
+        <v>23</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="0"/>
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="32" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I32">
+        <v>24</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="0"/>
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="33" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I33">
+        <v>25</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="0"/>
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="34" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I34">
+        <v>26</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="0"/>
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="35" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I35">
+        <v>27</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="0"/>
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="36" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I36">
+        <v>28</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="0"/>
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="37" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I37">
+        <v>29</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="0"/>
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="38" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I38">
+        <v>30</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="0"/>
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="39" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I39">
+        <v>31</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="0"/>
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="40" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I40">
+        <v>32</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="0"/>
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="41" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I41">
+        <v>33</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="0"/>
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="42" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I42">
+        <v>34</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="0"/>
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="43" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I43">
+        <v>35</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="0"/>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="44" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I44">
+        <v>36</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="0"/>
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="45" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I45">
+        <v>37</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="0"/>
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="46" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I46">
+        <v>38</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="0"/>
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="47" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I47">
+        <v>39</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="0"/>
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="48" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I48">
+        <v>40</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="0"/>
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="49" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I49">
+        <v>41</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="0"/>
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="50" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="0"/>
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="51" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I51">
+        <v>43</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="0"/>
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="52" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I52">
+        <v>44</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="0"/>
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="53" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I53">
+        <v>45</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="0"/>
+        <v>2060</v>
       </c>
     </row>
   </sheetData>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555CE780-5F1D-FA42-B598-C2460E7FB20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D23817-D686-4245-BAE9-A0530A652096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-45060" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2396,9 +2396,7 @@
         <v>12</v>
       </c>
       <c r="M7" s="17"/>
-      <c r="N7" s="79">
-        <v>1</v>
-      </c>
+      <c r="N7" s="79"/>
       <c r="O7" s="10"/>
       <c r="P7" s="10">
         <f t="shared" si="0"/>
@@ -2491,9 +2489,7 @@
         <v>12</v>
       </c>
       <c r="M9" s="17"/>
-      <c r="N9" s="79">
-        <v>1</v>
-      </c>
+      <c r="N9" s="79"/>
       <c r="O9" s="10"/>
       <c r="P9" s="10">
         <f t="shared" ref="P9:P15" si="1">K9*M9</f>
@@ -2619,9 +2615,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="17"/>
-      <c r="N12" s="79">
-        <v>1</v>
-      </c>
+      <c r="N12" s="79"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10">
         <f t="shared" si="1"/>
@@ -2629,7 +2623,7 @@
       </c>
       <c r="Q12" s="10">
         <f>K12*N12</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R12" s="11"/>
     </row>
@@ -2663,9 +2657,7 @@
         <v>12</v>
       </c>
       <c r="M13" s="78"/>
-      <c r="N13" s="79">
-        <v>1</v>
-      </c>
+      <c r="N13" s="79"/>
       <c r="O13" s="10" t="e">
         <f>K13*#REF!</f>
         <v>#REF!</v>
@@ -2676,7 +2668,7 @@
       </c>
       <c r="Q13" s="66">
         <f>K13*N13</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R13" s="11"/>
     </row>
@@ -2714,9 +2706,7 @@
         <v>12</v>
       </c>
       <c r="M14" s="17"/>
-      <c r="N14" s="79">
-        <v>1</v>
-      </c>
+      <c r="N14" s="79"/>
       <c r="O14" s="10"/>
       <c r="P14" s="10">
         <f t="shared" si="1"/>
@@ -2724,7 +2714,7 @@
       </c>
       <c r="Q14" s="10">
         <f>K14*N14</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R14" s="11"/>
     </row>
@@ -2762,9 +2752,7 @@
         <v>12</v>
       </c>
       <c r="M15" s="17"/>
-      <c r="N15" s="79">
-        <v>1</v>
-      </c>
+      <c r="N15" s="79"/>
       <c r="O15" s="10"/>
       <c r="P15" s="10">
         <f t="shared" si="1"/>
@@ -2772,7 +2760,7 @@
       </c>
       <c r="Q15" s="10">
         <f>K15*N15</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R15" s="11"/>
     </row>
@@ -2806,9 +2794,7 @@
         <v>12</v>
       </c>
       <c r="M16" s="17"/>
-      <c r="N16" s="79">
-        <v>1</v>
-      </c>
+      <c r="N16" s="79"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
       <c r="Q16" s="11"/>
@@ -2848,9 +2834,7 @@
         <v>12</v>
       </c>
       <c r="M17" s="81"/>
-      <c r="N17" s="82">
-        <v>1</v>
-      </c>
+      <c r="N17" s="82"/>
       <c r="O17" s="10"/>
       <c r="P17" s="10">
         <f t="shared" ref="P17:P41" si="2">K17*M17</f>
@@ -2858,7 +2842,7 @@
       </c>
       <c r="Q17" s="10">
         <f>K17*N17</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R17" s="63"/>
     </row>
@@ -2896,9 +2880,7 @@
         <v>12</v>
       </c>
       <c r="M18" s="17"/>
-      <c r="N18" s="79">
-        <v>1</v>
-      </c>
+      <c r="N18" s="79"/>
       <c r="O18" s="10"/>
       <c r="P18" s="10">
         <f t="shared" si="2"/>
@@ -2941,9 +2923,7 @@
         <v>12</v>
       </c>
       <c r="M19" s="17"/>
-      <c r="N19" s="79">
-        <v>1</v>
-      </c>
+      <c r="N19" s="79"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10">
         <f t="shared" si="2"/>
@@ -2982,9 +2962,7 @@
         <v>12</v>
       </c>
       <c r="M20" s="17"/>
-      <c r="N20" s="79">
-        <v>1</v>
-      </c>
+      <c r="N20" s="79"/>
       <c r="O20" s="10"/>
       <c r="P20" s="10">
         <f t="shared" si="2"/>
@@ -3023,9 +3001,7 @@
         <v>12</v>
       </c>
       <c r="M21" s="17"/>
-      <c r="N21" s="79">
-        <v>1</v>
-      </c>
+      <c r="N21" s="79"/>
       <c r="O21" s="10"/>
       <c r="P21" s="10">
         <f t="shared" si="2"/>
@@ -3064,9 +3040,7 @@
         <v>12</v>
       </c>
       <c r="M22" s="17"/>
-      <c r="N22" s="79">
-        <v>1</v>
-      </c>
+      <c r="N22" s="79"/>
       <c r="O22" s="10"/>
       <c r="P22" s="10">
         <f t="shared" si="2"/>
@@ -3109,9 +3083,7 @@
         <v>10</v>
       </c>
       <c r="M23" s="17"/>
-      <c r="N23" s="79">
-        <v>1</v>
-      </c>
+      <c r="N23" s="79"/>
       <c r="O23" s="66"/>
       <c r="P23" s="66">
         <f t="shared" si="2"/>
@@ -3119,7 +3091,7 @@
       </c>
       <c r="Q23" s="67">
         <f>K23*N23</f>
-        <v>0.999</v>
+        <v>0</v>
       </c>
       <c r="R23" s="11"/>
     </row>
@@ -3157,9 +3129,7 @@
         <v>12</v>
       </c>
       <c r="M24" s="17"/>
-      <c r="N24" s="79">
-        <v>1</v>
-      </c>
+      <c r="N24" s="79"/>
       <c r="O24" s="10"/>
       <c r="P24" s="10">
         <f t="shared" si="2"/>
@@ -3202,9 +3172,7 @@
         <v>8</v>
       </c>
       <c r="M25" s="17"/>
-      <c r="N25" s="79">
-        <v>1</v>
-      </c>
+      <c r="N25" s="79"/>
       <c r="O25" s="10"/>
       <c r="P25" s="10">
         <f t="shared" si="2"/>
@@ -3212,7 +3180,7 @@
       </c>
       <c r="Q25" s="67">
         <f>K25*N25</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R25" s="11"/>
     </row>
@@ -3250,9 +3218,7 @@
         <v>12</v>
       </c>
       <c r="M26" s="17"/>
-      <c r="N26" s="79">
-        <v>1</v>
-      </c>
+      <c r="N26" s="79"/>
       <c r="O26" s="10"/>
       <c r="P26" s="10">
         <f t="shared" si="2"/>
@@ -3291,9 +3257,7 @@
         <v>12</v>
       </c>
       <c r="M27" s="17"/>
-      <c r="N27" s="79">
-        <v>1</v>
-      </c>
+      <c r="N27" s="79"/>
       <c r="O27" s="10"/>
       <c r="P27" s="10">
         <f t="shared" si="2"/>
@@ -3332,9 +3296,7 @@
         <v>12</v>
       </c>
       <c r="M28" s="17"/>
-      <c r="N28" s="79">
-        <v>1</v>
-      </c>
+      <c r="N28" s="79"/>
       <c r="O28" s="10"/>
       <c r="P28" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3373,9 +3335,7 @@
         <v>12</v>
       </c>
       <c r="M29" s="17"/>
-      <c r="N29" s="79">
-        <v>1</v>
-      </c>
+      <c r="N29" s="79"/>
       <c r="O29" s="10"/>
       <c r="P29" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3414,9 +3374,7 @@
         <v>12</v>
       </c>
       <c r="M30" s="17"/>
-      <c r="N30" s="79">
-        <v>1</v>
-      </c>
+      <c r="N30" s="79"/>
       <c r="O30" s="10"/>
       <c r="P30" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3455,9 +3413,7 @@
         <v>12</v>
       </c>
       <c r="M31" s="17"/>
-      <c r="N31" s="79">
-        <v>1</v>
-      </c>
+      <c r="N31" s="79"/>
       <c r="O31" s="10"/>
       <c r="P31" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3496,9 +3452,7 @@
         <v>12</v>
       </c>
       <c r="M32" s="17"/>
-      <c r="N32" s="79">
-        <v>1</v>
-      </c>
+      <c r="N32" s="79"/>
       <c r="O32" s="10"/>
       <c r="P32" s="10">
         <f t="shared" si="2"/>
@@ -3541,9 +3495,7 @@
         <v>12</v>
       </c>
       <c r="M33" s="17"/>
-      <c r="N33" s="79">
-        <v>1</v>
-      </c>
+      <c r="N33" s="79"/>
       <c r="O33" s="10"/>
       <c r="P33" s="10">
         <f t="shared" si="2"/>
@@ -3582,9 +3534,7 @@
         <v>12</v>
       </c>
       <c r="M34" s="17"/>
-      <c r="N34" s="79">
-        <v>1</v>
-      </c>
+      <c r="N34" s="79"/>
       <c r="O34" s="10"/>
       <c r="P34" s="10">
         <f t="shared" si="2"/>
@@ -3623,9 +3573,7 @@
         <v>12</v>
       </c>
       <c r="M35" s="17"/>
-      <c r="N35" s="79">
-        <v>1</v>
-      </c>
+      <c r="N35" s="79"/>
       <c r="O35" s="10"/>
       <c r="P35" s="10">
         <f t="shared" si="2"/>
@@ -3664,9 +3612,7 @@
         <v>10</v>
       </c>
       <c r="M36" s="17"/>
-      <c r="N36" s="79">
-        <v>1</v>
-      </c>
+      <c r="N36" s="79"/>
       <c r="O36" s="10"/>
       <c r="P36" s="10">
         <f t="shared" si="2"/>
@@ -3674,7 +3620,7 @@
       </c>
       <c r="Q36" s="10">
         <f>K36*N36</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R36" s="11"/>
     </row>
@@ -3708,9 +3654,7 @@
         <v>10</v>
       </c>
       <c r="M37" s="17"/>
-      <c r="N37" s="79">
-        <v>1</v>
-      </c>
+      <c r="N37" s="79"/>
       <c r="O37" s="10"/>
       <c r="P37" s="10">
         <f t="shared" si="2"/>
@@ -3749,9 +3693,7 @@
         <v>10</v>
       </c>
       <c r="M38" s="17"/>
-      <c r="N38" s="79">
-        <v>1</v>
-      </c>
+      <c r="N38" s="79"/>
       <c r="O38" s="10"/>
       <c r="P38" s="10">
         <f t="shared" si="2"/>
@@ -3790,9 +3732,7 @@
         <v>12</v>
       </c>
       <c r="M39" s="17"/>
-      <c r="N39" s="79">
-        <v>1</v>
-      </c>
+      <c r="N39" s="79"/>
       <c r="O39" s="10"/>
       <c r="P39" s="10">
         <f t="shared" si="2"/>
@@ -3831,9 +3771,7 @@
         <v>12</v>
       </c>
       <c r="M40" s="17"/>
-      <c r="N40" s="79">
-        <v>1</v>
-      </c>
+      <c r="N40" s="79"/>
       <c r="O40" s="10"/>
       <c r="P40" s="10">
         <f t="shared" si="2"/>
@@ -3876,9 +3814,7 @@
         <v>12</v>
       </c>
       <c r="M41" s="17"/>
-      <c r="N41" s="79">
-        <v>1</v>
-      </c>
+      <c r="N41" s="79"/>
       <c r="O41" s="10"/>
       <c r="P41" s="10">
         <f t="shared" si="2"/>
@@ -3886,7 +3822,7 @@
       </c>
       <c r="Q41" s="10">
         <f>K41*N41</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R41" s="11"/>
     </row>
@@ -3924,17 +3860,15 @@
         <v>12</v>
       </c>
       <c r="M42" s="17"/>
-      <c r="N42" s="79">
-        <v>1</v>
-      </c>
+      <c r="N42" s="79"/>
       <c r="O42" s="10"/>
       <c r="P42" s="10">
         <f t="shared" ref="P42:P50" si="3">K42*N42</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="10">
         <f>K42*P42</f>
-        <v>6.25E-2</v>
+        <v>0</v>
       </c>
       <c r="R42" s="11"/>
     </row>
@@ -3972,13 +3906,11 @@
         <v>12</v>
       </c>
       <c r="M43" s="17"/>
-      <c r="N43" s="79">
-        <v>1</v>
-      </c>
+      <c r="N43" s="79"/>
       <c r="O43" s="10"/>
       <c r="P43" s="10">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
@@ -4013,13 +3945,11 @@
         <v>12</v>
       </c>
       <c r="M44" s="17"/>
-      <c r="N44" s="79">
-        <v>1</v>
-      </c>
+      <c r="N44" s="79"/>
       <c r="O44" s="10"/>
       <c r="P44" s="10">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
@@ -4054,13 +3984,11 @@
         <v>12</v>
       </c>
       <c r="M45" s="17"/>
-      <c r="N45" s="79">
-        <v>1</v>
-      </c>
+      <c r="N45" s="79"/>
       <c r="O45" s="10"/>
       <c r="P45" s="10">
         <f t="shared" si="3"/>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
@@ -4099,13 +4027,11 @@
         <v>12</v>
       </c>
       <c r="M46" s="17"/>
-      <c r="N46" s="79">
-        <v>1</v>
-      </c>
+      <c r="N46" s="79"/>
       <c r="O46" s="10"/>
       <c r="P46" s="10">
         <f t="shared" si="3"/>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
@@ -4144,13 +4070,11 @@
         <v>12</v>
       </c>
       <c r="M47" s="17"/>
-      <c r="N47" s="79">
-        <v>1</v>
-      </c>
+      <c r="N47" s="79"/>
       <c r="O47" s="10"/>
       <c r="P47" s="10">
         <f t="shared" si="3"/>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
@@ -4185,13 +4109,11 @@
         <v>12</v>
       </c>
       <c r="M48" s="17"/>
-      <c r="N48" s="79">
-        <v>1</v>
-      </c>
+      <c r="N48" s="79"/>
       <c r="O48" s="10"/>
       <c r="P48" s="10">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
@@ -4230,13 +4152,11 @@
         <v>12</v>
       </c>
       <c r="M49" s="17"/>
-      <c r="N49" s="79">
-        <v>1</v>
-      </c>
+      <c r="N49" s="79"/>
       <c r="O49" s="10"/>
       <c r="P49" s="10">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
@@ -4275,13 +4195,11 @@
         <v>12</v>
       </c>
       <c r="M50" s="17"/>
-      <c r="N50" s="79">
-        <v>1</v>
-      </c>
+      <c r="N50" s="79"/>
       <c r="O50" s="10"/>
       <c r="P50" s="10">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
@@ -4320,9 +4238,7 @@
         <v>12</v>
       </c>
       <c r="M51" s="17"/>
-      <c r="N51" s="79">
-        <v>1</v>
-      </c>
+      <c r="N51" s="79"/>
       <c r="O51" s="10"/>
       <c r="P51" s="10"/>
       <c r="Q51" s="11"/>
@@ -4358,9 +4274,7 @@
         <v>12</v>
       </c>
       <c r="M52" s="17"/>
-      <c r="N52" s="79">
-        <v>1</v>
-      </c>
+      <c r="N52" s="79"/>
       <c r="O52" s="10"/>
       <c r="P52" s="10">
         <f>K52*M52</f>
@@ -4403,9 +4317,7 @@
         <v>12</v>
       </c>
       <c r="M53" s="17"/>
-      <c r="N53" s="79">
-        <v>1</v>
-      </c>
+      <c r="N53" s="79"/>
       <c r="O53" s="10"/>
       <c r="P53" s="10">
         <f>K53*M53</f>
@@ -4448,9 +4360,7 @@
         <v>10</v>
       </c>
       <c r="M54" s="17"/>
-      <c r="N54" s="79">
-        <v>1</v>
-      </c>
+      <c r="N54" s="79"/>
       <c r="O54" s="10"/>
       <c r="P54" s="10"/>
       <c r="Q54" s="11"/>
@@ -4490,9 +4400,7 @@
         <v>10</v>
       </c>
       <c r="M55" s="17"/>
-      <c r="N55" s="79">
-        <v>1</v>
-      </c>
+      <c r="N55" s="79"/>
       <c r="O55" s="10"/>
       <c r="P55" s="10"/>
       <c r="Q55" s="11"/>
@@ -4532,9 +4440,7 @@
         <v>12</v>
       </c>
       <c r="M56" s="17"/>
-      <c r="N56" s="79">
-        <v>1</v>
-      </c>
+      <c r="N56" s="79"/>
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
       <c r="Q56" s="11"/>
@@ -4574,9 +4480,7 @@
         <v>12</v>
       </c>
       <c r="M57" s="17"/>
-      <c r="N57" s="79">
-        <v>1</v>
-      </c>
+      <c r="N57" s="79"/>
       <c r="O57" s="10"/>
       <c r="P57" s="10">
         <f>K57*M57</f>
@@ -4655,9 +4559,7 @@
         <v>12</v>
       </c>
       <c r="M59" s="17"/>
-      <c r="N59" s="79">
-        <v>1</v>
-      </c>
+      <c r="N59" s="79"/>
       <c r="O59" s="10"/>
       <c r="P59" s="10">
         <f t="shared" ref="P59:P64" si="4">K59*M59</f>
@@ -4696,9 +4598,7 @@
         <v>12</v>
       </c>
       <c r="M60" s="17"/>
-      <c r="N60" s="79">
-        <v>1</v>
-      </c>
+      <c r="N60" s="79"/>
       <c r="O60" s="10"/>
       <c r="P60" s="10">
         <f t="shared" si="4"/>
@@ -4737,9 +4637,7 @@
         <v>12</v>
       </c>
       <c r="M61" s="17"/>
-      <c r="N61" s="79">
-        <v>1</v>
-      </c>
+      <c r="N61" s="79"/>
       <c r="O61" s="10"/>
       <c r="P61" s="10">
         <f t="shared" si="4"/>
@@ -4782,9 +4680,7 @@
         <v>12</v>
       </c>
       <c r="M62" s="43"/>
-      <c r="N62" s="79">
-        <v>1</v>
-      </c>
+      <c r="N62" s="79"/>
       <c r="O62" s="10"/>
       <c r="P62" s="10">
         <f t="shared" si="4"/>
@@ -4827,9 +4723,7 @@
         <v>12</v>
       </c>
       <c r="M63" s="48"/>
-      <c r="N63" s="79">
-        <v>1</v>
-      </c>
+      <c r="N63" s="79"/>
       <c r="O63" s="10"/>
       <c r="P63" s="10">
         <f t="shared" si="4"/>
@@ -4897,6 +4791,18 @@
   <autoFilter ref="A1:R65" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="M1">
     <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M8">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4967,18 +4873,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M8">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D23817-D686-4245-BAE9-A0530A652096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214F51CC-1DB3-234C-AFAF-B73ACAD022A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45060" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38480" yWindow="600" windowWidth="31860" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2094,7 +2094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R65"/>
@@ -2163,7 +2163,7 @@
       <c r="Q1" s="11"/>
       <c r="R1" s="11"/>
     </row>
-    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>212</v>
       </c>
@@ -2204,7 +2204,7 @@
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
     </row>
-    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>212</v>
       </c>
@@ -2243,7 +2243,7 @@
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
     </row>
-    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>212</v>
       </c>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="R4" s="11"/>
     </row>
-    <row r="5" spans="1:18" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" s="4" customFormat="1" ht="95.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>212</v>
       </c>
@@ -2323,7 +2323,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
     </row>
-    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>212</v>
       </c>
@@ -2366,7 +2366,7 @@
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>226</v>
       </c>
@@ -2405,7 +2405,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>226</v>
       </c>
@@ -2498,7 +2498,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>226</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>226</v>
       </c>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>226</v>
       </c>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>226</v>
       </c>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="64" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" s="64" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="R17" s="63"/>
     </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2889,7 +2889,7 @@
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2932,7 +2932,7 @@
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -2971,7 +2971,7 @@
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -3010,7 +3010,7 @@
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
@@ -3049,7 +3049,7 @@
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
     </row>
-    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>212</v>
       </c>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="R23" s="11"/>
     </row>
-    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>212</v>
       </c>
@@ -3138,7 +3138,7 @@
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>212</v>
       </c>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="R25" s="11"/>
     </row>
-    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>212</v>
       </c>
@@ -3227,7 +3227,7 @@
       <c r="Q26" s="11"/>
       <c r="R26" s="11"/>
     </row>
-    <row r="27" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>212</v>
       </c>
@@ -3266,7 +3266,7 @@
       <c r="Q27" s="11"/>
       <c r="R27" s="28"/>
     </row>
-    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>212</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>212</v>
       </c>
@@ -3344,7 +3344,7 @@
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
     </row>
-    <row r="30" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>212</v>
       </c>
@@ -3383,7 +3383,7 @@
       <c r="Q30" s="11"/>
       <c r="R30" s="11"/>
     </row>
-    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>212</v>
       </c>
@@ -3422,7 +3422,7 @@
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
     </row>
-    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>212</v>
       </c>
@@ -3461,7 +3461,7 @@
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
     </row>
-    <row r="33" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>212</v>
       </c>
@@ -3504,7 +3504,7 @@
       <c r="Q33" s="17"/>
       <c r="R33" s="29"/>
     </row>
-    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>309</v>
       </c>
@@ -3543,7 +3543,7 @@
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
     </row>
-    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>309</v>
       </c>
@@ -3582,7 +3582,7 @@
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
     </row>
-    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>226</v>
       </c>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="R36" s="11"/>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>226</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>226</v>
       </c>
@@ -3702,7 +3702,7 @@
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
     </row>
-    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>212</v>
       </c>
@@ -3741,7 +3741,7 @@
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
     </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>212</v>
       </c>
@@ -3780,7 +3780,7 @@
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
     </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>226</v>
       </c>
@@ -3859,16 +3859,20 @@
       <c r="L42" s="16">
         <v>12</v>
       </c>
-      <c r="M42" s="17"/>
-      <c r="N42" s="79"/>
+      <c r="M42" s="17">
+        <v>1</v>
+      </c>
+      <c r="N42" s="17">
+        <v>1</v>
+      </c>
       <c r="O42" s="10"/>
       <c r="P42" s="10">
-        <f t="shared" ref="P42:P50" si="3">K42*N42</f>
-        <v>0</v>
+        <f>K42*N42</f>
+        <v>0.25</v>
       </c>
       <c r="Q42" s="10">
         <f>K42*P42</f>
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
       <c r="R42" s="11"/>
     </row>
@@ -3909,7 +3913,7 @@
       <c r="N43" s="79"/>
       <c r="O43" s="10"/>
       <c r="P43" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="P43:P50" si="3">K43*N43</f>
         <v>0</v>
       </c>
       <c r="Q43" s="11"/>
@@ -3981,14 +3985,18 @@
         <v>0.7</v>
       </c>
       <c r="L45" s="16">
-        <v>12</v>
-      </c>
-      <c r="M45" s="17"/>
-      <c r="N45" s="79"/>
+        <v>10</v>
+      </c>
+      <c r="M45" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="N45" s="79">
+        <v>1.35</v>
+      </c>
       <c r="O45" s="10"/>
       <c r="P45" s="10">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>K45*N45</f>
+        <v>0.94499999999999995</v>
       </c>
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
@@ -4070,11 +4078,13 @@
         <v>12</v>
       </c>
       <c r="M47" s="17"/>
-      <c r="N47" s="79"/>
+      <c r="N47" s="79">
+        <v>0.8</v>
+      </c>
       <c r="O47" s="10"/>
       <c r="P47" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
@@ -4152,11 +4162,13 @@
         <v>12</v>
       </c>
       <c r="M49" s="17"/>
-      <c r="N49" s="79"/>
+      <c r="N49" s="79">
+        <v>2</v>
+      </c>
       <c r="O49" s="10"/>
       <c r="P49" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
@@ -4195,11 +4207,13 @@
         <v>12</v>
       </c>
       <c r="M50" s="17"/>
-      <c r="N50" s="79"/>
+      <c r="N50" s="79">
+        <v>1</v>
+      </c>
       <c r="O50" s="10"/>
       <c r="P50" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
@@ -4244,7 +4258,7 @@
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>51</v>
       </c>
@@ -4283,7 +4297,7 @@
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
     </row>
-    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>51</v>
       </c>
@@ -4326,7 +4340,7 @@
       <c r="Q53" s="11"/>
       <c r="R53" s="11"/>
     </row>
-    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>369</v>
       </c>
@@ -4366,7 +4380,7 @@
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
     </row>
-    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>369</v>
       </c>
@@ -4406,7 +4420,7 @@
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
     </row>
-    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>369</v>
       </c>
@@ -4446,7 +4460,7 @@
       <c r="Q56" s="11"/>
       <c r="R56" s="11"/>
     </row>
-    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>369</v>
       </c>
@@ -4489,7 +4503,7 @@
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
     </row>
-    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>369</v>
       </c>
@@ -4525,7 +4539,7 @@
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
     </row>
-    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>369</v>
       </c>
@@ -4568,7 +4582,7 @@
       <c r="Q59" s="11"/>
       <c r="R59" s="11"/>
     </row>
-    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>369</v>
       </c>
@@ -4607,7 +4621,7 @@
       <c r="Q60" s="11"/>
       <c r="R60" s="11"/>
     </row>
-    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>369</v>
       </c>
@@ -4646,7 +4660,7 @@
       <c r="Q61" s="11"/>
       <c r="R61" s="11"/>
     </row>
-    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="40" t="s">
         <v>369</v>
       </c>
@@ -4689,7 +4703,7 @@
       <c r="Q62" s="11"/>
       <c r="R62" s="11"/>
     </row>
-    <row r="63" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="44" t="s">
         <v>369</v>
       </c>
@@ -4732,7 +4746,7 @@
       <c r="Q63" s="11"/>
       <c r="R63" s="11"/>
     </row>
-    <row r="64" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="45" t="s">
         <v>226</v>
       </c>
@@ -4767,7 +4781,7 @@
       <c r="Q64" s="11"/>
       <c r="R64" s="28"/>
     </row>
-    <row r="65" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="31"/>
       <c r="B65" s="31"/>
       <c r="C65" s="31"/>
@@ -4788,8 +4802,74 @@
       <c r="R65" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R65" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R65" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="TRNS"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="M1">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M8">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M10">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M64:N1048576 M2:M7 M11:M63 M9">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N10 N12:N41 N43:N63">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -4801,55 +4881,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M8">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M10">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M64:N1048576 M2:M7 M11:M63 M9">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10 N12:N63">
+  <conditionalFormatting sqref="N11">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4861,8 +4893,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N11">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="N42">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214F51CC-1DB3-234C-AFAF-B73ACAD022A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566290ED-BE12-9541-8B16-98427988A5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38480" yWindow="600" windowWidth="31860" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$R$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$R$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$64</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="419">
   <si>
     <t>subsector</t>
   </si>
@@ -1333,6 +1333,15 @@
   </si>
   <si>
     <t>strategy_LEDS</t>
+  </si>
+  <si>
+    <t>TX:TRNS:SHIFT_FUEL_PUBLIC</t>
+  </si>
+  <si>
+    <t>Electrify urban public transport</t>
+  </si>
+  <si>
+    <t>transformation_trns_shift_fuel_public.yaml</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1554,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1789,6 +1798,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2097,7 +2109,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="13.1640625" style="34" bestFit="1" customWidth="1"/>
@@ -3913,7 +3925,7 @@
       <c r="N43" s="79"/>
       <c r="O43" s="10"/>
       <c r="P43" s="10">
-        <f t="shared" ref="P43:P50" si="3">K43*N43</f>
+        <f t="shared" ref="P43:P51" si="3">K43*N43</f>
         <v>0</v>
       </c>
       <c r="Q43" s="11"/>
@@ -4052,39 +4064,37 @@
         <v>134</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>150</v>
+        <v>416</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="E47" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="K47" s="20">
+      <c r="E47" s="20">
         <v>0.7</v>
       </c>
+      <c r="F47" s="16">
+        <v>12</v>
+      </c>
+      <c r="G47" s="17"/>
+      <c r="H47" s="79">
+        <v>0.8</v>
+      </c>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="83">
+        <v>0.06</v>
+      </c>
       <c r="L47" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M47" s="17"/>
       <c r="N47" s="79">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O47" s="10"/>
       <c r="P47" s="10">
         <f t="shared" si="3"/>
-        <v>0.55999999999999994</v>
+        <v>0.06</v>
       </c>
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
@@ -4097,33 +4107,39 @@
         <v>134</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="19">
-        <v>0.25</v>
+      <c r="I48" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="K48" s="20">
+        <v>0.7</v>
       </c>
       <c r="L48" s="16">
         <v>12</v>
       </c>
       <c r="M48" s="17"/>
-      <c r="N48" s="79"/>
+      <c r="N48" s="79">
+        <v>0.8</v>
+      </c>
       <c r="O48" s="10"/>
       <c r="P48" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
@@ -4136,39 +4152,33 @@
         <v>134</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
-      <c r="I49" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>353</v>
-      </c>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
       <c r="K49" s="19">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L49" s="16">
         <v>12</v>
       </c>
       <c r="M49" s="17"/>
-      <c r="N49" s="79">
-        <v>2</v>
-      </c>
+      <c r="N49" s="79"/>
       <c r="O49" s="10"/>
       <c r="P49" s="10">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
@@ -4181,39 +4191,39 @@
         <v>134</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K50" s="19">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L50" s="16">
         <v>12</v>
       </c>
       <c r="M50" s="17"/>
       <c r="N50" s="79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="10"/>
       <c r="P50" s="10">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
@@ -4226,63 +4236,72 @@
         <v>134</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G51" s="12"/>
       <c r="H51" s="12"/>
       <c r="I51" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="K51" s="19" t="s">
-        <v>362</v>
+        <v>357</v>
+      </c>
+      <c r="K51" s="19">
+        <v>0.3</v>
       </c>
       <c r="L51" s="16">
         <v>12</v>
       </c>
       <c r="M51" s="17"/>
-      <c r="N51" s="79"/>
+      <c r="N51" s="79">
+        <v>1</v>
+      </c>
       <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
+      <c r="P51" s="10">
+        <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="19">
-        <v>0.85</v>
+      <c r="I52" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="K52" s="19" t="s">
+        <v>362</v>
       </c>
       <c r="L52" s="16">
         <v>12</v>
@@ -4290,10 +4309,7 @@
       <c r="M52" s="17"/>
       <c r="N52" s="79"/>
       <c r="O52" s="10"/>
-      <c r="P52" s="10">
-        <f>K52*M52</f>
-        <v>0</v>
-      </c>
+      <c r="P52" s="10"/>
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
     </row>
@@ -4305,27 +4321,23 @@
         <v>165</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G53" s="12"/>
       <c r="H53" s="12"/>
-      <c r="I53" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>368</v>
-      </c>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
       <c r="K53" s="19">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L53" s="16">
         <v>12</v>
@@ -4342,41 +4354,44 @@
     </row>
     <row r="54" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
-        <v>369</v>
+        <v>51</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="K54" s="19" t="s">
-        <v>374</v>
+        <v>368</v>
+      </c>
+      <c r="K54" s="19">
+        <v>0.9</v>
       </c>
       <c r="L54" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M54" s="17"/>
       <c r="N54" s="79"/>
       <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
+      <c r="P54" s="10">
+        <f>K54*M54</f>
+        <v>0</v>
+      </c>
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
     </row>
@@ -4388,13 +4403,13 @@
         <v>172</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="F55" s="12" t="s">
         <v>371</v>
@@ -4402,13 +4417,13 @@
       <c r="G55" s="12"/>
       <c r="H55" s="12"/>
       <c r="I55" s="12" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="L55" s="16">
         <v>10</v>
@@ -4428,13 +4443,13 @@
         <v>172</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>371</v>
@@ -4442,16 +4457,16 @@
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="12" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K56" s="19" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="L56" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M56" s="17"/>
       <c r="N56" s="79"/>
@@ -4465,30 +4480,30 @@
         <v>369</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C57" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="D57" s="69" t="s">
-        <v>184</v>
+        <v>172</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>180</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="G57" s="12"/>
       <c r="H57" s="12"/>
       <c r="I57" s="12" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="K57" s="19">
-        <v>0.3</v>
+        <v>381</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>382</v>
       </c>
       <c r="L57" s="16">
         <v>12</v>
@@ -4496,10 +4511,7 @@
       <c r="M57" s="17"/>
       <c r="N57" s="79"/>
       <c r="O57" s="10"/>
-      <c r="P57" s="10">
-        <f>K57*M57</f>
-        <v>0</v>
-      </c>
+      <c r="P57" s="10"/>
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
     </row>
@@ -4511,23 +4523,27 @@
         <v>182</v>
       </c>
       <c r="C58" s="74" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D58" s="69" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G58" s="12"/>
       <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="15" t="s">
-        <v>389</v>
+      <c r="I58" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="J58" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="K58" s="19">
+        <v>0.3</v>
       </c>
       <c r="L58" s="16">
         <v>12</v>
@@ -4535,7 +4551,10 @@
       <c r="M58" s="17"/>
       <c r="N58" s="79"/>
       <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
+      <c r="P58" s="10">
+        <f>K58*M58</f>
+        <v>0</v>
+      </c>
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
     </row>
@@ -4547,27 +4566,23 @@
         <v>182</v>
       </c>
       <c r="C59" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="D59" s="71" t="s">
-        <v>167</v>
-      </c>
-      <c r="E59" s="59" t="s">
-        <v>390</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>391</v>
+        <v>186</v>
+      </c>
+      <c r="D59" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>388</v>
       </c>
       <c r="G59" s="12"/>
       <c r="H59" s="12"/>
-      <c r="I59" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="K59" s="15">
-        <v>0.85</v>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="15" t="s">
+        <v>389</v>
       </c>
       <c r="L59" s="16">
         <v>12</v>
@@ -4575,10 +4590,7 @@
       <c r="M59" s="17"/>
       <c r="N59" s="79"/>
       <c r="O59" s="10"/>
-      <c r="P59" s="10">
-        <f t="shared" ref="P59:P64" si="4">K59*M59</f>
-        <v>0</v>
-      </c>
+      <c r="P59" s="10"/>
       <c r="Q59" s="11"/>
       <c r="R59" s="11"/>
     </row>
@@ -4590,21 +4602,25 @@
         <v>182</v>
       </c>
       <c r="C60" s="74" t="s">
-        <v>191</v>
-      </c>
-      <c r="D60" s="69" t="s">
-        <v>192</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>395</v>
+        <v>189</v>
+      </c>
+      <c r="D60" s="71" t="s">
+        <v>167</v>
+      </c>
+      <c r="E60" s="59" t="s">
+        <v>390</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>391</v>
       </c>
       <c r="G60" s="12"/>
       <c r="H60" s="12"/>
-      <c r="I60" s="12"/>
-      <c r="J60" s="12"/>
+      <c r="I60" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>393</v>
+      </c>
       <c r="K60" s="15">
         <v>0.85</v>
       </c>
@@ -4615,7 +4631,7 @@
       <c r="N60" s="79"/>
       <c r="O60" s="10"/>
       <c r="P60" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="P60:P65" si="4">K60*M60</f>
         <v>0</v>
       </c>
       <c r="Q60" s="11"/>
@@ -4629,16 +4645,16 @@
         <v>182</v>
       </c>
       <c r="C61" s="74" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D61" s="69" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
@@ -4661,39 +4677,35 @@
       <c r="R61" s="11"/>
     </row>
     <row r="62" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="40" t="s">
+      <c r="A62" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="B62" s="61" t="s">
+      <c r="B62" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="D62" s="72" t="s">
-        <v>198</v>
-      </c>
-      <c r="E62" s="61" t="s">
-        <v>398</v>
-      </c>
-      <c r="F62" s="40" t="s">
-        <v>399</v>
-      </c>
-      <c r="G62" s="40"/>
-      <c r="H62" s="40"/>
-      <c r="I62" s="40" t="s">
-        <v>400</v>
-      </c>
-      <c r="J62" s="40" t="s">
-        <v>401</v>
-      </c>
-      <c r="K62" s="41">
-        <v>1</v>
-      </c>
-      <c r="L62" s="42">
+      <c r="C62" s="74" t="s">
+        <v>194</v>
+      </c>
+      <c r="D62" s="69" t="s">
+        <v>195</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="L62" s="16">
         <v>12</v>
       </c>
-      <c r="M62" s="43"/>
+      <c r="M62" s="17"/>
       <c r="N62" s="79"/>
       <c r="O62" s="10"/>
       <c r="P62" s="10">
@@ -4704,39 +4716,39 @@
       <c r="R62" s="11"/>
     </row>
     <row r="63" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="44" t="s">
+      <c r="A63" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="B63" s="45" t="s">
+      <c r="B63" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="C63" s="77" t="s">
-        <v>200</v>
-      </c>
-      <c r="D63" s="73" t="s">
-        <v>201</v>
-      </c>
-      <c r="E63" s="45" t="s">
-        <v>402</v>
-      </c>
-      <c r="F63" s="44" t="s">
-        <v>403</v>
-      </c>
-      <c r="G63" s="44"/>
-      <c r="H63" s="44"/>
-      <c r="I63" s="44" t="s">
-        <v>404</v>
-      </c>
-      <c r="J63" s="44" t="s">
-        <v>405</v>
-      </c>
-      <c r="K63" s="46">
-        <v>0.95</v>
-      </c>
-      <c r="L63" s="47">
+      <c r="C63" s="76" t="s">
+        <v>197</v>
+      </c>
+      <c r="D63" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="E63" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="F63" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="G63" s="40"/>
+      <c r="H63" s="40"/>
+      <c r="I63" s="40" t="s">
+        <v>400</v>
+      </c>
+      <c r="J63" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="K63" s="41">
+        <v>1</v>
+      </c>
+      <c r="L63" s="42">
         <v>12</v>
       </c>
-      <c r="M63" s="48"/>
+      <c r="M63" s="43"/>
       <c r="N63" s="79"/>
       <c r="O63" s="10"/>
       <c r="P63" s="10">
@@ -4746,63 +4758,106 @@
       <c r="Q63" s="11"/>
       <c r="R63" s="11"/>
     </row>
-    <row r="64" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="45" t="s">
-        <v>226</v>
+    <row r="64" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="44" t="s">
+        <v>369</v>
       </c>
       <c r="B64" s="45" t="s">
-        <v>407</v>
-      </c>
-      <c r="C64" s="45" t="s">
-        <v>406</v>
-      </c>
-      <c r="D64" s="45" t="s">
-        <v>408</v>
-      </c>
-      <c r="E64" s="45"/>
-      <c r="F64" s="45"/>
-      <c r="G64" s="45"/>
-      <c r="H64" s="45"/>
-      <c r="I64" s="45"/>
-      <c r="J64" s="45"/>
-      <c r="K64" s="51">
-        <v>1.5</v>
-      </c>
-      <c r="L64" s="52">
+        <v>182</v>
+      </c>
+      <c r="C64" s="77" t="s">
+        <v>200</v>
+      </c>
+      <c r="D64" s="73" t="s">
+        <v>201</v>
+      </c>
+      <c r="E64" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="F64" s="44" t="s">
+        <v>403</v>
+      </c>
+      <c r="G64" s="44"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="44" t="s">
+        <v>404</v>
+      </c>
+      <c r="J64" s="44" t="s">
+        <v>405</v>
+      </c>
+      <c r="K64" s="46">
+        <v>0.95</v>
+      </c>
+      <c r="L64" s="47">
         <v>12</v>
       </c>
-      <c r="M64" s="49"/>
-      <c r="N64" s="17"/>
-      <c r="O64" s="50"/>
-      <c r="P64" s="50">
+      <c r="M64" s="48"/>
+      <c r="N64" s="79"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q64" s="11"/>
-      <c r="R64" s="28"/>
+      <c r="R64" s="11"/>
     </row>
     <row r="65" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="31"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="31"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="32"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="33"/>
-      <c r="P65" s="33"/>
+      <c r="A65" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="B65" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="C65" s="45" t="s">
+        <v>406</v>
+      </c>
+      <c r="D65" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="45"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="51">
+        <v>1.5</v>
+      </c>
+      <c r="L65" s="52">
+        <v>12</v>
+      </c>
+      <c r="M65" s="49"/>
+      <c r="N65" s="17"/>
+      <c r="O65" s="50"/>
+      <c r="P65" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="Q65" s="11"/>
-      <c r="R65" s="27"/>
+      <c r="R65" s="28"/>
+    </row>
+    <row r="66" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="31"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="31"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="32"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="11"/>
+      <c r="O66" s="33"/>
+      <c r="P66" s="33"/>
+      <c r="Q66" s="11"/>
+      <c r="R66" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R65" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:R66" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
         <filter val="TRNS"/>
@@ -4810,6 +4865,78 @@
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="M1">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M8">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M10">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M65:N1048576 M2:M7 M11:M64 M9">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N10 N12:N41 N43:N64">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N11">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -4821,7 +4948,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M8">
+  <conditionalFormatting sqref="N42">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G47">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -4833,67 +4972,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M10">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M64:N1048576 M2:M7 M11:M63 M9">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10 N12:N41 N43:N63">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N11">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N42">
+  <conditionalFormatting sqref="H47">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4914,7 +4993,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" style="3" bestFit="1" customWidth="1"/>
@@ -5572,13 +5651,13 @@
         <v>134</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>150</v>
+        <v>416</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>151</v>
+        <v>417</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>152</v>
+        <v>418</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5586,13 +5665,13 @@
         <v>134</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5600,13 +5679,13 @@
         <v>134</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5614,13 +5693,13 @@
         <v>134</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5628,27 +5707,27 @@
         <v>134</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5656,27 +5735,27 @@
         <v>165</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5684,13 +5763,13 @@
         <v>172</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5698,27 +5777,27 @@
         <v>172</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5726,13 +5805,13 @@
         <v>182</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5740,13 +5819,13 @@
         <v>182</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5754,41 +5833,41 @@
         <v>182</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="53" t="s">
+    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="B61" s="53" t="s">
+      <c r="B62" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="C61" s="53" t="s">
+      <c r="C62" s="53" t="s">
         <v>195</v>
       </c>
-      <c r="D61" s="53" t="s">
+      <c r="D62" s="53" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="B62" s="54" t="s">
-        <v>197</v>
-      </c>
-      <c r="C62" s="54" t="s">
-        <v>198</v>
-      </c>
-      <c r="D62" s="54" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5796,26 +5875,40 @@
         <v>182</v>
       </c>
       <c r="B63" s="54" t="s">
+        <v>197</v>
+      </c>
+      <c r="C63" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="D63" s="54" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C63" s="54" t="s">
+      <c r="C64" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="D63" s="54" t="s">
+      <c r="D64" s="54" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="55" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="55" t="s">
         <v>407</v>
       </c>
-      <c r="B64" s="55" t="s">
+      <c r="B65" s="55" t="s">
         <v>406</v>
       </c>
-      <c r="C64" s="55" t="s">
+      <c r="C65" s="55" t="s">
         <v>408</v>
       </c>
-      <c r="D64" s="55" t="s">
+      <c r="D65" s="55" t="s">
         <v>409</v>
       </c>
     </row>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566290ED-BE12-9541-8B16-98427988A5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E5A693-E08B-B741-8E92-B1B3B067D954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51200" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4003,12 +4003,12 @@
         <v>0.5</v>
       </c>
       <c r="N45" s="79">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="O45" s="10"/>
       <c r="P45" s="10">
         <f>K45*N45</f>
-        <v>0.94499999999999995</v>
+        <v>0.84</v>
       </c>
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
@@ -4217,13 +4217,11 @@
         <v>12</v>
       </c>
       <c r="M50" s="17"/>
-      <c r="N50" s="79">
-        <v>2</v>
-      </c>
+      <c r="N50" s="79"/>
       <c r="O50" s="10"/>
       <c r="P50" s="10">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
@@ -4262,13 +4260,11 @@
         <v>12</v>
       </c>
       <c r="M51" s="17"/>
-      <c r="N51" s="79">
-        <v>1</v>
-      </c>
+      <c r="N51" s="79"/>
       <c r="O51" s="10"/>
       <c r="P51" s="10">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
@@ -4864,6 +4860,30 @@
       </filters>
     </filterColumn>
   </autoFilter>
+  <conditionalFormatting sqref="G47">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H47">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M1">
     <cfRule type="colorScale" priority="8">
       <colorScale>
@@ -4960,30 +4980,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G47">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H47">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E5A693-E08B-B741-8E92-B1B3B067D954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F87293-3617-F647-AC60-0D2F7650D437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33320" yWindow="4420" windowWidth="29760" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>226</v>
       </c>
@@ -2718,7 +2718,9 @@
         <v>12</v>
       </c>
       <c r="M14" s="17"/>
-      <c r="N14" s="79"/>
+      <c r="N14" s="79">
+        <v>0.5</v>
+      </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10">
         <f t="shared" si="1"/>
@@ -2726,11 +2728,11 @@
       </c>
       <c r="Q14" s="10">
         <f>K14*N14</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
@@ -2764,7 +2766,9 @@
         <v>12</v>
       </c>
       <c r="M15" s="17"/>
-      <c r="N15" s="79"/>
+      <c r="N15" s="79">
+        <v>0.5</v>
+      </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10">
         <f t="shared" si="1"/>
@@ -2772,11 +2776,11 @@
       </c>
       <c r="Q15" s="10">
         <f>K15*N15</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -2806,7 +2810,9 @@
         <v>12</v>
       </c>
       <c r="M16" s="17"/>
-      <c r="N16" s="79"/>
+      <c r="N16" s="79">
+        <v>0.5</v>
+      </c>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
       <c r="Q16" s="11"/>
@@ -3624,7 +3630,9 @@
         <v>10</v>
       </c>
       <c r="M36" s="17"/>
-      <c r="N36" s="79"/>
+      <c r="N36" s="79">
+        <v>0.25</v>
+      </c>
       <c r="O36" s="10"/>
       <c r="P36" s="10">
         <f t="shared" si="2"/>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="Q36" s="10">
         <f>K36*N36</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="R36" s="11"/>
     </row>
@@ -3666,7 +3674,9 @@
         <v>10</v>
       </c>
       <c r="M37" s="17"/>
-      <c r="N37" s="79"/>
+      <c r="N37" s="79">
+        <v>0.25</v>
+      </c>
       <c r="O37" s="10"/>
       <c r="P37" s="10">
         <f t="shared" si="2"/>
@@ -3705,7 +3715,9 @@
         <v>10</v>
       </c>
       <c r="M38" s="17"/>
-      <c r="N38" s="79"/>
+      <c r="N38" s="79">
+        <v>0.25</v>
+      </c>
       <c r="O38" s="10"/>
       <c r="P38" s="10">
         <f t="shared" si="2"/>
@@ -3838,7 +3850,7 @@
       </c>
       <c r="R41" s="11"/>
     </row>
-    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>226</v>
       </c>
@@ -3888,7 +3900,7 @@
       </c>
       <c r="R42" s="11"/>
     </row>
-    <row r="43" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" s="4" customFormat="1" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>226</v>
       </c>
@@ -3931,7 +3943,7 @@
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
     </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>226</v>
       </c>
@@ -3970,7 +3982,7 @@
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -4013,7 +4025,7 @@
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>226</v>
       </c>
@@ -4056,7 +4068,7 @@
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
     </row>
-    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>226</v>
       </c>
@@ -4099,7 +4111,7 @@
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
     </row>
-    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>226</v>
       </c>
@@ -4144,7 +4156,7 @@
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
     </row>
-    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>226</v>
       </c>
@@ -4183,7 +4195,7 @@
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
     </row>
-    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>226</v>
       </c>
@@ -4226,7 +4238,7 @@
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
     </row>
-    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>226</v>
       </c>
@@ -4269,7 +4281,7 @@
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>226</v>
       </c>
@@ -4856,7 +4868,7 @@
   <autoFilter ref="A1:R66" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="TRNS"/>
+        <filter val="INEN"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F87293-3617-F647-AC60-0D2F7650D437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D3ED07-2E5F-F34E-BA5A-3490D5E66EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-33320" yWindow="4420" windowWidth="29760" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2106,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R66"/>
@@ -2175,7 +2175,7 @@
       <c r="Q1" s="11"/>
       <c r="R1" s="11"/>
     </row>
-    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>212</v>
       </c>
@@ -2216,7 +2216,7 @@
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
     </row>
-    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>212</v>
       </c>
@@ -2255,7 +2255,7 @@
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
     </row>
-    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>212</v>
       </c>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="R4" s="11"/>
     </row>
-    <row r="5" spans="1:18" s="4" customFormat="1" ht="95.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>212</v>
       </c>
@@ -2335,7 +2335,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
     </row>
-    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>212</v>
       </c>
@@ -2378,7 +2378,7 @@
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>226</v>
       </c>
@@ -2417,7 +2417,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>226</v>
       </c>
@@ -2510,7 +2510,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>226</v>
       </c>
@@ -2557,7 +2557,7 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>226</v>
       </c>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>226</v>
       </c>
@@ -2818,7 +2818,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="64" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" s="64" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="R17" s="63"/>
     </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2907,7 +2907,7 @@
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2950,7 +2950,7 @@
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -2989,7 +2989,7 @@
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
@@ -3067,7 +3067,7 @@
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
     </row>
-    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>212</v>
       </c>
@@ -3101,7 +3101,9 @@
         <v>10</v>
       </c>
       <c r="M23" s="17"/>
-      <c r="N23" s="79"/>
+      <c r="N23" s="79">
+        <v>0.99</v>
+      </c>
       <c r="O23" s="66"/>
       <c r="P23" s="66">
         <f t="shared" si="2"/>
@@ -3109,11 +3111,11 @@
       </c>
       <c r="Q23" s="67">
         <f>K23*N23</f>
-        <v>0</v>
+        <v>0.98900999999999994</v>
       </c>
       <c r="R23" s="11"/>
     </row>
-    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>212</v>
       </c>
@@ -3156,7 +3158,7 @@
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>212</v>
       </c>
@@ -3190,7 +3192,9 @@
         <v>8</v>
       </c>
       <c r="M25" s="17"/>
-      <c r="N25" s="79"/>
+      <c r="N25" s="79">
+        <v>1</v>
+      </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10">
         <f t="shared" si="2"/>
@@ -3198,11 +3202,11 @@
       </c>
       <c r="Q25" s="67">
         <f>K25*N25</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R25" s="11"/>
     </row>
-    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>212</v>
       </c>
@@ -3245,7 +3249,7 @@
       <c r="Q26" s="11"/>
       <c r="R26" s="11"/>
     </row>
-    <row r="27" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>212</v>
       </c>
@@ -3284,7 +3288,7 @@
       <c r="Q27" s="11"/>
       <c r="R27" s="28"/>
     </row>
-    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>212</v>
       </c>
@@ -3323,7 +3327,7 @@
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>212</v>
       </c>
@@ -3362,7 +3366,7 @@
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
     </row>
-    <row r="30" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>212</v>
       </c>
@@ -3401,7 +3405,7 @@
       <c r="Q30" s="11"/>
       <c r="R30" s="11"/>
     </row>
-    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>212</v>
       </c>
@@ -3440,7 +3444,7 @@
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
     </row>
-    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>212</v>
       </c>
@@ -3479,7 +3483,7 @@
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
     </row>
-    <row r="33" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>212</v>
       </c>
@@ -3522,7 +3526,7 @@
       <c r="Q33" s="17"/>
       <c r="R33" s="29"/>
     </row>
-    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>309</v>
       </c>
@@ -3561,7 +3565,7 @@
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
     </row>
-    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>309</v>
       </c>
@@ -3600,7 +3604,7 @@
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
     </row>
-    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>226</v>
       </c>
@@ -3644,7 +3648,7 @@
       </c>
       <c r="R36" s="11"/>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>226</v>
       </c>
@@ -3685,7 +3689,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>226</v>
       </c>
@@ -3726,7 +3730,7 @@
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
     </row>
-    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>212</v>
       </c>
@@ -3765,7 +3769,7 @@
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
     </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>212</v>
       </c>
@@ -3804,7 +3808,7 @@
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
     </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>226</v>
       </c>
@@ -3850,7 +3854,7 @@
       </c>
       <c r="R41" s="11"/>
     </row>
-    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>226</v>
       </c>
@@ -3900,7 +3904,7 @@
       </c>
       <c r="R42" s="11"/>
     </row>
-    <row r="43" spans="1:18" s="4" customFormat="1" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>226</v>
       </c>
@@ -3943,7 +3947,7 @@
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
     </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>226</v>
       </c>
@@ -3982,7 +3986,7 @@
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -4025,7 +4029,7 @@
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>226</v>
       </c>
@@ -4068,7 +4072,7 @@
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
     </row>
-    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>226</v>
       </c>
@@ -4111,7 +4115,7 @@
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
     </row>
-    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>226</v>
       </c>
@@ -4156,7 +4160,7 @@
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
     </row>
-    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>226</v>
       </c>
@@ -4195,7 +4199,7 @@
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
     </row>
-    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>226</v>
       </c>
@@ -4238,7 +4242,7 @@
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
     </row>
-    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>226</v>
       </c>
@@ -4281,7 +4285,7 @@
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>226</v>
       </c>
@@ -4321,7 +4325,7 @@
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
     </row>
-    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>51</v>
       </c>
@@ -4360,7 +4364,7 @@
       <c r="Q53" s="11"/>
       <c r="R53" s="11"/>
     </row>
-    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>51</v>
       </c>
@@ -4403,7 +4407,7 @@
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
     </row>
-    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>369</v>
       </c>
@@ -4443,7 +4447,7 @@
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
     </row>
-    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>369</v>
       </c>
@@ -4483,7 +4487,7 @@
       <c r="Q56" s="11"/>
       <c r="R56" s="11"/>
     </row>
-    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>369</v>
       </c>
@@ -4523,7 +4527,7 @@
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
     </row>
-    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>369</v>
       </c>
@@ -4566,7 +4570,7 @@
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
     </row>
-    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>369</v>
       </c>
@@ -4602,7 +4606,7 @@
       <c r="Q59" s="11"/>
       <c r="R59" s="11"/>
     </row>
-    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>369</v>
       </c>
@@ -4645,7 +4649,7 @@
       <c r="Q60" s="11"/>
       <c r="R60" s="11"/>
     </row>
-    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>369</v>
       </c>
@@ -4684,7 +4688,7 @@
       <c r="Q61" s="11"/>
       <c r="R61" s="11"/>
     </row>
-    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>369</v>
       </c>
@@ -4723,7 +4727,7 @@
       <c r="Q62" s="11"/>
       <c r="R62" s="11"/>
     </row>
-    <row r="63" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="40" t="s">
         <v>369</v>
       </c>
@@ -4766,7 +4770,7 @@
       <c r="Q63" s="11"/>
       <c r="R63" s="11"/>
     </row>
-    <row r="64" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="44" t="s">
         <v>369</v>
       </c>
@@ -4809,7 +4813,7 @@
       <c r="Q64" s="11"/>
       <c r="R64" s="11"/>
     </row>
-    <row r="65" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="45" t="s">
         <v>226</v>
       </c>
@@ -4844,7 +4848,7 @@
       <c r="Q65" s="11"/>
       <c r="R65" s="28"/>
     </row>
-    <row r="66" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="31"/>
       <c r="B66" s="31"/>
       <c r="C66" s="31"/>
@@ -4865,13 +4869,7 @@
       <c r="R66" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R66" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="INEN"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R66" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="G47">
     <cfRule type="colorScale" priority="2">
       <colorScale>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D3ED07-2E5F-F34E-BA5A-3490D5E66EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D560ABB-06E2-3149-82F6-6773D7C1836B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33320" yWindow="4420" windowWidth="29760" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-42960" yWindow="600" windowWidth="35620" windowHeight="21980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$R$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$R$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$67</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="428">
   <si>
     <t>subsector</t>
   </si>
@@ -1342,6 +1342,33 @@
   </si>
   <si>
     <t>transformation_trns_shift_fuel_public.yaml</t>
+  </si>
+  <si>
+    <t>TX:SCOE:INC_EFFICIENCY_HEAT</t>
+  </si>
+  <si>
+    <t>Increase heat efficiency</t>
+  </si>
+  <si>
+    <t>transformation_scoe_inc_efficiency_heat.yaml</t>
+  </si>
+  <si>
+    <t>TX:LNDU:PLUR</t>
+  </si>
+  <si>
+    <t>Partial land use reallocation</t>
+  </si>
+  <si>
+    <t>transformation_lndu_plur.yaml</t>
+  </si>
+  <si>
+    <t>TX:LNDU:BOUND_CLASSES</t>
+  </si>
+  <si>
+    <t>Bound Classes</t>
+  </si>
+  <si>
+    <t>transformation_lndu_bound_classes.yaml</t>
   </si>
 </sst>
 </file>
@@ -1554,7 +1581,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1748,9 +1775,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -1801,6 +1825,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2106,10 +2136,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="13.1640625" style="34" bestFit="1" customWidth="1"/>
@@ -2182,10 +2212,10 @@
       <c r="B2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="69" t="s">
+      <c r="D2" s="68" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="13" t="s">
@@ -2223,10 +2253,10 @@
       <c r="B3" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="69" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="58" t="s">
@@ -2262,10 +2292,10 @@
       <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="68" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="13" t="s">
@@ -2303,10 +2333,10 @@
       <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="74" t="s">
+      <c r="C5" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="68" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="13" t="s">
@@ -2326,7 +2356,9 @@
         <v>12</v>
       </c>
       <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
+      <c r="N5" s="17">
+        <v>1</v>
+      </c>
       <c r="O5" s="10"/>
       <c r="P5" s="10" t="e">
         <f t="shared" si="0"/>
@@ -2342,10 +2374,10 @@
       <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="68" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="13" t="s">
@@ -2378,7 +2410,7 @@
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>226</v>
       </c>
@@ -2408,7 +2440,7 @@
         <v>12</v>
       </c>
       <c r="M7" s="17"/>
-      <c r="N7" s="79"/>
+      <c r="N7" s="78"/>
       <c r="O7" s="10"/>
       <c r="P7" s="10">
         <f t="shared" si="0"/>
@@ -2417,7 +2449,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2450,10 +2482,10 @@
       <c r="L8" s="16">
         <v>10</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="78">
         <v>1</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="78">
         <v>1</v>
       </c>
       <c r="O8" s="10"/>
@@ -2467,7 +2499,7 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>226</v>
       </c>
@@ -2501,7 +2533,7 @@
         <v>12</v>
       </c>
       <c r="M9" s="17"/>
-      <c r="N9" s="79"/>
+      <c r="N9" s="78"/>
       <c r="O9" s="10"/>
       <c r="P9" s="10">
         <f t="shared" ref="P9:P15" si="1">K9*M9</f>
@@ -2510,7 +2542,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>226</v>
       </c>
@@ -2543,10 +2575,10 @@
       <c r="L10" s="16">
         <v>12</v>
       </c>
-      <c r="M10" s="79">
+      <c r="M10" s="78">
         <v>1</v>
       </c>
-      <c r="N10" s="79">
+      <c r="N10" s="78">
         <v>1</v>
       </c>
       <c r="O10" s="10"/>
@@ -2557,7 +2589,7 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>226</v>
       </c>
@@ -2597,7 +2629,7 @@
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
@@ -2627,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="17"/>
-      <c r="N12" s="79"/>
+      <c r="N12" s="78"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10">
         <f t="shared" si="1"/>
@@ -2639,7 +2671,7 @@
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>226</v>
       </c>
@@ -2668,23 +2700,23 @@
       <c r="L13" s="16">
         <v>12</v>
       </c>
-      <c r="M13" s="78"/>
-      <c r="N13" s="79"/>
+      <c r="M13" s="77"/>
+      <c r="N13" s="78"/>
       <c r="O13" s="10" t="e">
         <f>K13*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="P13" s="66">
+      <c r="P13" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="66">
+      <c r="Q13" s="65">
         <f>K13*N13</f>
         <v>0</v>
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>226</v>
       </c>
@@ -2718,7 +2750,7 @@
         <v>12</v>
       </c>
       <c r="M14" s="17"/>
-      <c r="N14" s="79">
+      <c r="N14" s="78">
         <v>0.5</v>
       </c>
       <c r="O14" s="10"/>
@@ -2732,7 +2764,7 @@
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
@@ -2766,7 +2798,7 @@
         <v>12</v>
       </c>
       <c r="M15" s="17"/>
-      <c r="N15" s="79">
+      <c r="N15" s="78">
         <v>0.5</v>
       </c>
       <c r="O15" s="10"/>
@@ -2780,7 +2812,7 @@
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -2810,7 +2842,7 @@
         <v>12</v>
       </c>
       <c r="M16" s="17"/>
-      <c r="N16" s="79">
+      <c r="N16" s="78">
         <v>0.5</v>
       </c>
       <c r="O16" s="10"/>
@@ -2818,7 +2850,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="64" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" s="64" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2848,14 +2880,14 @@
       <c r="K17" s="15">
         <v>0.5</v>
       </c>
-      <c r="L17" s="80">
+      <c r="L17" s="79">
         <v>12</v>
       </c>
-      <c r="M17" s="81"/>
-      <c r="N17" s="82"/>
+      <c r="M17" s="80"/>
+      <c r="N17" s="81"/>
       <c r="O17" s="10"/>
       <c r="P17" s="10">
-        <f t="shared" ref="P17:P41" si="2">K17*M17</f>
+        <f t="shared" ref="P17:P44" si="2">K17*M17</f>
         <v>0</v>
       </c>
       <c r="Q17" s="10">
@@ -2864,7 +2896,7 @@
       </c>
       <c r="R17" s="63"/>
     </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2898,7 +2930,7 @@
         <v>12</v>
       </c>
       <c r="M18" s="17"/>
-      <c r="N18" s="79"/>
+      <c r="N18" s="78"/>
       <c r="O18" s="10"/>
       <c r="P18" s="10">
         <f t="shared" si="2"/>
@@ -2907,7 +2939,7 @@
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2941,7 +2973,7 @@
         <v>12</v>
       </c>
       <c r="M19" s="17"/>
-      <c r="N19" s="79"/>
+      <c r="N19" s="78"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10">
         <f t="shared" si="2"/>
@@ -2950,7 +2982,7 @@
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -2980,7 +3012,7 @@
         <v>12</v>
       </c>
       <c r="M20" s="17"/>
-      <c r="N20" s="79"/>
+      <c r="N20" s="78"/>
       <c r="O20" s="10"/>
       <c r="P20" s="10">
         <f t="shared" si="2"/>
@@ -2989,7 +3021,7 @@
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -3019,7 +3051,7 @@
         <v>12</v>
       </c>
       <c r="M21" s="17"/>
-      <c r="N21" s="79"/>
+      <c r="N21" s="78"/>
       <c r="O21" s="10"/>
       <c r="P21" s="10">
         <f t="shared" si="2"/>
@@ -3028,7 +3060,7 @@
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
@@ -3058,7 +3090,7 @@
         <v>12</v>
       </c>
       <c r="M22" s="17"/>
-      <c r="N22" s="79"/>
+      <c r="N22" s="78"/>
       <c r="O22" s="10"/>
       <c r="P22" s="10">
         <f t="shared" si="2"/>
@@ -3101,17 +3133,17 @@
         <v>10</v>
       </c>
       <c r="M23" s="17"/>
-      <c r="N23" s="79">
-        <v>0.99</v>
-      </c>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66">
+      <c r="N23" s="84">
+        <v>0.98999899999999996</v>
+      </c>
+      <c r="O23" s="65"/>
+      <c r="P23" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="67">
+      <c r="Q23" s="66">
         <f>K23*N23</f>
-        <v>0.98900999999999994</v>
+        <v>0.989009001</v>
       </c>
       <c r="R23" s="11"/>
     </row>
@@ -3123,39 +3155,44 @@
         <v>70</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>74</v>
+        <v>425</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="J24" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="K24" s="19">
+        <v>426</v>
+      </c>
+      <c r="E24" s="19">
         <v>0.95</v>
       </c>
+      <c r="F24" s="16">
+        <v>12</v>
+      </c>
+      <c r="G24" s="17"/>
+      <c r="H24" s="78">
+        <v>1</v>
+      </c>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10">
+        <v>0</v>
+      </c>
+      <c r="K24" s="15">
+        <v>0.999</v>
+      </c>
       <c r="L24" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M24" s="17"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10">
+      <c r="N24" s="84">
+        <v>1</v>
+      </c>
+      <c r="O24" s="65"/>
+      <c r="P24" s="65">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="11"/>
+      <c r="Q24" s="66">
+        <f>K24*N24</f>
+        <v>0.999</v>
+      </c>
       <c r="R24" s="11"/>
     </row>
     <row r="25" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -3166,33 +3203,33 @@
         <v>70</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="60" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="59" t="s">
-        <v>283</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>284</v>
+        <v>74</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>280</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
-      <c r="I25" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="K25" s="15">
-        <v>0.2</v>
+      <c r="I25" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="K25" s="19">
+        <v>0.95</v>
       </c>
       <c r="L25" s="16">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M25" s="17"/>
-      <c r="N25" s="79">
+      <c r="N25" s="78">
         <v>1</v>
       </c>
       <c r="O25" s="10"/>
@@ -3200,9 +3237,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="67">
+      <c r="Q25" s="66">
         <f>K25*N25</f>
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="R25" s="11"/>
     </row>
@@ -3214,120 +3251,140 @@
         <v>70</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>288</v>
+        <v>77</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="59" t="s">
+        <v>283</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>284</v>
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
-      <c r="I26" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="K26" s="19">
-        <v>0.1</v>
+      <c r="I26" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="K26" s="15">
+        <v>0.2</v>
       </c>
       <c r="L26" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M26" s="17"/>
-      <c r="N26" s="79"/>
+      <c r="N26" s="78">
+        <v>4</v>
+      </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="11"/>
+      <c r="Q26" s="66">
+        <f>K26*N26</f>
+        <v>0.8</v>
+      </c>
       <c r="R26" s="11"/>
     </row>
-    <row r="27" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="19">
-        <v>0.9</v>
+        <v>423</v>
+      </c>
+      <c r="E27" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="F27" s="16">
+        <v>12</v>
+      </c>
+      <c r="G27" s="17"/>
+      <c r="H27" s="78">
+        <v>1</v>
+      </c>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10">
+        <v>0</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0.5</v>
       </c>
       <c r="L27" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M27" s="17"/>
-      <c r="N27" s="79"/>
+      <c r="N27" s="78">
+        <v>1</v>
+      </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="28"/>
+      <c r="Q27" s="66">
+        <f>K27*N27</f>
+        <v>0.5</v>
+      </c>
+      <c r="R27" s="11"/>
     </row>
     <row r="28" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="19" t="s">
-        <v>295</v>
+      <c r="I28" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0.1</v>
       </c>
       <c r="L28" s="16">
         <v>12</v>
       </c>
       <c r="M28" s="17"/>
-      <c r="N28" s="79"/>
+      <c r="N28" s="78">
+        <v>1</v>
+      </c>
       <c r="O28" s="10"/>
-      <c r="P28" s="10" t="e">
+      <c r="P28" s="10">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>212</v>
       </c>
@@ -3335,36 +3392,38 @@
         <v>83</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="19" t="s">
-        <v>297</v>
+      <c r="K29" s="19">
+        <v>0.9</v>
       </c>
       <c r="L29" s="16">
         <v>12</v>
       </c>
       <c r="M29" s="17"/>
-      <c r="N29" s="79"/>
+      <c r="N29" s="78">
+        <v>1</v>
+      </c>
       <c r="O29" s="10"/>
-      <c r="P29" s="10" t="e">
+      <c r="P29" s="10">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
+      <c r="R29" s="28"/>
     </row>
     <row r="30" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
@@ -3374,13 +3433,13 @@
         <v>83</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>294</v>
@@ -3390,13 +3449,15 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="19" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="L30" s="16">
         <v>12</v>
       </c>
       <c r="M30" s="17"/>
-      <c r="N30" s="79"/>
+      <c r="N30" s="78">
+        <v>1</v>
+      </c>
       <c r="O30" s="10"/>
       <c r="P30" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3410,32 +3471,32 @@
         <v>212</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" s="69" t="s">
-        <v>98</v>
+        <v>83</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>91</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
-      <c r="K31" s="15" t="s">
-        <v>302</v>
+      <c r="K31" s="19" t="s">
+        <v>297</v>
       </c>
       <c r="L31" s="16">
         <v>12</v>
       </c>
       <c r="M31" s="17"/>
-      <c r="N31" s="79"/>
+      <c r="N31" s="78"/>
       <c r="O31" s="10"/>
       <c r="P31" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3449,101 +3510,97 @@
         <v>212</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="69" t="s">
-        <v>101</v>
+        <v>83</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
-      <c r="K32" s="19">
-        <v>0.5</v>
+      <c r="K32" s="19" t="s">
+        <v>299</v>
       </c>
       <c r="L32" s="16">
         <v>12</v>
       </c>
       <c r="M32" s="17"/>
-      <c r="N32" s="79"/>
+      <c r="N32" s="78"/>
       <c r="O32" s="10"/>
-      <c r="P32" s="10">
+      <c r="P32" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
     </row>
-    <row r="33" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="74" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" s="69" t="s">
-        <v>104</v>
+      <c r="C33" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="68" t="s">
+        <v>98</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="12" t="s">
-        <v>307</v>
-      </c>
-      <c r="J33" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="K33" s="19">
-        <v>0.3</v>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="15" t="s">
+        <v>302</v>
       </c>
       <c r="L33" s="16">
         <v>12</v>
       </c>
       <c r="M33" s="17"/>
-      <c r="N33" s="79"/>
+      <c r="N33" s="78"/>
       <c r="O33" s="10"/>
-      <c r="P33" s="10">
+      <c r="P33" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="29"/>
-    </row>
-    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+    </row>
+    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
-        <v>309</v>
+        <v>212</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>108</v>
+        <v>96</v>
+      </c>
+      <c r="C34" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="68" t="s">
+        <v>101</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
@@ -3556,7 +3613,7 @@
         <v>12</v>
       </c>
       <c r="M34" s="17"/>
-      <c r="N34" s="79"/>
+      <c r="N34" s="78"/>
       <c r="O34" s="10"/>
       <c r="P34" s="10">
         <f t="shared" si="2"/>
@@ -3565,122 +3622,119 @@
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
     </row>
-    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
-        <v>309</v>
+        <v>212</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>111</v>
+        <v>96</v>
+      </c>
+      <c r="C35" s="73" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>104</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
+      <c r="I35" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>308</v>
+      </c>
       <c r="K35" s="19">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="L35" s="16">
         <v>12</v>
       </c>
       <c r="M35" s="17"/>
-      <c r="N35" s="79"/>
+      <c r="N35" s="78"/>
       <c r="O35" s="10"/>
       <c r="P35" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-    </row>
-    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q35" s="17"/>
+      <c r="R35" s="29"/>
+    </row>
+    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
-        <v>226</v>
+        <v>309</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="65" t="s">
-        <v>114</v>
+        <v>106</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
-      <c r="K36" s="20">
+      <c r="K36" s="19">
         <v>0.5</v>
       </c>
       <c r="L36" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M36" s="17"/>
-      <c r="N36" s="79">
-        <v>0.25</v>
-      </c>
+      <c r="N36" s="78"/>
       <c r="O36" s="10"/>
       <c r="P36" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="10">
-        <f>K36*N36</f>
-        <v>0.125</v>
-      </c>
+      <c r="Q36" s="11"/>
       <c r="R36" s="11"/>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
-        <v>226</v>
+        <v>309</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" s="65" t="s">
-        <v>117</v>
+        <v>106</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
       <c r="K37" s="19">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L37" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M37" s="17"/>
-      <c r="N37" s="79">
-        <v>0.25</v>
-      </c>
+      <c r="N37" s="78"/>
       <c r="O37" s="10"/>
       <c r="P37" s="10">
         <f t="shared" si="2"/>
@@ -3689,38 +3743,40 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>120</v>
+      <c r="C38" s="83" t="s">
+        <v>419</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
+        <v>420</v>
+      </c>
+      <c r="E38" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="F38" s="16">
+        <v>10</v>
+      </c>
+      <c r="G38" s="17"/>
+      <c r="H38" s="78">
+        <v>0.25</v>
+      </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
-      <c r="K38" s="20">
-        <v>0.95</v>
+      <c r="K38" s="82">
+        <v>0.2</v>
       </c>
       <c r="L38" s="16">
         <v>10</v>
       </c>
       <c r="M38" s="17"/>
-      <c r="N38" s="79">
-        <v>0.25</v>
+      <c r="N38" s="78">
+        <v>1</v>
       </c>
       <c r="O38" s="10"/>
       <c r="P38" s="10">
@@ -3730,76 +3786,83 @@
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
     </row>
-    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>124</v>
+        <v>113</v>
+      </c>
+      <c r="C39" s="83" t="s">
+        <v>114</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
-      <c r="K39" s="19">
-        <v>0.2</v>
+      <c r="K39" s="20">
+        <v>0.5</v>
       </c>
       <c r="L39" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M39" s="17"/>
-      <c r="N39" s="79"/>
+      <c r="N39" s="78">
+        <v>0.1</v>
+      </c>
       <c r="O39" s="10"/>
       <c r="P39" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q39" s="11"/>
+      <c r="Q39" s="10">
+        <f>K39*N39</f>
+        <v>0.05</v>
+      </c>
       <c r="R39" s="11"/>
     </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>127</v>
+        <v>113</v>
+      </c>
+      <c r="C40" s="83" t="s">
+        <v>117</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
       <c r="K40" s="19">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L40" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M40" s="17"/>
-      <c r="N40" s="79"/>
+      <c r="N40" s="78">
+        <v>1</v>
+      </c>
       <c r="O40" s="10"/>
       <c r="P40" s="10">
         <f t="shared" si="2"/>
@@ -3808,168 +3871,154 @@
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
     </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>131</v>
+        <v>113</v>
+      </c>
+      <c r="C41" s="83" t="s">
+        <v>120</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="K41" s="19">
-        <v>0.25</v>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="20">
+        <v>0.95</v>
       </c>
       <c r="L41" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M41" s="17"/>
-      <c r="N41" s="79"/>
+      <c r="N41" s="78">
+        <v>1</v>
+      </c>
       <c r="O41" s="10"/>
       <c r="P41" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="10">
-        <f>K41*N41</f>
-        <v>0</v>
-      </c>
+      <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
     </row>
     <row r="42" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="G42" s="12"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>331</v>
-      </c>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
       <c r="K42" s="19">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="L42" s="16">
         <v>12</v>
       </c>
-      <c r="M42" s="17">
-        <v>1</v>
-      </c>
-      <c r="N42" s="17">
-        <v>1</v>
-      </c>
+      <c r="M42" s="17"/>
+      <c r="N42" s="78"/>
       <c r="O42" s="10"/>
       <c r="P42" s="10">
-        <f>K42*N42</f>
-        <v>0.25</v>
-      </c>
-      <c r="Q42" s="10">
-        <f>K42*P42</f>
-        <v>6.25E-2</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
     </row>
-    <row r="43" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="G43" s="12"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>335</v>
-      </c>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
       <c r="K43" s="19">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="L43" s="16">
         <v>12</v>
       </c>
       <c r="M43" s="17"/>
-      <c r="N43" s="79"/>
+      <c r="N43" s="78">
+        <v>1</v>
+      </c>
       <c r="O43" s="10"/>
       <c r="P43" s="10">
-        <f t="shared" ref="P43:P51" si="3">K43*N43</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
     </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
+      <c r="I44" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>327</v>
+      </c>
       <c r="K44" s="19">
         <v>0.25</v>
       </c>
@@ -3977,16 +4026,19 @@
         <v>12</v>
       </c>
       <c r="M44" s="17"/>
-      <c r="N44" s="79"/>
+      <c r="N44" s="78"/>
       <c r="O44" s="10"/>
       <c r="P44" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q44" s="11"/>
+      <c r="Q44" s="10">
+        <f>K44*N44</f>
+        <v>0</v>
+      </c>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -3994,42 +4046,49 @@
         <v>134</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>331</v>
+      </c>
       <c r="K45" s="19">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="L45" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M45" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="N45" s="79">
-        <v>1.2</v>
+        <v>1</v>
+      </c>
+      <c r="N45" s="17">
+        <v>1</v>
       </c>
       <c r="O45" s="10"/>
       <c r="P45" s="10">
         <f>K45*N45</f>
-        <v>0.84</v>
-      </c>
-      <c r="Q45" s="11"/>
+        <v>0.25</v>
+      </c>
+      <c r="Q45" s="10">
+        <f>K45*P45</f>
+        <v>6.25E-2</v>
+      </c>
       <c r="R45" s="11"/>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>226</v>
       </c>
@@ -4037,42 +4096,42 @@
         <v>134</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
+      <c r="H46" s="30"/>
       <c r="I46" s="12" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="K46" s="19">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="L46" s="16">
         <v>12</v>
       </c>
       <c r="M46" s="17"/>
-      <c r="N46" s="79"/>
+      <c r="N46" s="78"/>
       <c r="O46" s="10"/>
       <c r="P46" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="P46:P54" si="3">K46*N46</f>
         <v>0</v>
       </c>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
     </row>
-    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>226</v>
       </c>
@@ -4080,42 +4139,38 @@
         <v>134</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E47" s="20">
-        <v>0.7</v>
-      </c>
-      <c r="F47" s="16">
-        <v>12</v>
-      </c>
-      <c r="G47" s="17"/>
-      <c r="H47" s="79">
-        <v>0.8</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
       <c r="I47" s="12"/>
       <c r="J47" s="12"/>
-      <c r="K47" s="83">
-        <v>0.06</v>
+      <c r="K47" s="19">
+        <v>0.25</v>
       </c>
       <c r="L47" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M47" s="17"/>
-      <c r="N47" s="79">
-        <v>1</v>
-      </c>
+      <c r="N47" s="78"/>
       <c r="O47" s="10"/>
       <c r="P47" s="10">
         <f t="shared" si="3"/>
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
     </row>
-    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>226</v>
       </c>
@@ -4123,44 +4178,42 @@
         <v>134</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
-      <c r="I48" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="J48" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="K48" s="20">
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="19">
         <v>0.7</v>
       </c>
       <c r="L48" s="16">
-        <v>12</v>
-      </c>
-      <c r="M48" s="17"/>
-      <c r="N48" s="79">
-        <v>0.8</v>
+        <v>10</v>
+      </c>
+      <c r="M48" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="N48" s="78">
+        <v>1.2</v>
       </c>
       <c r="O48" s="10"/>
       <c r="P48" s="10">
-        <f t="shared" si="3"/>
-        <v>0.55999999999999994</v>
+        <f>K48*N48</f>
+        <v>0.84</v>
       </c>
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
     </row>
-    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>226</v>
       </c>
@@ -4168,29 +4221,33 @@
         <v>134</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
+      <c r="I49" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>343</v>
+      </c>
       <c r="K49" s="19">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="L49" s="16">
         <v>12</v>
       </c>
       <c r="M49" s="17"/>
-      <c r="N49" s="79"/>
+      <c r="N49" s="78"/>
       <c r="O49" s="10"/>
       <c r="P49" s="10">
         <f t="shared" si="3"/>
@@ -4199,7 +4256,7 @@
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
     </row>
-    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>226</v>
       </c>
@@ -4207,42 +4264,42 @@
         <v>134</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>156</v>
+        <v>416</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="K50" s="19">
-        <v>0.2</v>
+        <v>151</v>
+      </c>
+      <c r="E50" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="F50" s="16">
+        <v>12</v>
+      </c>
+      <c r="G50" s="17"/>
+      <c r="H50" s="78">
+        <v>0.8</v>
+      </c>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="82">
+        <v>0.06</v>
       </c>
       <c r="L50" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M50" s="17"/>
-      <c r="N50" s="79"/>
+      <c r="N50" s="78">
+        <v>1</v>
+      </c>
       <c r="O50" s="10"/>
       <c r="P50" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
     </row>
-    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>226</v>
       </c>
@@ -4250,42 +4307,44 @@
         <v>134</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="G51" s="12"/>
       <c r="H51" s="12"/>
       <c r="I51" s="12" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="K51" s="19">
-        <v>0.3</v>
+        <v>347</v>
+      </c>
+      <c r="K51" s="20">
+        <v>0.7</v>
       </c>
       <c r="L51" s="16">
         <v>12</v>
       </c>
       <c r="M51" s="17"/>
-      <c r="N51" s="79"/>
+      <c r="N51" s="78">
+        <v>0.8</v>
+      </c>
       <c r="O51" s="10"/>
       <c r="P51" s="10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.55999999999999994</v>
       </c>
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>226</v>
       </c>
@@ -4293,359 +4352,362 @@
         <v>134</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
-      <c r="I52" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="J52" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="K52" s="19" t="s">
-        <v>362</v>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="19">
+        <v>0.25</v>
       </c>
       <c r="L52" s="16">
         <v>12</v>
       </c>
       <c r="M52" s="17"/>
-      <c r="N52" s="79"/>
+      <c r="N52" s="78"/>
       <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
+      <c r="P52" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
     </row>
-    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="G53" s="12"/>
       <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
+      <c r="I53" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>353</v>
+      </c>
       <c r="K53" s="19">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
       <c r="L53" s="16">
         <v>12</v>
       </c>
       <c r="M53" s="17"/>
-      <c r="N53" s="79"/>
+      <c r="N53" s="78"/>
       <c r="O53" s="10"/>
       <c r="P53" s="10">
-        <f>K53*M53</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q53" s="11"/>
       <c r="R53" s="11"/>
     </row>
-    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="K54" s="19">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="L54" s="16">
         <v>12</v>
       </c>
       <c r="M54" s="17"/>
-      <c r="N54" s="79"/>
+      <c r="N54" s="78"/>
       <c r="O54" s="10"/>
       <c r="P54" s="10">
-        <f>K54*M54</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
     </row>
-    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
-        <v>369</v>
+        <v>226</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="G55" s="12"/>
       <c r="H55" s="12"/>
       <c r="I55" s="12" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="K55" s="19" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="L55" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M55" s="17"/>
-      <c r="N55" s="79"/>
+      <c r="N55" s="78"/>
       <c r="O55" s="10"/>
       <c r="P55" s="10"/>
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
     </row>
-    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
-        <v>369</v>
+        <v>51</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
-      <c r="I56" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="J56" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="K56" s="19" t="s">
-        <v>378</v>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="19">
+        <v>0.85</v>
       </c>
       <c r="L56" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M56" s="17"/>
-      <c r="N56" s="79"/>
+      <c r="N56" s="78"/>
       <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
+      <c r="P56" s="10">
+        <f>K56*M56</f>
+        <v>0</v>
+      </c>
       <c r="Q56" s="11"/>
       <c r="R56" s="11"/>
     </row>
-    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
-        <v>369</v>
+        <v>51</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G57" s="12"/>
       <c r="H57" s="12"/>
       <c r="I57" s="12" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="K57" s="19" t="s">
-        <v>382</v>
+        <v>368</v>
+      </c>
+      <c r="K57" s="19">
+        <v>0.9</v>
       </c>
       <c r="L57" s="16">
         <v>12</v>
       </c>
       <c r="M57" s="17"/>
-      <c r="N57" s="79"/>
+      <c r="N57" s="78"/>
       <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
+      <c r="P57" s="10">
+        <f>K57*M57</f>
+        <v>0</v>
+      </c>
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
     </row>
-    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>369</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C58" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="D58" s="69" t="s">
-        <v>184</v>
+        <v>172</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="G58" s="12"/>
       <c r="H58" s="12"/>
       <c r="I58" s="12" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="K58" s="19">
-        <v>0.3</v>
+        <v>373</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>374</v>
       </c>
       <c r="L58" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M58" s="17"/>
-      <c r="N58" s="79"/>
+      <c r="N58" s="78"/>
       <c r="O58" s="10"/>
-      <c r="P58" s="10">
-        <f>K58*M58</f>
-        <v>0</v>
-      </c>
+      <c r="P58" s="10"/>
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
     </row>
-    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>369</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C59" s="74" t="s">
-        <v>186</v>
-      </c>
-      <c r="D59" s="69" t="s">
-        <v>187</v>
+        <v>172</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>177</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="G59" s="12"/>
       <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="15" t="s">
-        <v>389</v>
+      <c r="I59" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>378</v>
       </c>
       <c r="L59" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M59" s="17"/>
-      <c r="N59" s="79"/>
+      <c r="N59" s="78"/>
       <c r="O59" s="10"/>
       <c r="P59" s="10"/>
       <c r="Q59" s="11"/>
       <c r="R59" s="11"/>
     </row>
-    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>369</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C60" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="D60" s="71" t="s">
-        <v>167</v>
-      </c>
-      <c r="E60" s="59" t="s">
-        <v>390</v>
-      </c>
-      <c r="F60" s="22" t="s">
-        <v>391</v>
+        <v>172</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>371</v>
       </c>
       <c r="G60" s="12"/>
       <c r="H60" s="12"/>
       <c r="I60" s="12" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="K60" s="15">
-        <v>0.85</v>
+        <v>381</v>
+      </c>
+      <c r="K60" s="19" t="s">
+        <v>382</v>
       </c>
       <c r="L60" s="16">
         <v>12</v>
       </c>
       <c r="M60" s="17"/>
-      <c r="N60" s="79"/>
+      <c r="N60" s="78"/>
       <c r="O60" s="10"/>
-      <c r="P60" s="10">
-        <f t="shared" ref="P60:P65" si="4">K60*M60</f>
-        <v>0</v>
-      </c>
+      <c r="P60" s="10"/>
       <c r="Q60" s="11"/>
       <c r="R60" s="11"/>
     </row>
@@ -4656,33 +4718,37 @@
       <c r="B61" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="74" t="s">
-        <v>191</v>
-      </c>
-      <c r="D61" s="69" t="s">
-        <v>192</v>
+      <c r="C61" s="73" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" s="68" t="s">
+        <v>184</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="15">
-        <v>0.85</v>
+      <c r="I61" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="K61" s="19">
+        <v>0.3</v>
       </c>
       <c r="L61" s="16">
         <v>12</v>
       </c>
       <c r="M61" s="17"/>
-      <c r="N61" s="79"/>
+      <c r="N61" s="78"/>
       <c r="O61" s="10"/>
       <c r="P61" s="10">
-        <f t="shared" si="4"/>
+        <f>K61*M61</f>
         <v>0</v>
       </c>
       <c r="Q61" s="11"/>
@@ -4695,116 +4761,113 @@
       <c r="B62" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="74" t="s">
-        <v>194</v>
-      </c>
-      <c r="D62" s="69" t="s">
-        <v>195</v>
+      <c r="C62" s="73" t="s">
+        <v>186</v>
+      </c>
+      <c r="D62" s="68" t="s">
+        <v>187</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="G62" s="12"/>
       <c r="H62" s="12"/>
       <c r="I62" s="12"/>
       <c r="J62" s="12"/>
-      <c r="K62" s="15">
-        <v>0.85</v>
+      <c r="K62" s="15" t="s">
+        <v>389</v>
       </c>
       <c r="L62" s="16">
         <v>12</v>
       </c>
       <c r="M62" s="17"/>
-      <c r="N62" s="79"/>
+      <c r="N62" s="78">
+        <v>1</v>
+      </c>
       <c r="O62" s="10"/>
-      <c r="P62" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="P62" s="10"/>
       <c r="Q62" s="11"/>
       <c r="R62" s="11"/>
     </row>
     <row r="63" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="40" t="s">
+      <c r="A63" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="B63" s="61" t="s">
+      <c r="B63" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C63" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="D63" s="72" t="s">
-        <v>198</v>
-      </c>
-      <c r="E63" s="61" t="s">
-        <v>398</v>
-      </c>
-      <c r="F63" s="40" t="s">
-        <v>399</v>
-      </c>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="40" t="s">
-        <v>400</v>
-      </c>
-      <c r="J63" s="40" t="s">
-        <v>401</v>
-      </c>
-      <c r="K63" s="41">
-        <v>1</v>
-      </c>
-      <c r="L63" s="42">
+      <c r="C63" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="D63" s="70" t="s">
+        <v>167</v>
+      </c>
+      <c r="E63" s="59" t="s">
+        <v>390</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="K63" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="L63" s="16">
         <v>12</v>
       </c>
-      <c r="M63" s="43"/>
-      <c r="N63" s="79"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="78"/>
       <c r="O63" s="10"/>
       <c r="P63" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="P63:P68" si="4">K63*M63</f>
         <v>0</v>
       </c>
       <c r="Q63" s="11"/>
       <c r="R63" s="11"/>
     </row>
     <row r="64" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="44" t="s">
+      <c r="A64" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="B64" s="45" t="s">
+      <c r="B64" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C64" s="77" t="s">
-        <v>200</v>
-      </c>
-      <c r="D64" s="73" t="s">
-        <v>201</v>
-      </c>
-      <c r="E64" s="45" t="s">
-        <v>402</v>
-      </c>
-      <c r="F64" s="44" t="s">
-        <v>403</v>
-      </c>
-      <c r="G64" s="44"/>
-      <c r="H64" s="44"/>
-      <c r="I64" s="44" t="s">
-        <v>404</v>
-      </c>
-      <c r="J64" s="44" t="s">
-        <v>405</v>
-      </c>
-      <c r="K64" s="46">
-        <v>0.95</v>
-      </c>
-      <c r="L64" s="47">
+      <c r="C64" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="L64" s="16">
         <v>12</v>
       </c>
-      <c r="M64" s="48"/>
-      <c r="N64" s="79"/>
+      <c r="M64" s="17"/>
+      <c r="N64" s="78">
+        <v>1</v>
+      </c>
       <c r="O64" s="10"/>
       <c r="P64" s="10">
         <f t="shared" si="4"/>
@@ -4813,64 +4876,367 @@
       <c r="Q64" s="11"/>
       <c r="R64" s="11"/>
     </row>
-    <row r="65" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="45" t="s">
-        <v>226</v>
-      </c>
-      <c r="B65" s="45" t="s">
-        <v>407</v>
-      </c>
-      <c r="C65" s="45" t="s">
-        <v>406</v>
-      </c>
-      <c r="D65" s="45" t="s">
-        <v>408</v>
-      </c>
-      <c r="E65" s="45"/>
-      <c r="F65" s="45"/>
-      <c r="G65" s="45"/>
-      <c r="H65" s="45"/>
-      <c r="I65" s="45"/>
-      <c r="J65" s="45"/>
-      <c r="K65" s="51">
-        <v>1.5</v>
-      </c>
-      <c r="L65" s="52">
+    <row r="65" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C65" s="73" t="s">
+        <v>194</v>
+      </c>
+      <c r="D65" s="68" t="s">
+        <v>195</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="L65" s="16">
         <v>12</v>
       </c>
-      <c r="M65" s="49"/>
-      <c r="N65" s="17"/>
-      <c r="O65" s="50"/>
-      <c r="P65" s="50">
+      <c r="M65" s="17"/>
+      <c r="N65" s="78"/>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q65" s="11"/>
-      <c r="R65" s="28"/>
-    </row>
-    <row r="66" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="31"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="31"/>
-      <c r="I66" s="31"/>
-      <c r="J66" s="31"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="32"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="33"/>
-      <c r="P66" s="33"/>
+      <c r="R65" s="11"/>
+    </row>
+    <row r="66" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="40" t="s">
+        <v>369</v>
+      </c>
+      <c r="B66" s="61" t="s">
+        <v>182</v>
+      </c>
+      <c r="C66" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="D66" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="E66" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="F66" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="40" t="s">
+        <v>400</v>
+      </c>
+      <c r="J66" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="K66" s="41">
+        <v>1</v>
+      </c>
+      <c r="L66" s="42">
+        <v>12</v>
+      </c>
+      <c r="M66" s="43"/>
+      <c r="N66" s="78"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="Q66" s="11"/>
-      <c r="R66" s="27"/>
+      <c r="R66" s="11"/>
+    </row>
+    <row r="67" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="44" t="s">
+        <v>369</v>
+      </c>
+      <c r="B67" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="C67" s="76" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="E67" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="F67" s="44" t="s">
+        <v>403</v>
+      </c>
+      <c r="G67" s="44"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="44" t="s">
+        <v>404</v>
+      </c>
+      <c r="J67" s="44" t="s">
+        <v>405</v>
+      </c>
+      <c r="K67" s="46">
+        <v>0.95</v>
+      </c>
+      <c r="L67" s="47">
+        <v>12</v>
+      </c>
+      <c r="M67" s="48"/>
+      <c r="N67" s="78"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q67" s="11"/>
+      <c r="R67" s="11"/>
+    </row>
+    <row r="68" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="C68" s="45" t="s">
+        <v>406</v>
+      </c>
+      <c r="D68" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="E68" s="45"/>
+      <c r="F68" s="45"/>
+      <c r="G68" s="45"/>
+      <c r="H68" s="45"/>
+      <c r="I68" s="45"/>
+      <c r="J68" s="45"/>
+      <c r="K68" s="51">
+        <v>1.5</v>
+      </c>
+      <c r="L68" s="52">
+        <v>12</v>
+      </c>
+      <c r="M68" s="49"/>
+      <c r="N68" s="17"/>
+      <c r="O68" s="50"/>
+      <c r="P68" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="11"/>
+      <c r="R68" s="28"/>
+    </row>
+    <row r="69" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="31"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="10"/>
+      <c r="L69" s="32"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="33"/>
+      <c r="P69" s="33"/>
+      <c r="Q69" s="11"/>
+      <c r="R69" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R66" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="G47">
+  <autoFilter ref="A1:R69" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="AGRC"/>
+        <filter val="LNDU"/>
+        <filter val="LSMM"/>
+        <filter val="SOIL"/>
+        <filter val="WASO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="G50">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H50">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M8">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M10">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M68:N1048576 M2:M7 M11:M67 M9">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N10 N12:N44 N46:N67">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N11">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N45">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -4882,104 +5248,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H47">
+  <conditionalFormatting sqref="H24">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M1">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M8">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M10">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M65:N1048576 M2:M7 M11:M64 M9">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10 N12:N41 N43:N64">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N11">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N42">
-    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4999,7 +5269,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" style="3" bestFit="1" customWidth="1"/>
@@ -5349,13 +5619,13 @@
         <v>70</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>78</v>
+        <v>426</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>79</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5363,41 +5633,41 @@
         <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>87</v>
+        <v>422</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>88</v>
+        <v>423</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>89</v>
+        <v>424</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5405,13 +5675,13 @@
         <v>83</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5419,41 +5689,41 @@
         <v>83</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5461,69 +5731,69 @@
         <v>96</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5531,97 +5801,97 @@
         <v>113</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>124</v>
+        <v>419</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>125</v>
+        <v>420</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>126</v>
+        <v>421</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5629,13 +5899,13 @@
         <v>134</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5643,13 +5913,13 @@
         <v>134</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5657,13 +5927,13 @@
         <v>134</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>417</v>
+        <v>142</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>418</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5671,13 +5941,13 @@
         <v>134</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5685,13 +5955,13 @@
         <v>134</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5699,13 +5969,13 @@
         <v>134</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>156</v>
+        <v>416</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>157</v>
+        <v>417</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>158</v>
+        <v>418</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5713,13 +5983,13 @@
         <v>134</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5727,125 +5997,125 @@
         <v>134</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5853,68 +6123,110 @@
         <v>182</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="53" t="s">
+    <row r="65" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="B62" s="53" t="s">
+      <c r="B65" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="C62" s="53" t="s">
+      <c r="C65" s="53" t="s">
         <v>195</v>
       </c>
-      <c r="D62" s="53" t="s">
+      <c r="D65" s="53" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="54" t="s">
+    <row r="66" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="54" t="s">
         <v>182</v>
       </c>
-      <c r="B63" s="54" t="s">
+      <c r="B66" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="C63" s="54" t="s">
+      <c r="C66" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="D63" s="54" t="s">
+      <c r="D66" s="54" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="54" t="s">
+    <row r="67" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="54" t="s">
         <v>182</v>
       </c>
-      <c r="B64" s="54" t="s">
+      <c r="B67" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C64" s="54" t="s">
+      <c r="C67" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="D64" s="54" t="s">
+      <c r="D67" s="54" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="55" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="55" t="s">
         <v>407</v>
       </c>
-      <c r="B65" s="55" t="s">
+      <c r="B68" s="55" t="s">
         <v>406</v>
       </c>
-      <c r="C65" s="55" t="s">
+      <c r="C68" s="55" t="s">
         <v>408</v>
       </c>
-      <c r="D65" s="55" t="s">
+      <c r="D68" s="55" t="s">
         <v>409</v>
       </c>
     </row>
@@ -6001,10 +6313,10 @@
       </c>
     </row>
     <row r="16" spans="9:10" x14ac:dyDescent="0.2">
-      <c r="I16" s="68">
+      <c r="I16" s="67">
         <v>8</v>
       </c>
-      <c r="J16" s="68">
+      <c r="J16" s="67">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
@@ -6019,10 +6331,10 @@
       </c>
     </row>
     <row r="18" spans="9:10" x14ac:dyDescent="0.2">
-      <c r="I18" s="68">
+      <c r="I18" s="67">
         <v>10</v>
       </c>
-      <c r="J18" s="68">
+      <c r="J18" s="67">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
@@ -6109,10 +6421,10 @@
       </c>
     </row>
     <row r="28" spans="9:10" x14ac:dyDescent="0.2">
-      <c r="I28" s="68">
+      <c r="I28" s="67">
         <v>20</v>
       </c>
-      <c r="J28" s="68">
+      <c r="J28" s="67">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D560ABB-06E2-3149-82F6-6773D7C1836B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9A7F66-74F7-D446-8258-7BD1E107FB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-42960" yWindow="600" windowWidth="35620" windowHeight="21980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38460" yWindow="600" windowWidth="38440" windowHeight="28100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -1375,11 +1375,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00%"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1581,7 +1580,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1706,12 +1705,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1721,22 +1714,10 @@
     <xf numFmtId="4" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1809,29 +1790,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2136,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R69"/>
@@ -2148,7 +2117,7 @@
     <col min="5" max="5" width="44.1640625" style="34" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="88.33203125" style="34" hidden="1" customWidth="1"/>
     <col min="7" max="10" width="13" style="34" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" style="35" customWidth="1"/>
+    <col min="11" max="11" width="31.33203125" style="35" customWidth="1"/>
     <col min="12" max="12" width="16.33203125" style="36" customWidth="1"/>
     <col min="13" max="13" width="25.6640625" style="37" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="24.83203125" style="37" bestFit="1" customWidth="1"/>
@@ -2161,16 +2130,16 @@
       <c r="A1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="56" t="s">
+      <c r="C1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="50" t="s">
         <v>204</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -2212,10 +2181,10 @@
       <c r="B2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="62" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="13" t="s">
@@ -2232,16 +2201,16 @@
         <v>0.45</v>
       </c>
       <c r="L2" s="16">
-        <v>12</v>
-      </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M2" s="17">
+        <v>1</v>
+      </c>
+      <c r="N2" s="17"/>
       <c r="O2" s="10"/>
       <c r="P2" s="10">
         <f t="shared" ref="P2:P7" si="0">K2*M2</f>
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
@@ -2250,16 +2219,16 @@
       <c r="A3" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="52" t="s">
         <v>215</v>
       </c>
       <c r="F3" s="18" t="s">
@@ -2273,14 +2242,18 @@
         <v>0.5</v>
       </c>
       <c r="L3" s="16">
-        <v>12</v>
-      </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
+        <v>10</v>
+      </c>
+      <c r="M3" s="17">
+        <v>1</v>
+      </c>
+      <c r="N3" s="17">
+        <v>1.5</v>
+      </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
@@ -2292,10 +2265,10 @@
       <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C4" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="62" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="13" t="s">
@@ -2312,31 +2285,35 @@
         <v>0.3</v>
       </c>
       <c r="L4" s="16">
-        <v>12</v>
-      </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
+        <v>10</v>
+      </c>
+      <c r="M4" s="17">
+        <v>1</v>
+      </c>
+      <c r="N4" s="17">
+        <v>1</v>
+      </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>410</v>
       </c>
       <c r="R4" s="11"/>
     </row>
-    <row r="5" spans="1:18" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" s="4" customFormat="1" ht="153" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="13" t="s">
@@ -2349,13 +2326,15 @@
       <c r="H5" s="14"/>
       <c r="I5" s="12"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="74" t="s">
         <v>221</v>
       </c>
       <c r="L5" s="16">
-        <v>12</v>
-      </c>
-      <c r="M5" s="17"/>
+        <v>10</v>
+      </c>
+      <c r="M5" s="17">
+        <v>1</v>
+      </c>
       <c r="N5" s="17">
         <v>1</v>
       </c>
@@ -2374,10 +2353,10 @@
       <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="73" t="s">
+      <c r="C6" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="62" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="13" t="s">
@@ -2398,32 +2377,39 @@
         <v>0.2</v>
       </c>
       <c r="L6" s="16">
-        <v>12</v>
-      </c>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
+        <v>10</v>
+      </c>
+      <c r="M6" s="17">
+        <v>1</v>
+      </c>
+      <c r="N6" s="17">
+        <v>2.5</v>
+      </c>
       <c r="O6" s="10"/>
       <c r="P6" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="11"/>
+        <f>0.6*M6</f>
+        <v>0.6</v>
+      </c>
+      <c r="Q6" s="10">
+        <f>K6*N6</f>
+        <v>0.5</v>
+      </c>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>226</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="53" t="s">
         <v>227</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -2437,19 +2423,21 @@
         <v>50</v>
       </c>
       <c r="L7" s="16">
-        <v>12</v>
-      </c>
-      <c r="M7" s="17"/>
-      <c r="N7" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M7" s="17">
+        <v>1</v>
+      </c>
+      <c r="N7" s="17"/>
       <c r="O7" s="10"/>
       <c r="P7" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2482,10 +2470,10 @@
       <c r="L8" s="16">
         <v>10</v>
       </c>
-      <c r="M8" s="78">
-        <v>1</v>
-      </c>
-      <c r="N8" s="78">
+      <c r="M8" s="17">
+        <v>1</v>
+      </c>
+      <c r="N8" s="17">
         <v>1</v>
       </c>
       <c r="O8" s="10"/>
@@ -2499,7 +2487,7 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>226</v>
       </c>
@@ -2530,19 +2518,21 @@
         <v>0.95</v>
       </c>
       <c r="L9" s="16">
-        <v>12</v>
-      </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M9" s="17">
+        <v>1</v>
+      </c>
+      <c r="N9" s="71"/>
       <c r="O9" s="10"/>
       <c r="P9" s="10">
         <f t="shared" ref="P9:P15" si="1">K9*M9</f>
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>226</v>
       </c>
@@ -2573,12 +2563,12 @@
         <v>0.95</v>
       </c>
       <c r="L10" s="16">
-        <v>12</v>
-      </c>
-      <c r="M10" s="78">
-        <v>1</v>
-      </c>
-      <c r="N10" s="78">
+        <v>10</v>
+      </c>
+      <c r="M10" s="17">
+        <v>1</v>
+      </c>
+      <c r="N10" s="71">
         <v>1</v>
       </c>
       <c r="O10" s="10"/>
@@ -2589,14 +2579,14 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="56" t="s">
         <v>411</v>
       </c>
       <c r="D11" s="13" t="s">
@@ -2616,12 +2606,14 @@
       <c r="L11" s="16">
         <v>10</v>
       </c>
-      <c r="M11" s="17"/>
+      <c r="M11" s="17">
+        <v>1</v>
+      </c>
       <c r="N11" s="17"/>
       <c r="O11" s="10"/>
       <c r="P11" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q11" s="10">
         <f>K11*N11</f>
@@ -2629,14 +2621,14 @@
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="56" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="13" t="s">
@@ -2658,12 +2650,14 @@
       <c r="L12" s="16">
         <v>10</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="78"/>
+      <c r="M12" s="17">
+        <v>1</v>
+      </c>
+      <c r="N12" s="71"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q12" s="10">
         <f>K12*N12</f>
@@ -2671,14 +2665,14 @@
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="56" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="13" t="s">
@@ -2698,25 +2692,27 @@
         <v>0.8</v>
       </c>
       <c r="L13" s="16">
-        <v>12</v>
-      </c>
-      <c r="M13" s="77"/>
-      <c r="N13" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M13" s="17">
+        <v>1</v>
+      </c>
+      <c r="N13" s="71"/>
       <c r="O13" s="10" t="e">
         <f>K13*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="P13" s="65">
+      <c r="P13" s="59">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="65">
+        <v>0.8</v>
+      </c>
+      <c r="Q13" s="59">
         <f>K13*N13</f>
         <v>0</v>
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>226</v>
       </c>
@@ -2726,10 +2722,10 @@
       <c r="C14" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="60" t="s">
+      <c r="D14" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E14" s="54" t="s">
         <v>246</v>
       </c>
       <c r="F14" s="25" t="s">
@@ -2747,16 +2743,18 @@
         <v>0.3</v>
       </c>
       <c r="L14" s="16">
-        <v>12</v>
-      </c>
-      <c r="M14" s="17"/>
-      <c r="N14" s="78">
+        <v>10</v>
+      </c>
+      <c r="M14" s="17">
+        <v>1</v>
+      </c>
+      <c r="N14" s="71">
         <v>0.5</v>
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q14" s="10">
         <f>K14*N14</f>
@@ -2764,7 +2762,7 @@
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
@@ -2795,16 +2793,18 @@
         <v>0.4</v>
       </c>
       <c r="L15" s="16">
-        <v>12</v>
-      </c>
-      <c r="M15" s="17"/>
-      <c r="N15" s="78">
+        <v>10</v>
+      </c>
+      <c r="M15" s="17">
+        <v>1</v>
+      </c>
+      <c r="N15" s="71">
         <v>0.5</v>
       </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q15" s="10">
         <f>K15*N15</f>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -2839,10 +2839,12 @@
         <v>256</v>
       </c>
       <c r="L16" s="16">
-        <v>12</v>
-      </c>
-      <c r="M16" s="17"/>
-      <c r="N16" s="78">
+        <v>10</v>
+      </c>
+      <c r="M16" s="17">
+        <v>1</v>
+      </c>
+      <c r="N16" s="71">
         <v>0.5</v>
       </c>
       <c r="O16" s="10"/>
@@ -2850,7 +2852,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="64" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2880,23 +2882,25 @@
       <c r="K17" s="15">
         <v>0.5</v>
       </c>
-      <c r="L17" s="79">
-        <v>12</v>
-      </c>
-      <c r="M17" s="80"/>
-      <c r="N17" s="81"/>
+      <c r="L17" s="16">
+        <v>10</v>
+      </c>
+      <c r="M17" s="17">
+        <v>1</v>
+      </c>
+      <c r="N17" s="72"/>
       <c r="O17" s="10"/>
       <c r="P17" s="10">
         <f t="shared" ref="P17:P44" si="2">K17*M17</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q17" s="10">
         <f>K17*N17</f>
         <v>0</v>
       </c>
-      <c r="R17" s="63"/>
-    </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R17" s="57"/>
+    </row>
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2906,10 +2910,10 @@
       <c r="C18" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="60" t="s">
+      <c r="D18" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="53" t="s">
         <v>261</v>
       </c>
       <c r="F18" s="25" t="s">
@@ -2927,19 +2931,21 @@
         <v>0.3</v>
       </c>
       <c r="L18" s="16">
-        <v>12</v>
-      </c>
-      <c r="M18" s="17"/>
-      <c r="N18" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M18" s="17">
+        <v>1</v>
+      </c>
+      <c r="N18" s="71"/>
       <c r="O18" s="10"/>
       <c r="P18" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2970,19 +2976,21 @@
         <v>0.1</v>
       </c>
       <c r="L19" s="16">
-        <v>12</v>
-      </c>
-      <c r="M19" s="17"/>
-      <c r="N19" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M19" s="17">
+        <v>1</v>
+      </c>
+      <c r="N19" s="71"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -3009,19 +3017,21 @@
         <v>0.1</v>
       </c>
       <c r="L20" s="16">
-        <v>12</v>
-      </c>
-      <c r="M20" s="17"/>
-      <c r="N20" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M20" s="17">
+        <v>1</v>
+      </c>
+      <c r="N20" s="71"/>
       <c r="O20" s="10"/>
       <c r="P20" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -3048,19 +3058,21 @@
         <v>0.1</v>
       </c>
       <c r="L21" s="16">
-        <v>12</v>
-      </c>
-      <c r="M21" s="17"/>
-      <c r="N21" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M21" s="17">
+        <v>1</v>
+      </c>
+      <c r="N21" s="71"/>
       <c r="O21" s="10"/>
       <c r="P21" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
@@ -3087,14 +3099,16 @@
         <v>0.1</v>
       </c>
       <c r="L22" s="16">
-        <v>12</v>
-      </c>
-      <c r="M22" s="17"/>
-      <c r="N22" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M22" s="17">
+        <v>1</v>
+      </c>
+      <c r="N22" s="71"/>
       <c r="O22" s="10"/>
       <c r="P22" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
@@ -3109,10 +3123,10 @@
       <c r="C23" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="60" t="s">
+      <c r="D23" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="59" t="s">
+      <c r="E23" s="53" t="s">
         <v>275</v>
       </c>
       <c r="F23" s="25" t="s">
@@ -3132,18 +3146,20 @@
       <c r="L23" s="16">
         <v>10</v>
       </c>
-      <c r="M23" s="17"/>
-      <c r="N23" s="84">
-        <v>0.98999899999999996</v>
-      </c>
-      <c r="O23" s="65"/>
-      <c r="P23" s="65">
+      <c r="M23" s="17">
+        <v>1</v>
+      </c>
+      <c r="N23" s="17">
+        <v>1</v>
+      </c>
+      <c r="O23" s="59"/>
+      <c r="P23" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="66">
-        <f>K23*N23</f>
-        <v>0.989009001</v>
+        <v>0.999</v>
+      </c>
+      <c r="Q23" s="60">
+        <f t="shared" ref="Q23:Q28" si="3">K23*N23</f>
+        <v>0.999</v>
       </c>
       <c r="R23" s="11"/>
     </row>
@@ -3167,7 +3183,7 @@
         <v>12</v>
       </c>
       <c r="G24" s="17"/>
-      <c r="H24" s="78">
+      <c r="H24" s="71">
         <v>1</v>
       </c>
       <c r="I24" s="10"/>
@@ -3180,17 +3196,19 @@
       <c r="L24" s="16">
         <v>10</v>
       </c>
-      <c r="M24" s="17"/>
-      <c r="N24" s="84">
-        <v>1</v>
-      </c>
-      <c r="O24" s="65"/>
-      <c r="P24" s="65">
+      <c r="M24" s="17">
+        <v>1</v>
+      </c>
+      <c r="N24" s="17">
+        <v>1</v>
+      </c>
+      <c r="O24" s="59"/>
+      <c r="P24" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="66">
-        <f>K24*N24</f>
+        <v>0.999</v>
+      </c>
+      <c r="Q24" s="60">
+        <f t="shared" si="3"/>
         <v>0.999</v>
       </c>
       <c r="R24" s="11"/>
@@ -3226,19 +3244,21 @@
         <v>0.95</v>
       </c>
       <c r="L25" s="16">
-        <v>12</v>
-      </c>
-      <c r="M25" s="17"/>
-      <c r="N25" s="78">
+        <v>10</v>
+      </c>
+      <c r="M25" s="17">
+        <v>1</v>
+      </c>
+      <c r="N25" s="17">
         <v>1</v>
       </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="66">
-        <f>K25*N25</f>
+        <v>0.95</v>
+      </c>
+      <c r="Q25" s="60">
+        <f t="shared" si="3"/>
         <v>0.95</v>
       </c>
       <c r="R25" s="11"/>
@@ -3253,10 +3273,10 @@
       <c r="C26" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="60" t="s">
+      <c r="D26" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="E26" s="59" t="s">
+      <c r="E26" s="53" t="s">
         <v>283</v>
       </c>
       <c r="F26" s="25" t="s">
@@ -3276,18 +3296,20 @@
       <c r="L26" s="16">
         <v>10</v>
       </c>
-      <c r="M26" s="17"/>
-      <c r="N26" s="78">
-        <v>4</v>
+      <c r="M26" s="17">
+        <v>1</v>
+      </c>
+      <c r="N26" s="17">
+        <v>2</v>
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="66">
-        <f>K26*N26</f>
-        <v>0.8</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q26" s="60">
+        <f t="shared" si="3"/>
+        <v>0.4</v>
       </c>
       <c r="R26" s="11"/>
     </row>
@@ -3311,7 +3333,7 @@
         <v>12</v>
       </c>
       <c r="G27" s="17"/>
-      <c r="H27" s="78">
+      <c r="H27" s="71">
         <v>1</v>
       </c>
       <c r="I27" s="10"/>
@@ -3324,17 +3346,19 @@
       <c r="L27" s="16">
         <v>10</v>
       </c>
-      <c r="M27" s="17"/>
-      <c r="N27" s="78">
+      <c r="M27" s="17">
+        <v>1</v>
+      </c>
+      <c r="N27" s="17">
         <v>1</v>
       </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="66">
-        <f>K27*N27</f>
+        <v>0.5</v>
+      </c>
+      <c r="Q27" s="60">
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
       <c r="R27" s="11"/>
@@ -3370,18 +3394,23 @@
         <v>0.1</v>
       </c>
       <c r="L28" s="16">
-        <v>12</v>
-      </c>
-      <c r="M28" s="17"/>
-      <c r="N28" s="78">
+        <v>10</v>
+      </c>
+      <c r="M28" s="17">
+        <v>1</v>
+      </c>
+      <c r="N28" s="17">
         <v>1</v>
       </c>
       <c r="O28" s="10"/>
       <c r="P28" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="11"/>
+        <v>0.1</v>
+      </c>
+      <c r="Q28" s="11">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
       <c r="R28" s="11"/>
     </row>
     <row r="29" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -3411,16 +3440,18 @@
         <v>0.9</v>
       </c>
       <c r="L29" s="16">
-        <v>12</v>
-      </c>
-      <c r="M29" s="17"/>
-      <c r="N29" s="78">
+        <v>10</v>
+      </c>
+      <c r="M29" s="17">
+        <v>1</v>
+      </c>
+      <c r="N29" s="17">
         <v>1</v>
       </c>
       <c r="O29" s="10"/>
       <c r="P29" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q29" s="11"/>
       <c r="R29" s="28"/>
@@ -3452,10 +3483,12 @@
         <v>295</v>
       </c>
       <c r="L30" s="16">
-        <v>12</v>
-      </c>
-      <c r="M30" s="17"/>
-      <c r="N30" s="78">
+        <v>10</v>
+      </c>
+      <c r="M30" s="17">
+        <v>1</v>
+      </c>
+      <c r="N30" s="17">
         <v>1</v>
       </c>
       <c r="O30" s="10"/>
@@ -3493,10 +3526,14 @@
         <v>297</v>
       </c>
       <c r="L31" s="16">
-        <v>12</v>
-      </c>
-      <c r="M31" s="17"/>
-      <c r="N31" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M31" s="17">
+        <v>1</v>
+      </c>
+      <c r="N31" s="17">
+        <v>1</v>
+      </c>
       <c r="O31" s="10"/>
       <c r="P31" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3532,10 +3569,14 @@
         <v>299</v>
       </c>
       <c r="L32" s="16">
-        <v>12</v>
-      </c>
-      <c r="M32" s="17"/>
-      <c r="N32" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M32" s="17">
+        <v>1</v>
+      </c>
+      <c r="N32" s="17">
+        <v>1</v>
+      </c>
       <c r="O32" s="10"/>
       <c r="P32" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3544,17 +3585,17 @@
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
     </row>
-    <row r="33" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="73" t="s">
+      <c r="C33" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="68" t="s">
+      <c r="D33" s="62" t="s">
         <v>98</v>
       </c>
       <c r="E33" s="13" t="s">
@@ -3571,10 +3612,14 @@
         <v>302</v>
       </c>
       <c r="L33" s="16">
-        <v>12</v>
-      </c>
-      <c r="M33" s="17"/>
-      <c r="N33" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M33" s="17">
+        <v>1</v>
+      </c>
+      <c r="N33" s="17">
+        <v>1</v>
+      </c>
       <c r="O33" s="10"/>
       <c r="P33" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3583,17 +3628,17 @@
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
     </row>
-    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="73" t="s">
+      <c r="C34" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="68" t="s">
+      <c r="D34" s="62" t="s">
         <v>101</v>
       </c>
       <c r="E34" s="13" t="s">
@@ -3610,29 +3655,33 @@
         <v>0.5</v>
       </c>
       <c r="L34" s="16">
-        <v>12</v>
-      </c>
-      <c r="M34" s="17"/>
-      <c r="N34" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M34" s="17">
+        <v>1</v>
+      </c>
+      <c r="N34" s="17">
+        <v>1</v>
+      </c>
       <c r="O34" s="10"/>
       <c r="P34" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
     </row>
-    <row r="35" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="73" t="s">
+      <c r="C35" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="68" t="s">
+      <c r="D35" s="62" t="s">
         <v>104</v>
       </c>
       <c r="E35" s="13" t="s">
@@ -3653,19 +3702,26 @@
         <v>0.3</v>
       </c>
       <c r="L35" s="16">
-        <v>12</v>
-      </c>
-      <c r="M35" s="17"/>
-      <c r="N35" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M35" s="17">
+        <v>1</v>
+      </c>
+      <c r="N35" s="17">
+        <v>1</v>
+      </c>
       <c r="O35" s="10"/>
-      <c r="P35" s="10">
+      <c r="P35" s="60">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="17"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q35" s="60">
+        <f>K35*N35</f>
+        <v>0.3</v>
+      </c>
       <c r="R35" s="29"/>
     </row>
-    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>309</v>
       </c>
@@ -3692,19 +3748,23 @@
         <v>0.5</v>
       </c>
       <c r="L36" s="16">
-        <v>12</v>
-      </c>
-      <c r="M36" s="17"/>
-      <c r="N36" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M36" s="17">
+        <v>1</v>
+      </c>
+      <c r="N36" s="71">
+        <v>1</v>
+      </c>
       <c r="O36" s="10"/>
       <c r="P36" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q36" s="11"/>
       <c r="R36" s="11"/>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>309</v>
       </c>
@@ -3731,26 +3791,28 @@
         <v>0.9</v>
       </c>
       <c r="L37" s="16">
-        <v>12</v>
-      </c>
-      <c r="M37" s="17"/>
-      <c r="N37" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M37" s="17">
+        <v>1</v>
+      </c>
+      <c r="N37" s="71"/>
       <c r="O37" s="10"/>
       <c r="P37" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="83" t="s">
+      <c r="C38" s="13" t="s">
         <v>419</v>
       </c>
       <c r="D38" s="13" t="s">
@@ -3763,37 +3825,39 @@
         <v>10</v>
       </c>
       <c r="G38" s="17"/>
-      <c r="H38" s="78">
+      <c r="H38" s="71">
         <v>0.25</v>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
-      <c r="K38" s="82">
+      <c r="K38" s="73">
         <v>0.2</v>
       </c>
       <c r="L38" s="16">
         <v>10</v>
       </c>
-      <c r="M38" s="17"/>
-      <c r="N38" s="78">
+      <c r="M38" s="17">
+        <v>1</v>
+      </c>
+      <c r="N38" s="71">
         <v>1</v>
       </c>
       <c r="O38" s="10"/>
       <c r="P38" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
     </row>
-    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="83" t="s">
+      <c r="C39" s="13" t="s">
         <v>114</v>
       </c>
       <c r="D39" s="13" t="s">
@@ -3815,14 +3879,16 @@
       <c r="L39" s="16">
         <v>10</v>
       </c>
-      <c r="M39" s="17"/>
-      <c r="N39" s="78">
+      <c r="M39" s="17">
+        <v>1</v>
+      </c>
+      <c r="N39" s="71">
         <v>0.1</v>
       </c>
       <c r="O39" s="10"/>
       <c r="P39" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q39" s="10">
         <f>K39*N39</f>
@@ -3830,14 +3896,14 @@
       </c>
       <c r="R39" s="11"/>
     </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C40" s="83" t="s">
+      <c r="C40" s="13" t="s">
         <v>117</v>
       </c>
       <c r="D40" s="13" t="s">
@@ -3859,26 +3925,28 @@
       <c r="L40" s="16">
         <v>10</v>
       </c>
-      <c r="M40" s="17"/>
-      <c r="N40" s="78">
+      <c r="M40" s="17">
+        <v>1</v>
+      </c>
+      <c r="N40" s="71">
         <v>1</v>
       </c>
       <c r="O40" s="10"/>
       <c r="P40" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
     </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C41" s="83" t="s">
+      <c r="C41" s="13" t="s">
         <v>120</v>
       </c>
       <c r="D41" s="13" t="s">
@@ -3900,14 +3968,16 @@
       <c r="L41" s="16">
         <v>10</v>
       </c>
-      <c r="M41" s="17"/>
-      <c r="N41" s="78">
+      <c r="M41" s="17">
+        <v>1</v>
+      </c>
+      <c r="N41" s="71">
         <v>1</v>
       </c>
       <c r="O41" s="10"/>
       <c r="P41" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
@@ -3939,14 +4009,18 @@
         <v>0.2</v>
       </c>
       <c r="L42" s="16">
-        <v>12</v>
-      </c>
-      <c r="M42" s="17"/>
-      <c r="N42" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M42" s="17">
+        <v>1</v>
+      </c>
+      <c r="N42" s="17">
+        <v>1</v>
+      </c>
       <c r="O42" s="10"/>
       <c r="P42" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
@@ -3978,21 +4052,23 @@
         <v>0.2</v>
       </c>
       <c r="L43" s="16">
-        <v>12</v>
-      </c>
-      <c r="M43" s="17"/>
-      <c r="N43" s="78">
+        <v>10</v>
+      </c>
+      <c r="M43" s="17">
+        <v>1</v>
+      </c>
+      <c r="N43" s="17">
         <v>1</v>
       </c>
       <c r="O43" s="10"/>
       <c r="P43" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
     </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>226</v>
       </c>
@@ -4023,14 +4099,16 @@
         <v>0.25</v>
       </c>
       <c r="L44" s="16">
-        <v>12</v>
-      </c>
-      <c r="M44" s="17"/>
-      <c r="N44" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M44" s="17">
+        <v>1</v>
+      </c>
+      <c r="N44" s="71"/>
       <c r="O44" s="10"/>
       <c r="P44" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Q44" s="10">
         <f>K44*N44</f>
@@ -4038,7 +4116,7 @@
       </c>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -4069,7 +4147,7 @@
         <v>0.25</v>
       </c>
       <c r="L45" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M45" s="17">
         <v>1</v>
@@ -4088,7 +4166,7 @@
       </c>
       <c r="R45" s="11"/>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>226</v>
       </c>
@@ -4119,19 +4197,21 @@
         <v>0.25</v>
       </c>
       <c r="L46" s="16">
-        <v>12</v>
-      </c>
-      <c r="M46" s="17"/>
-      <c r="N46" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M46" s="17">
+        <v>1</v>
+      </c>
+      <c r="N46" s="71"/>
       <c r="O46" s="10"/>
       <c r="P46" s="10">
-        <f t="shared" ref="P46:P54" si="3">K46*N46</f>
+        <f t="shared" ref="P46:P54" si="4">K46*N46</f>
         <v>0</v>
       </c>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
     </row>
-    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>226</v>
       </c>
@@ -4158,19 +4238,21 @@
         <v>0.25</v>
       </c>
       <c r="L47" s="16">
-        <v>12</v>
-      </c>
-      <c r="M47" s="17"/>
-      <c r="N47" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M47" s="17">
+        <v>1</v>
+      </c>
+      <c r="N47" s="71"/>
       <c r="O47" s="10"/>
       <c r="P47" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
     </row>
-    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>226</v>
       </c>
@@ -4200,9 +4282,9 @@
         <v>10</v>
       </c>
       <c r="M48" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="N48" s="78">
+        <v>1</v>
+      </c>
+      <c r="N48" s="71">
         <v>1.2</v>
       </c>
       <c r="O48" s="10"/>
@@ -4213,7 +4295,7 @@
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
     </row>
-    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>226</v>
       </c>
@@ -4244,19 +4326,21 @@
         <v>0.7</v>
       </c>
       <c r="L49" s="16">
-        <v>12</v>
-      </c>
-      <c r="M49" s="17"/>
-      <c r="N49" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M49" s="17">
+        <v>1</v>
+      </c>
+      <c r="N49" s="71"/>
       <c r="O49" s="10"/>
       <c r="P49" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
     </row>
-    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>226</v>
       </c>
@@ -4276,30 +4360,32 @@
         <v>12</v>
       </c>
       <c r="G50" s="17"/>
-      <c r="H50" s="78">
+      <c r="H50" s="71">
         <v>0.8</v>
       </c>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
-      <c r="K50" s="82">
+      <c r="K50" s="73">
         <v>0.06</v>
       </c>
       <c r="L50" s="16">
         <v>10</v>
       </c>
-      <c r="M50" s="17"/>
-      <c r="N50" s="78">
+      <c r="M50" s="17">
+        <v>1</v>
+      </c>
+      <c r="N50" s="71">
         <v>1</v>
       </c>
       <c r="O50" s="10"/>
       <c r="P50" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.06</v>
       </c>
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
     </row>
-    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>226</v>
       </c>
@@ -4330,21 +4416,23 @@
         <v>0.7</v>
       </c>
       <c r="L51" s="16">
-        <v>12</v>
-      </c>
-      <c r="M51" s="17"/>
-      <c r="N51" s="78">
+        <v>10</v>
+      </c>
+      <c r="M51" s="17">
+        <v>1</v>
+      </c>
+      <c r="N51" s="71">
         <v>0.8</v>
       </c>
       <c r="O51" s="10"/>
       <c r="P51" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.55999999999999994</v>
       </c>
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>226</v>
       </c>
@@ -4371,19 +4459,21 @@
         <v>0.25</v>
       </c>
       <c r="L52" s="16">
-        <v>12</v>
-      </c>
-      <c r="M52" s="17"/>
-      <c r="N52" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M52" s="17">
+        <v>1</v>
+      </c>
+      <c r="N52" s="71"/>
       <c r="O52" s="10"/>
       <c r="P52" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
     </row>
-    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>226</v>
       </c>
@@ -4414,19 +4504,21 @@
         <v>0.2</v>
       </c>
       <c r="L53" s="16">
-        <v>12</v>
-      </c>
-      <c r="M53" s="17"/>
-      <c r="N53" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M53" s="17">
+        <v>1</v>
+      </c>
+      <c r="N53" s="71"/>
       <c r="O53" s="10"/>
       <c r="P53" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q53" s="11"/>
       <c r="R53" s="11"/>
     </row>
-    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>226</v>
       </c>
@@ -4457,19 +4549,21 @@
         <v>0.3</v>
       </c>
       <c r="L54" s="16">
-        <v>12</v>
-      </c>
-      <c r="M54" s="17"/>
-      <c r="N54" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M54" s="17">
+        <v>1</v>
+      </c>
+      <c r="N54" s="71"/>
       <c r="O54" s="10"/>
       <c r="P54" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
     </row>
-    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>226</v>
       </c>
@@ -4500,16 +4594,18 @@
         <v>362</v>
       </c>
       <c r="L55" s="16">
-        <v>12</v>
-      </c>
-      <c r="M55" s="17"/>
-      <c r="N55" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M55" s="17">
+        <v>1</v>
+      </c>
+      <c r="N55" s="71"/>
       <c r="O55" s="10"/>
       <c r="P55" s="10"/>
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
     </row>
-    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>51</v>
       </c>
@@ -4536,19 +4632,23 @@
         <v>0.85</v>
       </c>
       <c r="L56" s="16">
-        <v>12</v>
-      </c>
-      <c r="M56" s="17"/>
-      <c r="N56" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M56" s="17">
+        <v>1</v>
+      </c>
+      <c r="N56" s="17">
+        <v>1</v>
+      </c>
       <c r="O56" s="10"/>
       <c r="P56" s="10">
         <f>K56*M56</f>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="Q56" s="11"/>
       <c r="R56" s="11"/>
     </row>
-    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>51</v>
       </c>
@@ -4579,19 +4679,23 @@
         <v>0.9</v>
       </c>
       <c r="L57" s="16">
-        <v>12</v>
-      </c>
-      <c r="M57" s="17"/>
-      <c r="N57" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M57" s="17">
+        <v>1</v>
+      </c>
+      <c r="N57" s="17">
+        <v>1</v>
+      </c>
       <c r="O57" s="10"/>
       <c r="P57" s="10">
         <f>K57*M57</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
     </row>
-    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>369</v>
       </c>
@@ -4624,14 +4728,18 @@
       <c r="L58" s="16">
         <v>10</v>
       </c>
-      <c r="M58" s="17"/>
-      <c r="N58" s="78"/>
+      <c r="M58" s="17">
+        <v>1</v>
+      </c>
+      <c r="N58" s="17">
+        <v>1</v>
+      </c>
       <c r="O58" s="10"/>
       <c r="P58" s="10"/>
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
     </row>
-    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>369</v>
       </c>
@@ -4664,14 +4772,18 @@
       <c r="L59" s="16">
         <v>10</v>
       </c>
-      <c r="M59" s="17"/>
-      <c r="N59" s="78"/>
+      <c r="M59" s="17">
+        <v>1</v>
+      </c>
+      <c r="N59" s="17">
+        <v>1</v>
+      </c>
       <c r="O59" s="10"/>
       <c r="P59" s="10"/>
       <c r="Q59" s="11"/>
       <c r="R59" s="11"/>
     </row>
-    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>369</v>
       </c>
@@ -4702,10 +4814,14 @@
         <v>382</v>
       </c>
       <c r="L60" s="16">
-        <v>12</v>
-      </c>
-      <c r="M60" s="17"/>
-      <c r="N60" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M60" s="17">
+        <v>1</v>
+      </c>
+      <c r="N60" s="17">
+        <v>1</v>
+      </c>
       <c r="O60" s="10"/>
       <c r="P60" s="10"/>
       <c r="Q60" s="11"/>
@@ -4718,10 +4834,10 @@
       <c r="B61" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="73" t="s">
+      <c r="C61" s="67" t="s">
         <v>183</v>
       </c>
-      <c r="D61" s="68" t="s">
+      <c r="D61" s="62" t="s">
         <v>184</v>
       </c>
       <c r="E61" s="13" t="s">
@@ -4742,14 +4858,18 @@
         <v>0.3</v>
       </c>
       <c r="L61" s="16">
-        <v>12</v>
-      </c>
-      <c r="M61" s="17"/>
-      <c r="N61" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M61" s="17">
+        <v>1</v>
+      </c>
+      <c r="N61" s="17">
+        <v>1</v>
+      </c>
       <c r="O61" s="10"/>
       <c r="P61" s="10">
         <f>K61*M61</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q61" s="11"/>
       <c r="R61" s="11"/>
@@ -4761,10 +4881,10 @@
       <c r="B62" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="73" t="s">
+      <c r="C62" s="67" t="s">
         <v>186</v>
       </c>
-      <c r="D62" s="68" t="s">
+      <c r="D62" s="62" t="s">
         <v>187</v>
       </c>
       <c r="E62" s="13" t="s">
@@ -4781,10 +4901,12 @@
         <v>389</v>
       </c>
       <c r="L62" s="16">
-        <v>12</v>
-      </c>
-      <c r="M62" s="17"/>
-      <c r="N62" s="78">
+        <v>10</v>
+      </c>
+      <c r="M62" s="17">
+        <v>1</v>
+      </c>
+      <c r="N62" s="17">
         <v>1</v>
       </c>
       <c r="O62" s="10"/>
@@ -4799,13 +4921,13 @@
       <c r="B63" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C63" s="73" t="s">
+      <c r="C63" s="67" t="s">
         <v>189</v>
       </c>
-      <c r="D63" s="70" t="s">
+      <c r="D63" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="E63" s="59" t="s">
+      <c r="E63" s="53" t="s">
         <v>390</v>
       </c>
       <c r="F63" s="22" t="s">
@@ -4823,14 +4945,18 @@
         <v>0.85</v>
       </c>
       <c r="L63" s="16">
-        <v>12</v>
-      </c>
-      <c r="M63" s="17"/>
-      <c r="N63" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M63" s="17">
+        <v>1</v>
+      </c>
+      <c r="N63" s="17">
+        <v>1</v>
+      </c>
       <c r="O63" s="10"/>
       <c r="P63" s="10">
-        <f t="shared" ref="P63:P68" si="4">K63*M63</f>
-        <v>0</v>
+        <f t="shared" ref="P63:P68" si="5">K63*M63</f>
+        <v>0.85</v>
       </c>
       <c r="Q63" s="11"/>
       <c r="R63" s="11"/>
@@ -4842,10 +4968,10 @@
       <c r="B64" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C64" s="73" t="s">
+      <c r="C64" s="67" t="s">
         <v>191</v>
       </c>
-      <c r="D64" s="68" t="s">
+      <c r="D64" s="62" t="s">
         <v>192</v>
       </c>
       <c r="E64" s="13" t="s">
@@ -4862,16 +4988,18 @@
         <v>0.85</v>
       </c>
       <c r="L64" s="16">
-        <v>12</v>
-      </c>
-      <c r="M64" s="17"/>
-      <c r="N64" s="78">
+        <v>10</v>
+      </c>
+      <c r="M64" s="17">
+        <v>1</v>
+      </c>
+      <c r="N64" s="17">
         <v>1</v>
       </c>
       <c r="O64" s="10"/>
       <c r="P64" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>0.85</v>
       </c>
       <c r="Q64" s="11"/>
       <c r="R64" s="11"/>
@@ -4883,10 +5011,10 @@
       <c r="B65" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C65" s="73" t="s">
+      <c r="C65" s="67" t="s">
         <v>194</v>
       </c>
-      <c r="D65" s="68" t="s">
+      <c r="D65" s="62" t="s">
         <v>195</v>
       </c>
       <c r="E65" s="13" t="s">
@@ -4903,14 +5031,18 @@
         <v>0.85</v>
       </c>
       <c r="L65" s="16">
-        <v>12</v>
-      </c>
-      <c r="M65" s="17"/>
-      <c r="N65" s="78"/>
+        <v>10</v>
+      </c>
+      <c r="M65" s="17">
+        <v>1</v>
+      </c>
+      <c r="N65" s="17">
+        <v>1</v>
+      </c>
       <c r="O65" s="10"/>
       <c r="P65" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>0.85</v>
       </c>
       <c r="Q65" s="11"/>
       <c r="R65" s="11"/>
@@ -4919,16 +5051,16 @@
       <c r="A66" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="B66" s="61" t="s">
+      <c r="B66" s="55" t="s">
         <v>182</v>
       </c>
-      <c r="C66" s="75" t="s">
+      <c r="C66" s="69" t="s">
         <v>197</v>
       </c>
-      <c r="D66" s="71" t="s">
+      <c r="D66" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="E66" s="61" t="s">
+      <c r="E66" s="55" t="s">
         <v>398</v>
       </c>
       <c r="F66" s="40" t="s">
@@ -4945,98 +5077,108 @@
       <c r="K66" s="41">
         <v>1</v>
       </c>
-      <c r="L66" s="42">
-        <v>12</v>
-      </c>
-      <c r="M66" s="43"/>
-      <c r="N66" s="78"/>
+      <c r="L66" s="16">
+        <v>10</v>
+      </c>
+      <c r="M66" s="17">
+        <v>1</v>
+      </c>
+      <c r="N66" s="17">
+        <v>1</v>
+      </c>
       <c r="O66" s="10"/>
       <c r="P66" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="Q66" s="11"/>
       <c r="R66" s="11"/>
     </row>
     <row r="67" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="44" t="s">
+      <c r="A67" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="B67" s="45" t="s">
+      <c r="B67" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="C67" s="76" t="s">
+      <c r="C67" s="70" t="s">
         <v>200</v>
       </c>
-      <c r="D67" s="72" t="s">
+      <c r="D67" s="66" t="s">
         <v>201</v>
       </c>
-      <c r="E67" s="45" t="s">
+      <c r="E67" s="43" t="s">
         <v>402</v>
       </c>
-      <c r="F67" s="44" t="s">
+      <c r="F67" s="42" t="s">
         <v>403</v>
       </c>
-      <c r="G67" s="44"/>
-      <c r="H67" s="44"/>
-      <c r="I67" s="44" t="s">
+      <c r="G67" s="42"/>
+      <c r="H67" s="42"/>
+      <c r="I67" s="42" t="s">
         <v>404</v>
       </c>
-      <c r="J67" s="44" t="s">
+      <c r="J67" s="42" t="s">
         <v>405</v>
       </c>
-      <c r="K67" s="46">
+      <c r="K67" s="44">
         <v>0.95</v>
       </c>
-      <c r="L67" s="47">
-        <v>12</v>
-      </c>
-      <c r="M67" s="48"/>
-      <c r="N67" s="78"/>
+      <c r="L67" s="16">
+        <v>10</v>
+      </c>
+      <c r="M67" s="17">
+        <v>1</v>
+      </c>
+      <c r="N67" s="17">
+        <v>1</v>
+      </c>
       <c r="O67" s="10"/>
       <c r="P67" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>0.95</v>
       </c>
       <c r="Q67" s="11"/>
       <c r="R67" s="11"/>
     </row>
-    <row r="68" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="45" t="s">
+    <row r="68" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="43" t="s">
         <v>226</v>
       </c>
-      <c r="B68" s="45" t="s">
+      <c r="B68" s="43" t="s">
         <v>407</v>
       </c>
-      <c r="C68" s="45" t="s">
+      <c r="C68" s="43" t="s">
         <v>406</v>
       </c>
-      <c r="D68" s="45" t="s">
+      <c r="D68" s="43" t="s">
         <v>408</v>
       </c>
-      <c r="E68" s="45"/>
-      <c r="F68" s="45"/>
-      <c r="G68" s="45"/>
-      <c r="H68" s="45"/>
-      <c r="I68" s="45"/>
-      <c r="J68" s="45"/>
-      <c r="K68" s="51">
+      <c r="E68" s="43"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43"/>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="46">
         <v>1.5</v>
       </c>
-      <c r="L68" s="52">
-        <v>12</v>
-      </c>
-      <c r="M68" s="49"/>
+      <c r="L68" s="16">
+        <v>10</v>
+      </c>
+      <c r="M68" s="17">
+        <v>1</v>
+      </c>
       <c r="N68" s="17"/>
-      <c r="O68" s="50"/>
-      <c r="P68" s="50">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="O68" s="45"/>
+      <c r="P68" s="45">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
       </c>
       <c r="Q68" s="11"/>
       <c r="R68" s="28"/>
     </row>
-    <row r="69" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="31"/>
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
@@ -5057,19 +5199,81 @@
       <c r="R69" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R69" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="AGRC"/>
-        <filter val="LNDU"/>
-        <filter val="LSMM"/>
-        <filter val="SOIL"/>
-        <filter val="WASO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="G24">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G50">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5081,7 +5285,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H50">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5093,7 +5297,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5104,8 +5308,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M8">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="M68:N1048576 M2:M68">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5116,8 +5320,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M10">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="N1">
+    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5128,7 +5332,43 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M68:N1048576 M2:M7 M11:M67 M9">
+  <conditionalFormatting sqref="N2">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N5:N6">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -5140,8 +5380,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="15">
+  <conditionalFormatting sqref="N7:N8">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5152,7 +5392,55 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10 N12:N44 N46:N67">
+  <conditionalFormatting sqref="N9:N10 N12:N22 N46:N55 N36:N41 N44">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N11">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N23:N34">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N35">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N42">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -5164,7 +5452,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N11">
+  <conditionalFormatting sqref="N43">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -5177,6 +5465,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N45">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N59">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N60">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5188,7 +5512,31 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G38">
+  <conditionalFormatting sqref="N61">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N62">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N63">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -5200,7 +5548,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38">
+  <conditionalFormatting sqref="N64">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -5212,7 +5560,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
+  <conditionalFormatting sqref="N65">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5224,7 +5572,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
+  <conditionalFormatting sqref="N66">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -5236,7 +5584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24">
+  <conditionalFormatting sqref="N67">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5248,7 +5596,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
+  <conditionalFormatting sqref="N56:N57">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6175,58 +6523,58 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="53" t="s">
+      <c r="A65" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="B65" s="53" t="s">
+      <c r="B65" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="C65" s="53" t="s">
+      <c r="C65" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="D65" s="53" t="s">
+      <c r="D65" s="47" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="54" t="s">
+      <c r="A66" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B66" s="54" t="s">
+      <c r="B66" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="C66" s="54" t="s">
+      <c r="C66" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="D66" s="54" t="s">
+      <c r="D66" s="48" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="54" t="s">
+      <c r="A67" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B67" s="54" t="s">
+      <c r="B67" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="C67" s="54" t="s">
+      <c r="C67" s="48" t="s">
         <v>201</v>
       </c>
-      <c r="D67" s="54" t="s">
+      <c r="D67" s="48" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="55" t="s">
+      <c r="A68" s="49" t="s">
         <v>407</v>
       </c>
-      <c r="B68" s="55" t="s">
+      <c r="B68" s="49" t="s">
         <v>406</v>
       </c>
-      <c r="C68" s="55" t="s">
+      <c r="C68" s="49" t="s">
         <v>408</v>
       </c>
-      <c r="D68" s="55" t="s">
+      <c r="D68" s="49" t="s">
         <v>409</v>
       </c>
     </row>
@@ -6313,10 +6661,10 @@
       </c>
     </row>
     <row r="16" spans="9:10" x14ac:dyDescent="0.2">
-      <c r="I16" s="67">
+      <c r="I16" s="61">
         <v>8</v>
       </c>
-      <c r="J16" s="67">
+      <c r="J16" s="61">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
@@ -6331,10 +6679,10 @@
       </c>
     </row>
     <row r="18" spans="9:10" x14ac:dyDescent="0.2">
-      <c r="I18" s="67">
+      <c r="I18" s="61">
         <v>10</v>
       </c>
-      <c r="J18" s="67">
+      <c r="J18" s="61">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
@@ -6421,10 +6769,10 @@
       </c>
     </row>
     <row r="28" spans="9:10" x14ac:dyDescent="0.2">
-      <c r="I28" s="67">
+      <c r="I28" s="61">
         <v>20</v>
       </c>
-      <c r="J28" s="67">
+      <c r="J28" s="61">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9A7F66-74F7-D446-8258-7BD1E107FB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239FDE19-B6FD-E243-AAC2-6513AA846C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38460" yWindow="600" windowWidth="38440" windowHeight="28100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-43800" yWindow="600" windowWidth="36440" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2203,14 +2203,12 @@
       <c r="L2" s="16">
         <v>10</v>
       </c>
-      <c r="M2" s="17">
-        <v>1</v>
-      </c>
+      <c r="M2" s="17"/>
       <c r="N2" s="17"/>
       <c r="O2" s="10"/>
       <c r="P2" s="10">
         <f t="shared" ref="P2:P7" si="0">K2*M2</f>
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
@@ -2245,15 +2243,15 @@
         <v>10</v>
       </c>
       <c r="M3" s="17">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="N3" s="17">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
@@ -2288,15 +2286,15 @@
         <v>10</v>
       </c>
       <c r="M4" s="17">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N4" s="17">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>410</v>
@@ -2380,19 +2378,19 @@
         <v>10</v>
       </c>
       <c r="M6" s="17">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="N6" s="17">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O6" s="10"/>
       <c r="P6" s="10">
         <f>0.6*M6</f>
-        <v>0.6</v>
+        <v>2.6999999999999997</v>
       </c>
       <c r="Q6" s="10">
         <f>K6*N6</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R6" s="11"/>
     </row>
@@ -2426,18 +2424,20 @@
         <v>10</v>
       </c>
       <c r="M7" s="17">
-        <v>1</v>
-      </c>
-      <c r="N7" s="17"/>
+        <v>0.5</v>
+      </c>
+      <c r="N7" s="17">
+        <v>0.4</v>
+      </c>
       <c r="O7" s="10"/>
       <c r="P7" s="10">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2471,19 +2471,19 @@
         <v>10</v>
       </c>
       <c r="M8" s="17">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N8" s="17">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O8" s="10"/>
       <c r="P8" s="10">
         <f>0.6*M8</f>
-        <v>0.6</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="Q8" s="10">
         <f>0.6*N8</f>
-        <v>0.6</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="R8" s="11"/>
     </row>
@@ -2520,14 +2520,16 @@
       <c r="L9" s="16">
         <v>10</v>
       </c>
-      <c r="M9" s="17">
-        <v>1</v>
-      </c>
-      <c r="N9" s="71"/>
+      <c r="M9" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="N9" s="71">
+        <v>0.5</v>
+      </c>
       <c r="O9" s="10"/>
       <c r="P9" s="10">
         <f t="shared" ref="P9:P15" si="1">K9*M9</f>
-        <v>0.95</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -2565,7 +2567,7 @@
       <c r="L10" s="16">
         <v>10</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="71">
         <v>1</v>
       </c>
       <c r="N10" s="71">
@@ -2609,7 +2611,9 @@
       <c r="M11" s="17">
         <v>1</v>
       </c>
-      <c r="N11" s="17"/>
+      <c r="N11" s="17">
+        <v>1</v>
+      </c>
       <c r="O11" s="10"/>
       <c r="P11" s="10">
         <f t="shared" si="1"/>
@@ -2617,7 +2621,7 @@
       </c>
       <c r="Q11" s="10">
         <f>K11*N11</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" s="11"/>
     </row>
@@ -2650,10 +2654,12 @@
       <c r="L12" s="16">
         <v>10</v>
       </c>
-      <c r="M12" s="17">
-        <v>1</v>
-      </c>
-      <c r="N12" s="71"/>
+      <c r="M12" s="71">
+        <v>1</v>
+      </c>
+      <c r="N12" s="71">
+        <v>1</v>
+      </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10">
         <f t="shared" si="1"/>
@@ -2661,7 +2667,7 @@
       </c>
       <c r="Q12" s="10">
         <f>K12*N12</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="R12" s="11"/>
     </row>
@@ -2694,9 +2700,7 @@
       <c r="L13" s="16">
         <v>10</v>
       </c>
-      <c r="M13" s="17">
-        <v>1</v>
-      </c>
+      <c r="M13" s="71"/>
       <c r="N13" s="71"/>
       <c r="O13" s="10" t="e">
         <f>K13*#REF!</f>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="P13" s="59">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="59">
         <f>K13*N13</f>
@@ -2745,8 +2749,8 @@
       <c r="L14" s="16">
         <v>10</v>
       </c>
-      <c r="M14" s="17">
-        <v>1</v>
+      <c r="M14" s="71">
+        <v>0.5</v>
       </c>
       <c r="N14" s="71">
         <v>0.5</v>
@@ -2754,7 +2758,7 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="Q14" s="10">
         <f>K14*N14</f>
@@ -2795,8 +2799,8 @@
       <c r="L15" s="16">
         <v>10</v>
       </c>
-      <c r="M15" s="17">
-        <v>1</v>
+      <c r="M15" s="71">
+        <v>0.5</v>
       </c>
       <c r="N15" s="71">
         <v>0.5</v>
@@ -2804,7 +2808,7 @@
       <c r="O15" s="10"/>
       <c r="P15" s="10">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" s="10">
         <f>K15*N15</f>
@@ -2841,8 +2845,8 @@
       <c r="L16" s="16">
         <v>10</v>
       </c>
-      <c r="M16" s="17">
-        <v>1</v>
+      <c r="M16" s="71">
+        <v>0.5</v>
       </c>
       <c r="N16" s="71">
         <v>0.5</v>
@@ -2885,18 +2889,20 @@
       <c r="L17" s="16">
         <v>10</v>
       </c>
-      <c r="M17" s="17">
-        <v>1</v>
-      </c>
-      <c r="N17" s="72"/>
+      <c r="M17" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="N17" s="72">
+        <v>1.5</v>
+      </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10">
         <f t="shared" ref="P17:P44" si="2">K17*M17</f>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="Q17" s="10">
-        <f>K17*N17</f>
-        <v>0</v>
+        <f t="shared" ref="Q17:Q22" si="3">K17*N17</f>
+        <v>0.75</v>
       </c>
       <c r="R17" s="57"/>
     </row>
@@ -2933,16 +2939,21 @@
       <c r="L18" s="16">
         <v>10</v>
       </c>
-      <c r="M18" s="17">
-        <v>1</v>
-      </c>
-      <c r="N18" s="71"/>
+      <c r="M18" s="71">
+        <v>2</v>
+      </c>
+      <c r="N18" s="71">
+        <v>2</v>
+      </c>
       <c r="O18" s="10"/>
       <c r="P18" s="10">
-        <f t="shared" si="2"/>
-        <v>0.3</v>
-      </c>
-      <c r="Q18" s="11"/>
+        <f t="shared" ref="P18:P22" si="4">K18*M18</f>
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="10">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
       <c r="R18" s="11"/>
     </row>
     <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -2978,16 +2989,21 @@
       <c r="L19" s="16">
         <v>10</v>
       </c>
-      <c r="M19" s="17">
-        <v>1</v>
-      </c>
-      <c r="N19" s="71"/>
+      <c r="M19" s="71">
+        <v>1</v>
+      </c>
+      <c r="N19" s="71">
+        <v>1</v>
+      </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="Q19" s="11"/>
+      <c r="Q19" s="10">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
       <c r="R19" s="11"/>
     </row>
     <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -3019,16 +3035,21 @@
       <c r="L20" s="16">
         <v>10</v>
       </c>
-      <c r="M20" s="17">
-        <v>1</v>
-      </c>
-      <c r="N20" s="71"/>
+      <c r="M20" s="71">
+        <v>1</v>
+      </c>
+      <c r="N20" s="71">
+        <v>1</v>
+      </c>
       <c r="O20" s="10"/>
       <c r="P20" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="Q20" s="11"/>
+      <c r="Q20" s="10">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
       <c r="R20" s="11"/>
     </row>
     <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -3060,16 +3081,21 @@
       <c r="L21" s="16">
         <v>10</v>
       </c>
-      <c r="M21" s="17">
-        <v>1</v>
-      </c>
-      <c r="N21" s="71"/>
+      <c r="M21" s="71">
+        <v>1</v>
+      </c>
+      <c r="N21" s="71">
+        <v>1</v>
+      </c>
       <c r="O21" s="10"/>
       <c r="P21" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="Q21" s="11"/>
+      <c r="Q21" s="10">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
       <c r="R21" s="11"/>
     </row>
     <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -3101,16 +3127,21 @@
       <c r="L22" s="16">
         <v>10</v>
       </c>
-      <c r="M22" s="17">
-        <v>1</v>
-      </c>
-      <c r="N22" s="71"/>
+      <c r="M22" s="71">
+        <v>1</v>
+      </c>
+      <c r="N22" s="71">
+        <v>1</v>
+      </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1</v>
       </c>
-      <c r="Q22" s="11"/>
+      <c r="Q22" s="10">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
       <c r="R22" s="11"/>
     </row>
     <row r="23" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -3158,7 +3189,7 @@
         <v>0.999</v>
       </c>
       <c r="Q23" s="60">
-        <f t="shared" ref="Q23:Q28" si="3">K23*N23</f>
+        <f t="shared" ref="Q23:Q28" si="5">K23*N23</f>
         <v>0.999</v>
       </c>
       <c r="R23" s="11"/>
@@ -3208,7 +3239,7 @@
         <v>0.999</v>
       </c>
       <c r="Q24" s="60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.999</v>
       </c>
       <c r="R24" s="11"/>
@@ -3258,7 +3289,7 @@
         <v>0.95</v>
       </c>
       <c r="Q25" s="60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.95</v>
       </c>
       <c r="R25" s="11"/>
@@ -3294,22 +3325,22 @@
         <v>0.2</v>
       </c>
       <c r="L26" s="16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M26" s="17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N26" s="17">
-        <v>2</v>
+        <v>4.9999900000000004</v>
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" s="60">
-        <f t="shared" si="3"/>
-        <v>0.4</v>
+        <f t="shared" si="5"/>
+        <v>0.99999800000000016</v>
       </c>
       <c r="R26" s="11"/>
     </row>
@@ -3358,7 +3389,7 @@
         <v>0.5</v>
       </c>
       <c r="Q27" s="60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
       <c r="R27" s="11"/>
@@ -3408,7 +3439,7 @@
         <v>0.1</v>
       </c>
       <c r="Q28" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
       <c r="R28" s="11"/>
@@ -3750,7 +3781,7 @@
       <c r="L36" s="16">
         <v>10</v>
       </c>
-      <c r="M36" s="17">
+      <c r="M36" s="71">
         <v>1</v>
       </c>
       <c r="N36" s="71">
@@ -3793,14 +3824,14 @@
       <c r="L37" s="16">
         <v>10</v>
       </c>
-      <c r="M37" s="17">
-        <v>1</v>
-      </c>
-      <c r="N37" s="71"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="71">
+        <v>1</v>
+      </c>
       <c r="O37" s="10"/>
       <c r="P37" s="10">
         <f t="shared" si="2"/>
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
@@ -3836,7 +3867,7 @@
       <c r="L38" s="16">
         <v>10</v>
       </c>
-      <c r="M38" s="17">
+      <c r="M38" s="71">
         <v>1</v>
       </c>
       <c r="N38" s="71">
@@ -3879,8 +3910,8 @@
       <c r="L39" s="16">
         <v>10</v>
       </c>
-      <c r="M39" s="17">
-        <v>1</v>
+      <c r="M39" s="71">
+        <v>0.1</v>
       </c>
       <c r="N39" s="71">
         <v>0.1</v>
@@ -3888,7 +3919,7 @@
       <c r="O39" s="10"/>
       <c r="P39" s="10">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q39" s="10">
         <f>K39*N39</f>
@@ -3925,7 +3956,7 @@
       <c r="L40" s="16">
         <v>10</v>
       </c>
-      <c r="M40" s="17">
+      <c r="M40" s="71">
         <v>1</v>
       </c>
       <c r="N40" s="71">
@@ -3968,7 +3999,7 @@
       <c r="L41" s="16">
         <v>10</v>
       </c>
-      <c r="M41" s="17">
+      <c r="M41" s="71">
         <v>1</v>
       </c>
       <c r="N41" s="71">
@@ -4101,18 +4132,20 @@
       <c r="L44" s="16">
         <v>10</v>
       </c>
-      <c r="M44" s="17">
-        <v>1</v>
-      </c>
-      <c r="N44" s="71"/>
+      <c r="M44" s="71">
+        <v>2</v>
+      </c>
+      <c r="N44" s="71">
+        <v>2</v>
+      </c>
       <c r="O44" s="10"/>
       <c r="P44" s="10">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="Q44" s="10">
         <f>K44*N44</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R44" s="11"/>
     </row>
@@ -4199,13 +4232,11 @@
       <c r="L46" s="16">
         <v>10</v>
       </c>
-      <c r="M46" s="17">
-        <v>1</v>
-      </c>
+      <c r="M46" s="71"/>
       <c r="N46" s="71"/>
       <c r="O46" s="10"/>
       <c r="P46" s="10">
-        <f t="shared" ref="P46:P54" si="4">K46*N46</f>
+        <f t="shared" ref="P46:R54" si="6">K46*N46</f>
         <v>0</v>
       </c>
       <c r="Q46" s="11"/>
@@ -4240,13 +4271,11 @@
       <c r="L47" s="16">
         <v>10</v>
       </c>
-      <c r="M47" s="17">
-        <v>1</v>
-      </c>
+      <c r="M47" s="71"/>
       <c r="N47" s="71"/>
       <c r="O47" s="10"/>
       <c r="P47" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q47" s="11"/>
@@ -4281,18 +4310,18 @@
       <c r="L48" s="16">
         <v>10</v>
       </c>
-      <c r="M48" s="17">
-        <v>1</v>
+      <c r="M48" s="71">
+        <v>1.4</v>
       </c>
       <c r="N48" s="71">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="O48" s="10"/>
       <c r="P48" s="10">
         <f>K48*N48</f>
-        <v>0.84</v>
-      </c>
-      <c r="Q48" s="11"/>
+        <v>0.97999999999999987</v>
+      </c>
+      <c r="Q48" s="10"/>
       <c r="R48" s="11"/>
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -4328,14 +4357,16 @@
       <c r="L49" s="16">
         <v>10</v>
       </c>
-      <c r="M49" s="17">
-        <v>1</v>
-      </c>
-      <c r="N49" s="71"/>
+      <c r="M49" s="71">
+        <v>1</v>
+      </c>
+      <c r="N49" s="71">
+        <v>1</v>
+      </c>
       <c r="O49" s="10"/>
       <c r="P49" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.7</v>
       </c>
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
@@ -4371,7 +4402,7 @@
       <c r="L50" s="16">
         <v>10</v>
       </c>
-      <c r="M50" s="17">
+      <c r="M50" s="71">
         <v>1</v>
       </c>
       <c r="N50" s="71">
@@ -4379,7 +4410,7 @@
       </c>
       <c r="O50" s="10"/>
       <c r="P50" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.06</v>
       </c>
       <c r="Q50" s="11"/>
@@ -4418,15 +4449,15 @@
       <c r="L51" s="16">
         <v>10</v>
       </c>
-      <c r="M51" s="17">
-        <v>1</v>
+      <c r="M51" s="71">
+        <v>0.8</v>
       </c>
       <c r="N51" s="71">
         <v>0.8</v>
       </c>
       <c r="O51" s="10"/>
       <c r="P51" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.55999999999999994</v>
       </c>
       <c r="Q51" s="11"/>
@@ -4461,17 +4492,22 @@
       <c r="L52" s="16">
         <v>10</v>
       </c>
-      <c r="M52" s="17">
-        <v>1</v>
-      </c>
-      <c r="N52" s="71"/>
+      <c r="M52" s="71">
+        <v>2</v>
+      </c>
+      <c r="N52" s="71">
+        <v>2</v>
+      </c>
       <c r="O52" s="10"/>
       <c r="P52" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>K52*N52</f>
+        <v>0.5</v>
       </c>
       <c r="Q52" s="11"/>
-      <c r="R52" s="11"/>
+      <c r="R52" s="10">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
@@ -4506,13 +4542,11 @@
       <c r="L53" s="16">
         <v>10</v>
       </c>
-      <c r="M53" s="17">
-        <v>1</v>
-      </c>
+      <c r="M53" s="71"/>
       <c r="N53" s="71"/>
       <c r="O53" s="10"/>
       <c r="P53" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q53" s="11"/>
@@ -4551,13 +4585,11 @@
       <c r="L54" s="16">
         <v>10</v>
       </c>
-      <c r="M54" s="17">
-        <v>1</v>
-      </c>
+      <c r="M54" s="71"/>
       <c r="N54" s="71"/>
       <c r="O54" s="10"/>
       <c r="P54" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q54" s="11"/>
@@ -4596,9 +4628,7 @@
       <c r="L55" s="16">
         <v>10</v>
       </c>
-      <c r="M55" s="17">
-        <v>1</v>
-      </c>
+      <c r="M55" s="71"/>
       <c r="N55" s="71"/>
       <c r="O55" s="10"/>
       <c r="P55" s="10"/>
@@ -4955,7 +4985,7 @@
       </c>
       <c r="O63" s="10"/>
       <c r="P63" s="10">
-        <f t="shared" ref="P63:P68" si="5">K63*M63</f>
+        <f t="shared" ref="P63:P68" si="7">K63*M63</f>
         <v>0.85</v>
       </c>
       <c r="Q63" s="11"/>
@@ -4998,7 +5028,7 @@
       </c>
       <c r="O64" s="10"/>
       <c r="P64" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
       <c r="Q64" s="11"/>
@@ -5041,7 +5071,7 @@
       </c>
       <c r="O65" s="10"/>
       <c r="P65" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.85</v>
       </c>
       <c r="Q65" s="11"/>
@@ -5088,7 +5118,7 @@
       </c>
       <c r="O66" s="10"/>
       <c r="P66" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="Q66" s="11"/>
@@ -5135,7 +5165,7 @@
       </c>
       <c r="O67" s="10"/>
       <c r="P67" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.95</v>
       </c>
       <c r="Q67" s="11"/>
@@ -5166,14 +5196,12 @@
       <c r="L68" s="16">
         <v>10</v>
       </c>
-      <c r="M68" s="17">
-        <v>1</v>
-      </c>
+      <c r="M68" s="17"/>
       <c r="N68" s="17"/>
       <c r="O68" s="45"/>
       <c r="P68" s="45">
-        <f t="shared" si="5"/>
-        <v>1.5</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="Q68" s="11"/>
       <c r="R68" s="28"/>
@@ -5201,6 +5229,426 @@
   </sheetData>
   <autoFilter ref="A1:R69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="G24">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G50">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H50">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M6">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M8">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23:M34">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M46:M55">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M56:M57">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:N2">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:N3">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:N4">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M9:N10 M12:N22 M36:N41 M44:N44">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:N11">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M35:N35">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M42:N42">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M43:N43">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M45:N45">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M58:N58">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M59:N59">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M60:N60">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M61:N61">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M62:N62">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M63:N63">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M64:N64">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M65:N65">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M66:N66">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M67:N67">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M68:N1048576">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N5:N6">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -5212,8 +5660,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
-    <cfRule type="colorScale" priority="26">
+  <conditionalFormatting sqref="N7:N8">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5224,55 +5672,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G38">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G50">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H38">
+  <conditionalFormatting sqref="N23:N34">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -5284,247 +5684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H50">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M1">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M68:N1048576 M2:M68">
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="37">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N4">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N6">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N8">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N9:N10 N12:N22 N46:N55 N36:N41 N44">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N11">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N23:N34">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N35">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N42">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N43">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N45">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N58">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N59">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N60">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N61">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N62">
+  <conditionalFormatting sqref="N46:N55">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -5536,68 +5696,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N63">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N64">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N65">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N66">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N67">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N56:N57">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239FDE19-B6FD-E243-AAC2-6513AA846C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AE2884-094E-1E44-9BB0-3F11BEB7D84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-43800" yWindow="600" windowWidth="36440" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,8 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$R$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$R$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$68</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="431">
   <si>
     <t>subsector</t>
   </si>
@@ -1369,6 +1369,15 @@
   </si>
   <si>
     <t>transformation_lndu_bound_classes.yaml</t>
+  </si>
+  <si>
+    <t>TX:FRST:INCREASE_SEQUESTRATION</t>
+  </si>
+  <si>
+    <t>Increase Sequestration</t>
+  </si>
+  <si>
+    <t>transformation_frst_increase_sequestration.yaml</t>
   </si>
 </sst>
 </file>
@@ -2108,7 +2117,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="13.1640625" style="34" bestFit="1" customWidth="1"/>
@@ -2423,16 +2432,12 @@
       <c r="L7" s="16">
         <v>10</v>
       </c>
-      <c r="M7" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="N7" s="17">
-        <v>0.4</v>
-      </c>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
       <c r="O7" s="10"/>
       <c r="P7" s="10">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -2897,7 +2902,7 @@
       </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10">
-        <f t="shared" ref="P17:P44" si="2">K17*M17</f>
+        <f t="shared" ref="P17:P45" si="2">K17*M17</f>
         <v>0.75</v>
       </c>
       <c r="Q17" s="10">
@@ -3189,7 +3194,7 @@
         <v>0.999</v>
       </c>
       <c r="Q23" s="60">
-        <f t="shared" ref="Q23:Q28" si="5">K23*N23</f>
+        <f t="shared" ref="Q23:Q29" si="5">K23*N23</f>
         <v>0.999</v>
       </c>
       <c r="R23" s="11"/>
@@ -3302,45 +3307,32 @@
         <v>70</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>77</v>
+        <v>428</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="53" t="s">
-        <v>283</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>284</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="E26" s="53"/>
+      <c r="F26" s="25"/>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
-      <c r="I26" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>286</v>
-      </c>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
       <c r="K26" s="15">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="L26" s="16">
         <v>7</v>
       </c>
-      <c r="M26" s="17">
-        <v>4</v>
-      </c>
+      <c r="M26" s="17"/>
       <c r="N26" s="17">
-        <v>4.9999900000000004</v>
+        <v>1</v>
       </c>
       <c r="O26" s="10"/>
-      <c r="P26" s="10">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
-      </c>
+      <c r="P26" s="10"/>
       <c r="Q26" s="60">
         <f t="shared" si="5"/>
-        <v>0.99999800000000016</v>
+        <v>0.05</v>
       </c>
       <c r="R26" s="11"/>
     </row>
@@ -3352,45 +3344,43 @@
         <v>70</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="E27" s="19">
+        <v>77</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="L27" s="16">
+        <v>7</v>
+      </c>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17">
         <v>0.1</v>
-      </c>
-      <c r="F27" s="16">
-        <v>12</v>
-      </c>
-      <c r="G27" s="17"/>
-      <c r="H27" s="71">
-        <v>1</v>
-      </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10">
-        <v>0</v>
-      </c>
-      <c r="K27" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="L27" s="16">
-        <v>10</v>
-      </c>
-      <c r="M27" s="17">
-        <v>1</v>
-      </c>
-      <c r="N27" s="17">
-        <v>1</v>
       </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="60">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>2.0000000000000004E-2</v>
       </c>
       <c r="R27" s="11"/>
     </row>
@@ -3402,27 +3392,27 @@
         <v>70</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="K28" s="19">
+        <v>423</v>
+      </c>
+      <c r="E28" s="19">
         <v>0.1</v>
+      </c>
+      <c r="F28" s="16">
+        <v>12</v>
+      </c>
+      <c r="G28" s="17"/>
+      <c r="H28" s="71">
+        <v>1</v>
+      </c>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10">
+        <v>0</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0.5</v>
       </c>
       <c r="L28" s="16">
         <v>10</v>
@@ -3436,39 +3426,43 @@
       <c r="O28" s="10"/>
       <c r="P28" s="10">
         <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="Q28" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="Q28" s="60">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
+      <c r="I29" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>290</v>
+      </c>
       <c r="K29" s="19">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="L29" s="16">
         <v>10</v>
@@ -3482,12 +3476,15 @@
       <c r="O29" s="10"/>
       <c r="P29" s="10">
         <f t="shared" si="2"/>
-        <v>0.9</v>
-      </c>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="28"/>
-    </row>
-    <row r="30" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.1</v>
+      </c>
+      <c r="Q29" s="11">
+        <f t="shared" si="5"/>
+        <v>0.1</v>
+      </c>
+      <c r="R29" s="11"/>
+    </row>
+    <row r="30" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>212</v>
       </c>
@@ -3495,23 +3492,23 @@
         <v>83</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
-      <c r="K30" s="19" t="s">
-        <v>295</v>
+      <c r="K30" s="19">
+        <v>0.9</v>
       </c>
       <c r="L30" s="16">
         <v>10</v>
@@ -3523,12 +3520,12 @@
         <v>1</v>
       </c>
       <c r="O30" s="10"/>
-      <c r="P30" s="10" t="e">
+      <c r="P30" s="10">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>0.9</v>
       </c>
       <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
+      <c r="R30" s="28"/>
     </row>
     <row r="31" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
@@ -3538,13 +3535,13 @@
         <v>83</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>294</v>
@@ -3554,7 +3551,7 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L31" s="16">
         <v>10</v>
@@ -3581,13 +3578,13 @@
         <v>83</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>294</v>
@@ -3597,7 +3594,7 @@
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
       <c r="K32" s="19" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L32" s="16">
         <v>10</v>
@@ -3621,26 +3618,26 @@
         <v>212</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="67" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" s="62" t="s">
-        <v>98</v>
+        <v>83</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
-      <c r="K33" s="15" t="s">
-        <v>302</v>
+      <c r="K33" s="19" t="s">
+        <v>299</v>
       </c>
       <c r="L33" s="16">
         <v>10</v>
@@ -3667,23 +3664,23 @@
         <v>96</v>
       </c>
       <c r="C34" s="67" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D34" s="62" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
-      <c r="K34" s="19">
-        <v>0.5</v>
+      <c r="K34" s="15" t="s">
+        <v>302</v>
       </c>
       <c r="L34" s="16">
         <v>10</v>
@@ -3695,105 +3692,105 @@
         <v>1</v>
       </c>
       <c r="O34" s="10"/>
-      <c r="P34" s="10">
+      <c r="P34" s="10" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+    </row>
+    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="L35" s="16">
+        <v>10</v>
+      </c>
+      <c r="M35" s="17">
+        <v>1</v>
+      </c>
+      <c r="N35" s="17">
+        <v>1</v>
+      </c>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
-    </row>
-    <row r="35" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="12" t="s">
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+    </row>
+    <row r="36" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B36" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C36" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="62" t="s">
+      <c r="D36" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E36" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F36" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12" t="s">
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="J35" s="12" t="s">
+      <c r="J36" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="K35" s="19">
+      <c r="K36" s="19">
         <v>0.3</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L36" s="16">
         <v>10</v>
       </c>
-      <c r="M35" s="17">
-        <v>1</v>
-      </c>
-      <c r="N35" s="17">
-        <v>1</v>
-      </c>
-      <c r="O35" s="10"/>
-      <c r="P35" s="60">
+      <c r="M36" s="17">
+        <v>1</v>
+      </c>
+      <c r="N36" s="17">
+        <v>1</v>
+      </c>
+      <c r="O36" s="10"/>
+      <c r="P36" s="60">
         <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
-      <c r="Q35" s="60">
-        <f>K35*N35</f>
+      <c r="Q36" s="60">
+        <f>K36*N36</f>
         <v>0.3</v>
       </c>
-      <c r="R35" s="29"/>
-    </row>
-    <row r="36" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="19">
-        <v>0.5</v>
-      </c>
-      <c r="L36" s="16">
-        <v>10</v>
-      </c>
-      <c r="M36" s="71">
-        <v>1</v>
-      </c>
-      <c r="N36" s="71">
-        <v>1</v>
-      </c>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q36" s="11"/>
-      <c r="R36" s="11"/>
+      <c r="R36" s="29"/>
     </row>
     <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
@@ -3803,80 +3800,78 @@
         <v>106</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
       <c r="K37" s="19">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="L37" s="16">
         <v>10</v>
       </c>
-      <c r="M37" s="71"/>
+      <c r="M37" s="71">
+        <v>1</v>
+      </c>
       <c r="N37" s="71">
         <v>1</v>
       </c>
       <c r="O37" s="10"/>
       <c r="P37" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
     <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
-        <v>226</v>
+        <v>309</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>419</v>
+        <v>110</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>420</v>
-      </c>
-      <c r="E38" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="F38" s="16">
-        <v>10</v>
-      </c>
-      <c r="G38" s="17"/>
-      <c r="H38" s="71">
-        <v>0.25</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
-      <c r="K38" s="73">
-        <v>0.2</v>
+      <c r="K38" s="19">
+        <v>0.9</v>
       </c>
       <c r="L38" s="16">
         <v>10</v>
       </c>
-      <c r="M38" s="71">
-        <v>1</v>
-      </c>
+      <c r="M38" s="71"/>
       <c r="N38" s="71">
         <v>1</v>
       </c>
       <c r="O38" s="10"/>
       <c r="P38" s="10">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
@@ -3889,42 +3884,41 @@
         <v>113</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>114</v>
+        <v>419</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
+        <v>420</v>
+      </c>
+      <c r="E39" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="F39" s="16">
+        <v>10</v>
+      </c>
+      <c r="G39" s="17"/>
+      <c r="H39" s="71">
+        <v>0.25</v>
+      </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
-      <c r="K39" s="20">
-        <v>0.5</v>
+      <c r="K39" s="73">
+        <v>0.2</v>
       </c>
       <c r="L39" s="16">
         <v>10</v>
       </c>
       <c r="M39" s="71">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N39" s="71">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O39" s="10"/>
       <c r="P39" s="10">
         <f t="shared" si="2"/>
-        <v>0.05</v>
-      </c>
-      <c r="Q39" s="10">
-        <f>K39*N39</f>
-        <v>0.05</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
     </row>
     <row r="40" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -3935,39 +3929,42 @@
         <v>113</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
-      <c r="K40" s="19">
+      <c r="K40" s="20">
         <v>0.5</v>
       </c>
       <c r="L40" s="16">
         <v>10</v>
       </c>
       <c r="M40" s="71">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="N40" s="71">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="O40" s="10"/>
       <c r="P40" s="10">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q40" s="11"/>
+        <v>0.05</v>
+      </c>
+      <c r="Q40" s="10">
+        <f>K40*N40</f>
+        <v>0.05</v>
+      </c>
       <c r="R40" s="11"/>
     </row>
     <row r="41" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -3978,23 +3975,23 @@
         <v>113</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
-      <c r="K41" s="20">
-        <v>0.95</v>
+      <c r="K41" s="19">
+        <v>0.5</v>
       </c>
       <c r="L41" s="16">
         <v>10</v>
@@ -4008,50 +4005,50 @@
       <c r="O41" s="10"/>
       <c r="P41" s="10">
         <f t="shared" si="2"/>
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
     </row>
     <row r="42" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G42" s="12"/>
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
       <c r="J42" s="12"/>
-      <c r="K42" s="19">
-        <v>0.2</v>
+      <c r="K42" s="20">
+        <v>0.95</v>
       </c>
       <c r="L42" s="16">
         <v>10</v>
       </c>
-      <c r="M42" s="17">
-        <v>1</v>
-      </c>
-      <c r="N42" s="17">
+      <c r="M42" s="71">
+        <v>1</v>
+      </c>
+      <c r="N42" s="71">
         <v>1</v>
       </c>
       <c r="O42" s="10"/>
       <c r="P42" s="10">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
@@ -4064,16 +4061,16 @@
         <v>123</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G43" s="12"/>
       <c r="H43" s="12"/>
@@ -4101,52 +4098,45 @@
     </row>
     <row r="44" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
-      <c r="I44" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="J44" s="12" t="s">
-        <v>327</v>
-      </c>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
       <c r="K44" s="19">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="L44" s="16">
         <v>10</v>
       </c>
-      <c r="M44" s="71">
-        <v>2</v>
-      </c>
-      <c r="N44" s="71">
-        <v>2</v>
+      <c r="M44" s="17">
+        <v>1</v>
+      </c>
+      <c r="N44" s="17">
+        <v>1</v>
       </c>
       <c r="O44" s="10"/>
       <c r="P44" s="10">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q44" s="10">
-        <f>K44*N44</f>
-        <v>0.5</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
     </row>
     <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -4154,27 +4144,27 @@
         <v>226</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G45" s="12"/>
-      <c r="H45" s="30"/>
+      <c r="H45" s="12"/>
       <c r="I45" s="12" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="K45" s="19">
         <v>0.25</v>
@@ -4182,24 +4172,24 @@
       <c r="L45" s="16">
         <v>10</v>
       </c>
-      <c r="M45" s="17">
-        <v>1</v>
-      </c>
-      <c r="N45" s="17">
-        <v>1</v>
+      <c r="M45" s="71">
+        <v>2</v>
+      </c>
+      <c r="N45" s="71">
+        <v>2</v>
       </c>
       <c r="O45" s="10"/>
       <c r="P45" s="10">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="Q45" s="10">
         <f>K45*N45</f>
-        <v>0.25</v>
-      </c>
-      <c r="Q45" s="10">
-        <f>K45*P45</f>
-        <v>6.25E-2</v>
+        <v>0.5</v>
       </c>
       <c r="R45" s="11"/>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>226</v>
       </c>
@@ -4207,24 +4197,24 @@
         <v>134</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G46" s="12"/>
       <c r="H46" s="30"/>
       <c r="I46" s="12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="K46" s="19">
         <v>0.25</v>
@@ -4232,17 +4222,24 @@
       <c r="L46" s="16">
         <v>10</v>
       </c>
-      <c r="M46" s="71"/>
-      <c r="N46" s="71"/>
+      <c r="M46" s="17">
+        <v>1</v>
+      </c>
+      <c r="N46" s="17">
+        <v>1</v>
+      </c>
       <c r="O46" s="10"/>
       <c r="P46" s="10">
-        <f t="shared" ref="P46:R54" si="6">K46*N46</f>
-        <v>0</v>
-      </c>
-      <c r="Q46" s="11"/>
+        <f>K46*N46</f>
+        <v>0.25</v>
+      </c>
+      <c r="Q46" s="10">
+        <f>K46*P46</f>
+        <v>6.25E-2</v>
+      </c>
       <c r="R46" s="11"/>
     </row>
-    <row r="47" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>226</v>
       </c>
@@ -4250,21 +4247,25 @@
         <v>134</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>335</v>
+      </c>
       <c r="K47" s="19">
         <v>0.25</v>
       </c>
@@ -4275,7 +4276,7 @@
       <c r="N47" s="71"/>
       <c r="O47" s="10"/>
       <c r="P47" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="P47:R55" si="6">K47*N47</f>
         <v>0</v>
       </c>
       <c r="Q47" s="11"/>
@@ -4289,39 +4290,35 @@
         <v>134</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
       <c r="K48" s="19">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="L48" s="16">
         <v>10</v>
       </c>
-      <c r="M48" s="71">
-        <v>1.4</v>
-      </c>
-      <c r="N48" s="71">
-        <v>1.4</v>
-      </c>
+      <c r="M48" s="71"/>
+      <c r="N48" s="71"/>
       <c r="O48" s="10"/>
       <c r="P48" s="10">
-        <f>K48*N48</f>
-        <v>0.97999999999999987</v>
-      </c>
-      <c r="Q48" s="10"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -4332,25 +4329,21 @@
         <v>134</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
-      <c r="I49" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>343</v>
-      </c>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
       <c r="K49" s="19">
         <v>0.7</v>
       </c>
@@ -4358,17 +4351,17 @@
         <v>10</v>
       </c>
       <c r="M49" s="71">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N49" s="71">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="O49" s="10"/>
       <c r="P49" s="10">
-        <f t="shared" si="6"/>
-        <v>0.7</v>
-      </c>
-      <c r="Q49" s="11"/>
+        <f>K49*N49</f>
+        <v>0.97999999999999987</v>
+      </c>
+      <c r="Q49" s="10"/>
       <c r="R49" s="11"/>
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -4379,25 +4372,27 @@
         <v>134</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>416</v>
+        <v>147</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E50" s="20">
+        <v>148</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="K50" s="19">
         <v>0.7</v>
-      </c>
-      <c r="F50" s="16">
-        <v>12</v>
-      </c>
-      <c r="G50" s="17"/>
-      <c r="H50" s="71">
-        <v>0.8</v>
-      </c>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="73">
-        <v>0.06</v>
       </c>
       <c r="L50" s="16">
         <v>10</v>
@@ -4411,7 +4406,7 @@
       <c r="O50" s="10"/>
       <c r="P50" s="10">
         <f t="shared" si="6"/>
-        <v>0.06</v>
+        <v>0.7</v>
       </c>
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
@@ -4424,41 +4419,39 @@
         <v>134</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>150</v>
+        <v>416</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="E51" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="K51" s="20">
+      <c r="E51" s="20">
         <v>0.7</v>
+      </c>
+      <c r="F51" s="16">
+        <v>12</v>
+      </c>
+      <c r="G51" s="17"/>
+      <c r="H51" s="71">
+        <v>0.8</v>
+      </c>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="73">
+        <v>0.06</v>
       </c>
       <c r="L51" s="16">
         <v>10</v>
       </c>
       <c r="M51" s="71">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N51" s="71">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O51" s="10"/>
       <c r="P51" s="10">
         <f t="shared" si="6"/>
-        <v>0.55999999999999994</v>
+        <v>0.06</v>
       </c>
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
@@ -4471,43 +4464,44 @@
         <v>134</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="19">
-        <v>0.25</v>
+      <c r="I52" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="K52" s="20">
+        <v>0.7</v>
       </c>
       <c r="L52" s="16">
         <v>10</v>
       </c>
       <c r="M52" s="71">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N52" s="71">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="O52" s="10"/>
       <c r="P52" s="10">
-        <f>K52*N52</f>
-        <v>0.5</v>
+        <f t="shared" si="6"/>
+        <v>0.55999999999999994</v>
       </c>
       <c r="Q52" s="11"/>
-      <c r="R52" s="10">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
+      <c r="R52" s="11"/>
     </row>
     <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
@@ -4517,40 +4511,43 @@
         <v>134</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G53" s="12"/>
       <c r="H53" s="12"/>
-      <c r="I53" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>353</v>
-      </c>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
       <c r="K53" s="19">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L53" s="16">
         <v>10</v>
       </c>
-      <c r="M53" s="71"/>
-      <c r="N53" s="71"/>
+      <c r="M53" s="71">
+        <v>2</v>
+      </c>
+      <c r="N53" s="71">
+        <v>2</v>
+      </c>
       <c r="O53" s="10"/>
       <c r="P53" s="10">
+        <f>K53*N53</f>
+        <v>0.5</v>
+      </c>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="10">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q53" s="11"/>
-      <c r="R53" s="11"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
@@ -4560,27 +4557,27 @@
         <v>134</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K54" s="19">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L54" s="16">
         <v>10</v>
@@ -4603,27 +4600,27 @@
         <v>134</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G55" s="12"/>
       <c r="H55" s="12"/>
       <c r="I55" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="K55" s="19" t="s">
-        <v>362</v>
+        <v>357</v>
+      </c>
+      <c r="K55" s="19">
+        <v>0.3</v>
       </c>
       <c r="L55" s="16">
         <v>10</v>
@@ -4631,50 +4628,50 @@
       <c r="M55" s="71"/>
       <c r="N55" s="71"/>
       <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
+      <c r="P55" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
     </row>
     <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="19">
-        <v>0.85</v>
+      <c r="I56" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="J56" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>362</v>
       </c>
       <c r="L56" s="16">
         <v>10</v>
       </c>
-      <c r="M56" s="17">
-        <v>1</v>
-      </c>
-      <c r="N56" s="17">
-        <v>1</v>
-      </c>
+      <c r="M56" s="71"/>
+      <c r="N56" s="71"/>
       <c r="O56" s="10"/>
-      <c r="P56" s="10">
-        <f>K56*M56</f>
-        <v>0.85</v>
-      </c>
+      <c r="P56" s="10"/>
       <c r="Q56" s="11"/>
       <c r="R56" s="11"/>
     </row>
@@ -4686,27 +4683,23 @@
         <v>165</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G57" s="12"/>
       <c r="H57" s="12"/>
-      <c r="I57" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>368</v>
-      </c>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
       <c r="K57" s="19">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L57" s="16">
         <v>10</v>
@@ -4720,40 +4713,40 @@
       <c r="O57" s="10"/>
       <c r="P57" s="10">
         <f>K57*M57</f>
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
     </row>
     <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
-        <v>369</v>
+        <v>51</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G58" s="12"/>
       <c r="H58" s="12"/>
       <c r="I58" s="12" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="K58" s="19" t="s">
-        <v>374</v>
+        <v>368</v>
+      </c>
+      <c r="K58" s="19">
+        <v>0.9</v>
       </c>
       <c r="L58" s="16">
         <v>10</v>
@@ -4765,7 +4758,10 @@
         <v>1</v>
       </c>
       <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
+      <c r="P58" s="10">
+        <f>K58*M58</f>
+        <v>0.9</v>
+      </c>
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
     </row>
@@ -4777,13 +4773,13 @@
         <v>172</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>371</v>
@@ -4791,13 +4787,13 @@
       <c r="G59" s="12"/>
       <c r="H59" s="12"/>
       <c r="I59" s="12" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="K59" s="19" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="L59" s="16">
         <v>10</v>
@@ -4821,13 +4817,13 @@
         <v>172</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>371</v>
@@ -4835,13 +4831,13 @@
       <c r="G60" s="12"/>
       <c r="H60" s="12"/>
       <c r="I60" s="12" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K60" s="19" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="L60" s="16">
         <v>10</v>
@@ -4862,30 +4858,30 @@
         <v>369</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C61" s="67" t="s">
-        <v>183</v>
-      </c>
-      <c r="D61" s="62" t="s">
-        <v>184</v>
+        <v>172</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>180</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
       <c r="I61" s="12" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="K61" s="19">
-        <v>0.3</v>
+        <v>381</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>382</v>
       </c>
       <c r="L61" s="16">
         <v>10</v>
@@ -4897,10 +4893,7 @@
         <v>1</v>
       </c>
       <c r="O61" s="10"/>
-      <c r="P61" s="10">
-        <f>K61*M61</f>
-        <v>0.3</v>
-      </c>
+      <c r="P61" s="10"/>
       <c r="Q61" s="11"/>
       <c r="R61" s="11"/>
     </row>
@@ -4912,23 +4905,27 @@
         <v>182</v>
       </c>
       <c r="C62" s="67" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D62" s="62" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G62" s="12"/>
       <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="15" t="s">
-        <v>389</v>
+      <c r="I62" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="J62" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="K62" s="19">
+        <v>0.3</v>
       </c>
       <c r="L62" s="16">
         <v>10</v>
@@ -4940,7 +4937,10 @@
         <v>1</v>
       </c>
       <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
+      <c r="P62" s="10">
+        <f>K62*M62</f>
+        <v>0.3</v>
+      </c>
       <c r="Q62" s="11"/>
       <c r="R62" s="11"/>
     </row>
@@ -4952,27 +4952,23 @@
         <v>182</v>
       </c>
       <c r="C63" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="E63" s="53" t="s">
-        <v>390</v>
-      </c>
-      <c r="F63" s="22" t="s">
-        <v>391</v>
+        <v>186</v>
+      </c>
+      <c r="D63" s="62" t="s">
+        <v>187</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>388</v>
       </c>
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
-      <c r="I63" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="K63" s="15">
-        <v>0.85</v>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="15" t="s">
+        <v>389</v>
       </c>
       <c r="L63" s="16">
         <v>10</v>
@@ -4984,10 +4980,7 @@
         <v>1</v>
       </c>
       <c r="O63" s="10"/>
-      <c r="P63" s="10">
-        <f t="shared" ref="P63:P68" si="7">K63*M63</f>
-        <v>0.85</v>
-      </c>
+      <c r="P63" s="10"/>
       <c r="Q63" s="11"/>
       <c r="R63" s="11"/>
     </row>
@@ -4999,21 +4992,25 @@
         <v>182</v>
       </c>
       <c r="C64" s="67" t="s">
-        <v>191</v>
-      </c>
-      <c r="D64" s="62" t="s">
-        <v>192</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>395</v>
+        <v>189</v>
+      </c>
+      <c r="D64" s="64" t="s">
+        <v>167</v>
+      </c>
+      <c r="E64" s="53" t="s">
+        <v>390</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>391</v>
       </c>
       <c r="G64" s="12"/>
       <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
+      <c r="I64" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>393</v>
+      </c>
       <c r="K64" s="15">
         <v>0.85</v>
       </c>
@@ -5028,7 +5025,7 @@
       </c>
       <c r="O64" s="10"/>
       <c r="P64" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="P64:P69" si="7">K64*M64</f>
         <v>0.85</v>
       </c>
       <c r="Q64" s="11"/>
@@ -5042,16 +5039,16 @@
         <v>182</v>
       </c>
       <c r="C65" s="67" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D65" s="62" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
@@ -5078,34 +5075,30 @@
       <c r="R65" s="11"/>
     </row>
     <row r="66" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="40" t="s">
+      <c r="A66" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="B66" s="55" t="s">
+      <c r="B66" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C66" s="69" t="s">
-        <v>197</v>
-      </c>
-      <c r="D66" s="65" t="s">
-        <v>198</v>
-      </c>
-      <c r="E66" s="55" t="s">
-        <v>398</v>
-      </c>
-      <c r="F66" s="40" t="s">
-        <v>399</v>
-      </c>
-      <c r="G66" s="40"/>
-      <c r="H66" s="40"/>
-      <c r="I66" s="40" t="s">
-        <v>400</v>
-      </c>
-      <c r="J66" s="40" t="s">
-        <v>401</v>
-      </c>
-      <c r="K66" s="41">
-        <v>1</v>
+      <c r="C66" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D66" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="15">
+        <v>0.85</v>
       </c>
       <c r="L66" s="16">
         <v>10</v>
@@ -5119,40 +5112,40 @@
       <c r="O66" s="10"/>
       <c r="P66" s="10">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="Q66" s="11"/>
       <c r="R66" s="11"/>
     </row>
     <row r="67" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="42" t="s">
+      <c r="A67" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="B67" s="43" t="s">
+      <c r="B67" s="55" t="s">
         <v>182</v>
       </c>
-      <c r="C67" s="70" t="s">
-        <v>200</v>
-      </c>
-      <c r="D67" s="66" t="s">
-        <v>201</v>
-      </c>
-      <c r="E67" s="43" t="s">
-        <v>402</v>
-      </c>
-      <c r="F67" s="42" t="s">
-        <v>403</v>
-      </c>
-      <c r="G67" s="42"/>
-      <c r="H67" s="42"/>
-      <c r="I67" s="42" t="s">
-        <v>404</v>
-      </c>
-      <c r="J67" s="42" t="s">
-        <v>405</v>
-      </c>
-      <c r="K67" s="44">
-        <v>0.95</v>
+      <c r="C67" s="69" t="s">
+        <v>197</v>
+      </c>
+      <c r="D67" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="E67" s="55" t="s">
+        <v>398</v>
+      </c>
+      <c r="F67" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="G67" s="40"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="40" t="s">
+        <v>400</v>
+      </c>
+      <c r="J67" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="K67" s="41">
+        <v>1</v>
       </c>
       <c r="L67" s="16">
         <v>10</v>
@@ -5166,68 +5159,115 @@
       <c r="O67" s="10"/>
       <c r="P67" s="10">
         <f t="shared" si="7"/>
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="11"/>
       <c r="R67" s="11"/>
     </row>
-    <row r="68" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="43" t="s">
-        <v>226</v>
+    <row r="68" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="42" t="s">
+        <v>369</v>
       </c>
       <c r="B68" s="43" t="s">
-        <v>407</v>
-      </c>
-      <c r="C68" s="43" t="s">
-        <v>406</v>
-      </c>
-      <c r="D68" s="43" t="s">
-        <v>408</v>
-      </c>
-      <c r="E68" s="43"/>
-      <c r="F68" s="43"/>
-      <c r="G68" s="43"/>
-      <c r="H68" s="43"/>
-      <c r="I68" s="43"/>
-      <c r="J68" s="43"/>
-      <c r="K68" s="46">
-        <v>1.5</v>
+        <v>182</v>
+      </c>
+      <c r="C68" s="70" t="s">
+        <v>200</v>
+      </c>
+      <c r="D68" s="66" t="s">
+        <v>201</v>
+      </c>
+      <c r="E68" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="F68" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="J68" s="42" t="s">
+        <v>405</v>
+      </c>
+      <c r="K68" s="44">
+        <v>0.95</v>
       </c>
       <c r="L68" s="16">
         <v>10</v>
       </c>
-      <c r="M68" s="17"/>
-      <c r="N68" s="17"/>
-      <c r="O68" s="45"/>
-      <c r="P68" s="45">
+      <c r="M68" s="17">
+        <v>1</v>
+      </c>
+      <c r="N68" s="17">
+        <v>1</v>
+      </c>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10">
+        <f t="shared" si="7"/>
+        <v>0.95</v>
+      </c>
+      <c r="Q68" s="11"/>
+      <c r="R68" s="11"/>
+    </row>
+    <row r="69" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="B69" s="43" t="s">
+        <v>407</v>
+      </c>
+      <c r="C69" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="D69" s="43" t="s">
+        <v>408</v>
+      </c>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
+      <c r="H69" s="43"/>
+      <c r="I69" s="43"/>
+      <c r="J69" s="43"/>
+      <c r="K69" s="46">
+        <v>1.5</v>
+      </c>
+      <c r="L69" s="16">
+        <v>10</v>
+      </c>
+      <c r="M69" s="17"/>
+      <c r="N69" s="17"/>
+      <c r="O69" s="45"/>
+      <c r="P69" s="45">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q68" s="11"/>
-      <c r="R68" s="28"/>
-    </row>
-    <row r="69" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="31"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
-      <c r="J69" s="31"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="32"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="33"/>
-      <c r="P69" s="33"/>
       <c r="Q69" s="11"/>
-      <c r="R69" s="27"/>
+      <c r="R69" s="28"/>
+    </row>
+    <row r="70" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="31"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="10"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="33"/>
+      <c r="P70" s="33"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="G24">
     <cfRule type="colorScale" priority="31">
       <colorScale>
@@ -5240,7 +5280,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
+  <conditionalFormatting sqref="G28">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -5252,7 +5292,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G38">
+  <conditionalFormatting sqref="G39">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -5264,7 +5304,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G50">
+  <conditionalFormatting sqref="G51">
     <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
@@ -5288,7 +5328,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
+  <conditionalFormatting sqref="H28">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -5300,7 +5340,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38">
+  <conditionalFormatting sqref="H39">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -5312,7 +5352,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H50">
+  <conditionalFormatting sqref="H51">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -5360,7 +5400,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M23:M34">
+  <conditionalFormatting sqref="M23:M35">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5372,7 +5412,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M46:M55">
+  <conditionalFormatting sqref="M47:M56">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5384,7 +5424,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M56:M57">
+  <conditionalFormatting sqref="M57:M58">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5432,7 +5472,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N10 M12:N22 M36:N41 M44:N44">
+  <conditionalFormatting sqref="M9:N10 M12:N22 M37:N42 M45:N45">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
@@ -5456,7 +5496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M35:N35">
+  <conditionalFormatting sqref="M36:N36">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -5468,7 +5508,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M42:N42">
+  <conditionalFormatting sqref="M43:N43">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -5480,7 +5520,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M43:N43">
+  <conditionalFormatting sqref="M44:N44">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -5492,7 +5532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M45:N45">
+  <conditionalFormatting sqref="M46:N46">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -5504,7 +5544,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M58:N58">
+  <conditionalFormatting sqref="M59:N59">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -5516,7 +5556,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M59:N59">
+  <conditionalFormatting sqref="M60:N60">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -5528,7 +5568,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M60:N60">
+  <conditionalFormatting sqref="M61:N61">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -5540,7 +5580,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M61:N61">
+  <conditionalFormatting sqref="M62:N62">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -5552,7 +5592,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M62:N62">
+  <conditionalFormatting sqref="M63:N63">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -5564,7 +5604,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M63:N63">
+  <conditionalFormatting sqref="M64:N64">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -5576,7 +5616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M64:N64">
+  <conditionalFormatting sqref="M65:N65">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -5588,7 +5628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M65:N65">
+  <conditionalFormatting sqref="M66:N66">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -5600,7 +5640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M66:N66">
+  <conditionalFormatting sqref="M67:N67">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -5612,7 +5652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M67:N67">
+  <conditionalFormatting sqref="M68:N68">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5624,7 +5664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M68:N1048576">
+  <conditionalFormatting sqref="M69:N1048576">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
@@ -5672,7 +5712,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N23:N34">
+  <conditionalFormatting sqref="N23:N35">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -5684,7 +5724,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N46:N55">
+  <conditionalFormatting sqref="N47:N56">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -5696,7 +5736,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N56:N57">
+  <conditionalFormatting sqref="N57:N58">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -5717,7 +5757,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" style="3" bestFit="1" customWidth="1"/>
@@ -6053,13 +6093,13 @@
         <v>70</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>74</v>
+        <v>428</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>429</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>76</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6067,13 +6107,13 @@
         <v>70</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>425</v>
+        <v>74</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>426</v>
+        <v>75</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>427</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6081,13 +6121,13 @@
         <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>78</v>
+        <v>426</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6095,13 +6135,13 @@
         <v>70</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6109,27 +6149,27 @@
         <v>70</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>86</v>
+        <v>424</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6137,13 +6177,13 @@
         <v>83</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6151,13 +6191,13 @@
         <v>83</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6165,27 +6205,27 @@
         <v>83</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6193,13 +6233,13 @@
         <v>96</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6207,27 +6247,27 @@
         <v>96</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6235,27 +6275,27 @@
         <v>106</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6263,13 +6303,13 @@
         <v>113</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>419</v>
+        <v>114</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>420</v>
+        <v>115</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>421</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6277,13 +6317,13 @@
         <v>113</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>117</v>
+        <v>419</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>118</v>
+        <v>420</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>119</v>
+        <v>421</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6291,27 +6331,27 @@
         <v>113</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6319,41 +6359,41 @@
         <v>123</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6361,13 +6401,13 @@
         <v>134</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6375,13 +6415,13 @@
         <v>134</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6389,13 +6429,13 @@
         <v>134</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6403,13 +6443,13 @@
         <v>134</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6417,13 +6457,13 @@
         <v>134</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>416</v>
+        <v>147</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>417</v>
+        <v>148</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>418</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6431,13 +6471,13 @@
         <v>134</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>150</v>
+        <v>416</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>151</v>
+        <v>417</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>152</v>
+        <v>418</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6445,13 +6485,13 @@
         <v>134</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6459,13 +6499,13 @@
         <v>134</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6473,13 +6513,13 @@
         <v>134</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6487,27 +6527,27 @@
         <v>134</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6515,27 +6555,27 @@
         <v>165</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6543,13 +6583,13 @@
         <v>172</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6557,27 +6597,27 @@
         <v>172</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6585,13 +6625,13 @@
         <v>182</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6599,13 +6639,13 @@
         <v>182</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6613,41 +6653,41 @@
         <v>182</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="47" t="s">
+    <row r="66" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="B65" s="47" t="s">
+      <c r="B66" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="C65" s="47" t="s">
+      <c r="C66" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="D65" s="47" t="s">
+      <c r="D66" s="47" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="48" t="s">
-        <v>182</v>
-      </c>
-      <c r="B66" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="C66" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="D66" s="48" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6655,26 +6695,40 @@
         <v>182</v>
       </c>
       <c r="B67" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="C67" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="D67" s="48" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="C67" s="48" t="s">
+      <c r="C68" s="48" t="s">
         <v>201</v>
       </c>
-      <c r="D67" s="48" t="s">
+      <c r="D68" s="48" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="49" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="49" t="s">
         <v>407</v>
       </c>
-      <c r="B68" s="49" t="s">
+      <c r="B69" s="49" t="s">
         <v>406</v>
       </c>
-      <c r="C68" s="49" t="s">
+      <c r="C69" s="49" t="s">
         <v>408</v>
       </c>
-      <c r="D68" s="49" t="s">
+      <c r="D69" s="49" t="s">
         <v>409</v>
       </c>
     </row>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AE2884-094E-1E44-9BB0-3F11BEB7D84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D806F3-EF87-1C4E-891D-063E089CCC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-43800" yWindow="600" windowWidth="36440" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2114,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R70"/>
@@ -2183,7 +2183,7 @@
       <c r="Q1" s="11"/>
       <c r="R1" s="11"/>
     </row>
-    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>212</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
     </row>
-    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>212</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>1.8</v>
       </c>
       <c r="N3" s="17">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10">
@@ -2265,7 +2265,7 @@
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
     </row>
-    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>212</v>
       </c>
@@ -2297,9 +2297,7 @@
       <c r="M4" s="17">
         <v>1.5</v>
       </c>
-      <c r="N4" s="17">
-        <v>1.5</v>
-      </c>
+      <c r="N4" s="17"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10">
         <f t="shared" si="0"/>
@@ -2310,7 +2308,7 @@
       </c>
       <c r="R4" s="11"/>
     </row>
-    <row r="5" spans="1:18" s="4" customFormat="1" ht="153" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" s="4" customFormat="1" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>212</v>
       </c>
@@ -2342,9 +2340,7 @@
       <c r="M5" s="17">
         <v>1</v>
       </c>
-      <c r="N5" s="17">
-        <v>1</v>
-      </c>
+      <c r="N5" s="17"/>
       <c r="O5" s="10"/>
       <c r="P5" s="10" t="e">
         <f t="shared" si="0"/>
@@ -2353,7 +2349,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
     </row>
-    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>212</v>
       </c>
@@ -2389,9 +2385,7 @@
       <c r="M6" s="17">
         <v>4.5</v>
       </c>
-      <c r="N6" s="17">
-        <v>5</v>
-      </c>
+      <c r="N6" s="17"/>
       <c r="O6" s="10"/>
       <c r="P6" s="10">
         <f>0.6*M6</f>
@@ -2399,11 +2393,11 @@
       </c>
       <c r="Q6" s="10">
         <f>K6*N6</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>226</v>
       </c>
@@ -2442,7 +2436,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2492,7 +2486,7 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>226</v>
       </c>
@@ -2539,7 +2533,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>226</v>
       </c>
@@ -2586,7 +2580,7 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>226</v>
       </c>
@@ -2630,7 +2624,7 @@
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
@@ -2676,7 +2670,7 @@
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>226</v>
       </c>
@@ -2721,7 +2715,7 @@
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>226</v>
       </c>
@@ -2771,7 +2765,7 @@
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
@@ -2821,7 +2815,7 @@
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -2861,7 +2855,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2898,7 +2892,7 @@
         <v>1.5</v>
       </c>
       <c r="N17" s="72">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10">
@@ -2907,11 +2901,11 @@
       </c>
       <c r="Q17" s="10">
         <f t="shared" ref="Q17:Q22" si="3">K17*N17</f>
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="R17" s="57"/>
     </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2947,8 +2941,8 @@
       <c r="M18" s="71">
         <v>2</v>
       </c>
-      <c r="N18" s="71">
-        <v>2</v>
+      <c r="N18" s="72">
+        <v>1</v>
       </c>
       <c r="O18" s="10"/>
       <c r="P18" s="10">
@@ -2957,11 +2951,11 @@
       </c>
       <c r="Q18" s="10">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2997,7 +2991,7 @@
       <c r="M19" s="71">
         <v>1</v>
       </c>
-      <c r="N19" s="71">
+      <c r="N19" s="72">
         <v>1</v>
       </c>
       <c r="O19" s="10"/>
@@ -3011,7 +3005,7 @@
       </c>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -3043,7 +3037,7 @@
       <c r="M20" s="71">
         <v>1</v>
       </c>
-      <c r="N20" s="71">
+      <c r="N20" s="72">
         <v>1</v>
       </c>
       <c r="O20" s="10"/>
@@ -3057,7 +3051,7 @@
       </c>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -3089,7 +3083,7 @@
       <c r="M21" s="71">
         <v>1</v>
       </c>
-      <c r="N21" s="71">
+      <c r="N21" s="72">
         <v>1</v>
       </c>
       <c r="O21" s="10"/>
@@ -3103,7 +3097,7 @@
       </c>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
@@ -3135,7 +3129,7 @@
       <c r="M22" s="71">
         <v>1</v>
       </c>
-      <c r="N22" s="71">
+      <c r="N22" s="72">
         <v>1</v>
       </c>
       <c r="O22" s="10"/>
@@ -3149,7 +3143,7 @@
       </c>
       <c r="R22" s="11"/>
     </row>
-    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>212</v>
       </c>
@@ -3194,12 +3188,12 @@
         <v>0.999</v>
       </c>
       <c r="Q23" s="60">
-        <f t="shared" ref="Q23:Q29" si="5">K23*N23</f>
+        <f t="shared" ref="Q23:Q30" si="5">K23*N23</f>
         <v>0.999</v>
       </c>
       <c r="R23" s="11"/>
     </row>
-    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>212</v>
       </c>
@@ -3249,7 +3243,7 @@
       </c>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>212</v>
       </c>
@@ -3299,7 +3293,7 @@
       </c>
       <c r="R25" s="11"/>
     </row>
-    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>212</v>
       </c>
@@ -3336,7 +3330,7 @@
       </c>
       <c r="R26" s="11"/>
     </row>
-    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>212</v>
       </c>
@@ -3384,7 +3378,7 @@
       </c>
       <c r="R27" s="11"/>
     </row>
-    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>212</v>
       </c>
@@ -3434,7 +3428,7 @@
       </c>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>212</v>
       </c>
@@ -3484,7 +3478,7 @@
       </c>
       <c r="R29" s="11"/>
     </row>
-    <row r="30" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>212</v>
       </c>
@@ -3524,10 +3518,13 @@
         <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
-      <c r="Q30" s="11"/>
+      <c r="Q30" s="11">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
       <c r="R30" s="28"/>
     </row>
-    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>212</v>
       </c>
@@ -3559,9 +3556,7 @@
       <c r="M31" s="17">
         <v>1</v>
       </c>
-      <c r="N31" s="17">
-        <v>1</v>
-      </c>
+      <c r="N31" s="17"/>
       <c r="O31" s="10"/>
       <c r="P31" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3570,7 +3565,7 @@
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
     </row>
-    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>212</v>
       </c>
@@ -3602,9 +3597,7 @@
       <c r="M32" s="17">
         <v>1</v>
       </c>
-      <c r="N32" s="17">
-        <v>1</v>
-      </c>
+      <c r="N32" s="17"/>
       <c r="O32" s="10"/>
       <c r="P32" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3613,7 +3606,7 @@
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
     </row>
-    <row r="33" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>212</v>
       </c>
@@ -3645,9 +3638,7 @@
       <c r="M33" s="17">
         <v>1</v>
       </c>
-      <c r="N33" s="17">
-        <v>1</v>
-      </c>
+      <c r="N33" s="17"/>
       <c r="O33" s="10"/>
       <c r="P33" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3656,7 +3647,7 @@
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
     </row>
-    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>212</v>
       </c>
@@ -3688,9 +3679,7 @@
       <c r="M34" s="17">
         <v>1</v>
       </c>
-      <c r="N34" s="17">
-        <v>1</v>
-      </c>
+      <c r="N34" s="17"/>
       <c r="O34" s="10"/>
       <c r="P34" s="10" t="e">
         <f t="shared" si="2"/>
@@ -3699,7 +3688,7 @@
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
     </row>
-    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>212</v>
       </c>
@@ -3731,9 +3720,7 @@
       <c r="M35" s="17">
         <v>1</v>
       </c>
-      <c r="N35" s="17">
-        <v>1</v>
-      </c>
+      <c r="N35" s="17"/>
       <c r="O35" s="10"/>
       <c r="P35" s="10">
         <f t="shared" si="2"/>
@@ -3742,7 +3729,7 @@
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
     </row>
-    <row r="36" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>212</v>
       </c>
@@ -3778,9 +3765,7 @@
       <c r="M36" s="17">
         <v>1</v>
       </c>
-      <c r="N36" s="17">
-        <v>1</v>
-      </c>
+      <c r="N36" s="17"/>
       <c r="O36" s="10"/>
       <c r="P36" s="60">
         <f t="shared" si="2"/>
@@ -3788,11 +3773,11 @@
       </c>
       <c r="Q36" s="60">
         <f>K36*N36</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R36" s="29"/>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>309</v>
       </c>
@@ -3835,7 +3820,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>309</v>
       </c>
@@ -3876,7 +3861,7 @@
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
     </row>
-    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>226</v>
       </c>
@@ -3921,7 +3906,7 @@
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
     </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>226</v>
       </c>
@@ -3967,7 +3952,7 @@
       </c>
       <c r="R40" s="11"/>
     </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>226</v>
       </c>
@@ -4010,7 +3995,7 @@
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
     </row>
-    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>226</v>
       </c>
@@ -4053,7 +4038,7 @@
       <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
     </row>
-    <row r="43" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>212</v>
       </c>
@@ -4096,7 +4081,7 @@
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
     </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>212</v>
       </c>
@@ -4139,7 +4124,7 @@
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -4176,7 +4161,7 @@
         <v>2</v>
       </c>
       <c r="N45" s="71">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O45" s="10"/>
       <c r="P45" s="10">
@@ -4185,11 +4170,11 @@
       </c>
       <c r="Q45" s="10">
         <f>K45*N45</f>
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="R45" s="11"/>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>226</v>
       </c>
@@ -4239,7 +4224,7 @@
       </c>
       <c r="R46" s="11"/>
     </row>
-    <row r="47" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" s="4" customFormat="1" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>226</v>
       </c>
@@ -4282,7 +4267,7 @@
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
     </row>
-    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>226</v>
       </c>
@@ -4321,7 +4306,7 @@
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
     </row>
-    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>226</v>
       </c>
@@ -4364,7 +4349,7 @@
       <c r="Q49" s="10"/>
       <c r="R49" s="11"/>
     </row>
-    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>226</v>
       </c>
@@ -4411,7 +4396,7 @@
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
     </row>
-    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>226</v>
       </c>
@@ -4456,7 +4441,7 @@
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>226</v>
       </c>
@@ -4503,7 +4488,7 @@
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
     </row>
-    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>226</v>
       </c>
@@ -4549,7 +4534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>226</v>
       </c>
@@ -4592,7 +4577,7 @@
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
     </row>
-    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>226</v>
       </c>
@@ -4635,7 +4620,7 @@
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
     </row>
-    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>226</v>
       </c>
@@ -4675,7 +4660,7 @@
       <c r="Q56" s="11"/>
       <c r="R56" s="11"/>
     </row>
-    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>51</v>
       </c>
@@ -4718,7 +4703,7 @@
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
     </row>
-    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>51</v>
       </c>
@@ -4845,9 +4830,7 @@
       <c r="M60" s="17">
         <v>1</v>
       </c>
-      <c r="N60" s="17">
-        <v>1</v>
-      </c>
+      <c r="N60" s="17"/>
       <c r="O60" s="10"/>
       <c r="P60" s="10"/>
       <c r="Q60" s="11"/>
@@ -4889,9 +4872,7 @@
       <c r="M61" s="17">
         <v>1</v>
       </c>
-      <c r="N61" s="17">
-        <v>1</v>
-      </c>
+      <c r="N61" s="17"/>
       <c r="O61" s="10"/>
       <c r="P61" s="10"/>
       <c r="Q61" s="11"/>
@@ -5020,9 +5001,7 @@
       <c r="M64" s="17">
         <v>1</v>
       </c>
-      <c r="N64" s="17">
-        <v>1</v>
-      </c>
+      <c r="N64" s="17"/>
       <c r="O64" s="10"/>
       <c r="P64" s="10">
         <f t="shared" ref="P64:P69" si="7">K64*M64</f>
@@ -5063,9 +5042,7 @@
       <c r="M65" s="17">
         <v>1</v>
       </c>
-      <c r="N65" s="17">
-        <v>1</v>
-      </c>
+      <c r="N65" s="17"/>
       <c r="O65" s="10"/>
       <c r="P65" s="10">
         <f t="shared" si="7"/>
@@ -5106,9 +5083,7 @@
       <c r="M66" s="17">
         <v>1</v>
       </c>
-      <c r="N66" s="17">
-        <v>1</v>
-      </c>
+      <c r="N66" s="17"/>
       <c r="O66" s="10"/>
       <c r="P66" s="10">
         <f t="shared" si="7"/>
@@ -5153,9 +5128,7 @@
       <c r="M67" s="17">
         <v>1</v>
       </c>
-      <c r="N67" s="17">
-        <v>1</v>
-      </c>
+      <c r="N67" s="17"/>
       <c r="O67" s="10"/>
       <c r="P67" s="10">
         <f t="shared" si="7"/>
@@ -5200,9 +5173,7 @@
       <c r="M68" s="17">
         <v>1</v>
       </c>
-      <c r="N68" s="17">
-        <v>1</v>
-      </c>
+      <c r="N68" s="17"/>
       <c r="O68" s="10"/>
       <c r="P68" s="10">
         <f t="shared" si="7"/>
@@ -5211,7 +5182,7 @@
       <c r="Q68" s="11"/>
       <c r="R68" s="11"/>
     </row>
-    <row r="69" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="43" t="s">
         <v>226</v>
       </c>
@@ -5246,7 +5217,7 @@
       <c r="Q69" s="11"/>
       <c r="R69" s="28"/>
     </row>
-    <row r="70" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="31"/>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
@@ -5267,7 +5238,14 @@
       <c r="R70" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="WALI"/>
+        <filter val="WASO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="G24">
     <cfRule type="colorScale" priority="31">
       <colorScale>
@@ -5472,7 +5450,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N10 M12:N22 M37:N42 M45:N45">
+  <conditionalFormatting sqref="M9:N10 M37:N42 M45:N45 M12:N22">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D806F3-EF87-1C4E-891D-063E089CCC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1759BF-6FCA-434A-BDB3-36FA40B89C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="600" windowWidth="50800" windowHeight="27800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="R22" s="11"/>
     </row>
-    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>212</v>
       </c>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="R23" s="11"/>
     </row>
-    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>212</v>
       </c>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>212</v>
       </c>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="R25" s="11"/>
     </row>
-    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>212</v>
       </c>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="R26" s="11"/>
     </row>
-    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>212</v>
       </c>
@@ -3361,11 +3361,11 @@
         <v>0.2</v>
       </c>
       <c r="L27" s="16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M27" s="17"/>
       <c r="N27" s="17">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10">
@@ -3374,11 +3374,11 @@
       </c>
       <c r="Q27" s="60">
         <f t="shared" si="5"/>
-        <v>2.0000000000000004E-2</v>
+        <v>0.5</v>
       </c>
       <c r="R27" s="11"/>
     </row>
-    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>212</v>
       </c>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>212</v>
       </c>
@@ -4750,7 +4750,7 @@
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
     </row>
-    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>369</v>
       </c>
@@ -4794,7 +4794,7 @@
       <c r="Q59" s="11"/>
       <c r="R59" s="11"/>
     </row>
-    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>369</v>
       </c>
@@ -4836,7 +4836,7 @@
       <c r="Q60" s="11"/>
       <c r="R60" s="11"/>
     </row>
-    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>369</v>
       </c>
@@ -4878,7 +4878,7 @@
       <c r="Q61" s="11"/>
       <c r="R61" s="11"/>
     </row>
-    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>369</v>
       </c>
@@ -4925,7 +4925,7 @@
       <c r="Q62" s="11"/>
       <c r="R62" s="11"/>
     </row>
-    <row r="63" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>369</v>
       </c>
@@ -4965,7 +4965,7 @@
       <c r="Q63" s="11"/>
       <c r="R63" s="11"/>
     </row>
-    <row r="64" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>369</v>
       </c>
@@ -5010,7 +5010,7 @@
       <c r="Q64" s="11"/>
       <c r="R64" s="11"/>
     </row>
-    <row r="65" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>369</v>
       </c>
@@ -5051,7 +5051,7 @@
       <c r="Q65" s="11"/>
       <c r="R65" s="11"/>
     </row>
-    <row r="66" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>369</v>
       </c>
@@ -5092,7 +5092,7 @@
       <c r="Q66" s="11"/>
       <c r="R66" s="11"/>
     </row>
-    <row r="67" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="40" t="s">
         <v>369</v>
       </c>
@@ -5137,7 +5137,7 @@
       <c r="Q67" s="11"/>
       <c r="R67" s="11"/>
     </row>
-    <row r="68" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="42" t="s">
         <v>369</v>
       </c>
@@ -5241,8 +5241,7 @@
   <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="WALI"/>
-        <filter val="WASO"/>
+        <filter val="LNDU"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1759BF-6FCA-434A-BDB3-36FA40B89C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595A80CB-A83D-1D4F-B6E5-6F0FFEF0F3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="600" windowWidth="50800" windowHeight="27800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2580,7 +2580,7 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>226</v>
       </c>
@@ -2607,24 +2607,20 @@
       <c r="L11" s="16">
         <v>10</v>
       </c>
-      <c r="M11" s="17">
-        <v>1</v>
-      </c>
-      <c r="N11" s="17">
-        <v>1</v>
-      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
       <c r="O11" s="10"/>
       <c r="P11" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="10">
         <f>K11*N11</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
@@ -2653,24 +2649,20 @@
       <c r="L12" s="16">
         <v>10</v>
       </c>
-      <c r="M12" s="71">
-        <v>1</v>
-      </c>
-      <c r="N12" s="71">
-        <v>1</v>
-      </c>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="10">
         <f>K12*N12</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>226</v>
       </c>
@@ -2715,7 +2707,7 @@
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>226</v>
       </c>
@@ -2748,16 +2740,14 @@
       <c r="L14" s="16">
         <v>10</v>
       </c>
-      <c r="M14" s="71">
-        <v>0.5</v>
-      </c>
+      <c r="M14" s="71"/>
       <c r="N14" s="71">
         <v>0.5</v>
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10">
         <f t="shared" si="1"/>
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="10">
         <f>K14*N14</f>
@@ -2765,7 +2755,7 @@
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
@@ -2798,16 +2788,14 @@
       <c r="L15" s="16">
         <v>10</v>
       </c>
-      <c r="M15" s="71">
-        <v>0.5</v>
-      </c>
+      <c r="M15" s="71"/>
       <c r="N15" s="71">
         <v>0.5</v>
       </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="10">
         <f>K15*N15</f>
@@ -2815,7 +2803,7 @@
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -2844,18 +2832,16 @@
       <c r="L16" s="16">
         <v>10</v>
       </c>
-      <c r="M16" s="71">
-        <v>0.5</v>
-      </c>
+      <c r="M16" s="71"/>
       <c r="N16" s="71">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2888,16 +2874,14 @@
       <c r="L17" s="16">
         <v>10</v>
       </c>
-      <c r="M17" s="72">
-        <v>1.5</v>
-      </c>
+      <c r="M17" s="72"/>
       <c r="N17" s="72">
         <v>1</v>
       </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10">
         <f t="shared" ref="P17:P45" si="2">K17*M17</f>
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="10">
         <f t="shared" ref="Q17:Q22" si="3">K17*N17</f>
@@ -2905,7 +2889,7 @@
       </c>
       <c r="R17" s="57"/>
     </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2938,24 +2922,22 @@
       <c r="L18" s="16">
         <v>10</v>
       </c>
-      <c r="M18" s="71">
-        <v>2</v>
-      </c>
+      <c r="M18" s="71"/>
       <c r="N18" s="72">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="O18" s="10"/>
       <c r="P18" s="10">
         <f t="shared" ref="P18:P22" si="4">K18*M18</f>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="10">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2988,16 +2970,14 @@
       <c r="L19" s="16">
         <v>10</v>
       </c>
-      <c r="M19" s="71">
-        <v>1</v>
-      </c>
+      <c r="M19" s="71"/>
       <c r="N19" s="72">
         <v>1</v>
       </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="10">
         <f t="shared" si="3"/>
@@ -3005,7 +2985,7 @@
       </c>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -3034,16 +3014,14 @@
       <c r="L20" s="16">
         <v>10</v>
       </c>
-      <c r="M20" s="71">
-        <v>1</v>
-      </c>
+      <c r="M20" s="71"/>
       <c r="N20" s="72">
         <v>1</v>
       </c>
       <c r="O20" s="10"/>
       <c r="P20" s="10">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="10">
         <f t="shared" si="3"/>
@@ -3051,7 +3029,7 @@
       </c>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -3080,16 +3058,14 @@
       <c r="L21" s="16">
         <v>10</v>
       </c>
-      <c r="M21" s="71">
-        <v>1</v>
-      </c>
+      <c r="M21" s="71"/>
       <c r="N21" s="72">
         <v>1</v>
       </c>
       <c r="O21" s="10"/>
       <c r="P21" s="10">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="10">
         <f t="shared" si="3"/>
@@ -3097,7 +3073,7 @@
       </c>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
@@ -3126,16 +3102,14 @@
       <c r="L22" s="16">
         <v>10</v>
       </c>
-      <c r="M22" s="71">
-        <v>1</v>
-      </c>
+      <c r="M22" s="71"/>
       <c r="N22" s="72">
         <v>1</v>
       </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="10">
         <f t="shared" si="3"/>
@@ -3143,7 +3117,7 @@
       </c>
       <c r="R22" s="11"/>
     </row>
-    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>212</v>
       </c>
@@ -3193,7 +3167,7 @@
       </c>
       <c r="R23" s="11"/>
     </row>
-    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>212</v>
       </c>
@@ -3243,7 +3217,7 @@
       </c>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>212</v>
       </c>
@@ -3293,7 +3267,7 @@
       </c>
       <c r="R25" s="11"/>
     </row>
-    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>212</v>
       </c>
@@ -3330,7 +3304,7 @@
       </c>
       <c r="R26" s="11"/>
     </row>
-    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>212</v>
       </c>
@@ -3378,7 +3352,7 @@
       </c>
       <c r="R27" s="11"/>
     </row>
-    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>212</v>
       </c>
@@ -3428,7 +3402,7 @@
       </c>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>212</v>
       </c>
@@ -3777,7 +3751,7 @@
       </c>
       <c r="R36" s="29"/>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>309</v>
       </c>
@@ -3820,7 +3794,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>309</v>
       </c>
@@ -4124,7 +4098,7 @@
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -5241,7 +5215,11 @@
   <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="LNDU"/>
+        <filter val="FGTV"/>
+        <filter val="INEN"/>
+        <filter val="IPPU"/>
+        <filter val="PFLO"/>
+        <filter val="TRDE"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595A80CB-A83D-1D4F-B6E5-6F0FFEF0F3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05619E08-449D-FF4C-891F-FE0DE5089343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -1329,9 +1329,6 @@
     <t>transformation_fgtv_inc_gas_recovery.yaml</t>
   </si>
   <si>
-    <t>strategy_NDC</t>
-  </si>
-  <si>
     <t>strategy_LEDS</t>
   </si>
   <si>
@@ -1378,6 +1375,9 @@
   </si>
   <si>
     <t>transformation_frst_increase_sequestration.yaml</t>
+  </si>
+  <si>
+    <t>strategy_bau</t>
   </si>
 </sst>
 </file>
@@ -2173,10 +2173,10 @@
         <v>211</v>
       </c>
       <c r="M1" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>414</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>415</v>
       </c>
       <c r="O1" s="10"/>
       <c r="P1" s="10"/>
@@ -2251,16 +2251,14 @@
       <c r="L3" s="16">
         <v>10</v>
       </c>
-      <c r="M3" s="17">
-        <v>1.8</v>
-      </c>
+      <c r="M3" s="17"/>
       <c r="N3" s="17">
         <v>1</v>
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
@@ -2294,14 +2292,12 @@
       <c r="L4" s="16">
         <v>10</v>
       </c>
-      <c r="M4" s="17">
-        <v>1.5</v>
-      </c>
+      <c r="M4" s="17"/>
       <c r="N4" s="17"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10">
         <f t="shared" si="0"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>410</v>
@@ -2337,9 +2333,7 @@
       <c r="L5" s="16">
         <v>10</v>
       </c>
-      <c r="M5" s="17">
-        <v>1</v>
-      </c>
+      <c r="M5" s="17"/>
       <c r="N5" s="17"/>
       <c r="O5" s="10"/>
       <c r="P5" s="10" t="e">
@@ -2382,14 +2376,12 @@
       <c r="L6" s="16">
         <v>10</v>
       </c>
-      <c r="M6" s="17">
-        <v>4.5</v>
-      </c>
+      <c r="M6" s="17"/>
       <c r="N6" s="17"/>
       <c r="O6" s="10"/>
       <c r="P6" s="10">
         <f>0.6*M6</f>
-        <v>2.6999999999999997</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="10">
         <f>K6*N6</f>
@@ -2436,7 +2428,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2486,7 +2478,7 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>226</v>
       </c>
@@ -2533,7 +2525,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>226</v>
       </c>
@@ -2580,7 +2572,7 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>226</v>
       </c>
@@ -2620,7 +2612,7 @@
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
@@ -2662,7 +2654,7 @@
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>226</v>
       </c>
@@ -2707,7 +2699,7 @@
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>226</v>
       </c>
@@ -2755,7 +2747,7 @@
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
@@ -2803,7 +2795,7 @@
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -2841,7 +2833,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2889,7 +2881,7 @@
       </c>
       <c r="R17" s="57"/>
     </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2937,7 +2929,7 @@
       </c>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2985,7 +2977,7 @@
       </c>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -3029,7 +3021,7 @@
       </c>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -3073,7 +3065,7 @@
       </c>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
@@ -3150,16 +3142,14 @@
       <c r="L23" s="16">
         <v>10</v>
       </c>
-      <c r="M23" s="17">
-        <v>1</v>
-      </c>
+      <c r="M23" s="17"/>
       <c r="N23" s="17">
         <v>1</v>
       </c>
       <c r="O23" s="59"/>
       <c r="P23" s="59">
         <f t="shared" si="2"/>
-        <v>0.999</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="60">
         <f t="shared" ref="Q23:Q30" si="5">K23*N23</f>
@@ -3175,10 +3165,10 @@
         <v>70</v>
       </c>
       <c r="C24" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="D24" s="13" t="s">
         <v>425</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>426</v>
       </c>
       <c r="E24" s="19">
         <v>0.95</v>
@@ -3200,16 +3190,14 @@
       <c r="L24" s="16">
         <v>10</v>
       </c>
-      <c r="M24" s="17">
-        <v>1</v>
-      </c>
+      <c r="M24" s="17"/>
       <c r="N24" s="17">
         <v>1</v>
       </c>
       <c r="O24" s="59"/>
       <c r="P24" s="59">
         <f t="shared" si="2"/>
-        <v>0.999</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="60">
         <f t="shared" si="5"/>
@@ -3250,16 +3238,14 @@
       <c r="L25" s="16">
         <v>10</v>
       </c>
-      <c r="M25" s="17">
-        <v>1</v>
-      </c>
+      <c r="M25" s="17"/>
       <c r="N25" s="17">
         <v>1</v>
       </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10">
         <f t="shared" si="2"/>
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="60">
         <f t="shared" si="5"/>
@@ -3275,10 +3261,10 @@
         <v>70</v>
       </c>
       <c r="C26" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="D26" s="54" t="s">
         <v>428</v>
-      </c>
-      <c r="D26" s="54" t="s">
-        <v>429</v>
       </c>
       <c r="E26" s="53"/>
       <c r="F26" s="25"/>
@@ -3360,10 +3346,10 @@
         <v>70</v>
       </c>
       <c r="C28" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>422</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>423</v>
       </c>
       <c r="E28" s="19">
         <v>0.1</v>
@@ -3385,16 +3371,14 @@
       <c r="L28" s="16">
         <v>10</v>
       </c>
-      <c r="M28" s="17">
-        <v>1</v>
-      </c>
+      <c r="M28" s="17"/>
       <c r="N28" s="17">
         <v>1</v>
       </c>
       <c r="O28" s="10"/>
       <c r="P28" s="10">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="60">
         <f t="shared" si="5"/>
@@ -3435,16 +3419,14 @@
       <c r="L29" s="16">
         <v>10</v>
       </c>
-      <c r="M29" s="17">
-        <v>1</v>
-      </c>
+      <c r="M29" s="17"/>
       <c r="N29" s="17">
         <v>1</v>
       </c>
       <c r="O29" s="10"/>
       <c r="P29" s="10">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="11">
         <f t="shared" si="5"/>
@@ -3481,16 +3463,14 @@
       <c r="L30" s="16">
         <v>10</v>
       </c>
-      <c r="M30" s="17">
-        <v>1</v>
-      </c>
+      <c r="M30" s="17"/>
       <c r="N30" s="17">
         <v>1</v>
       </c>
       <c r="O30" s="10"/>
       <c r="P30" s="10">
         <f t="shared" si="2"/>
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="11">
         <f t="shared" si="5"/>
@@ -3527,9 +3507,7 @@
       <c r="L31" s="16">
         <v>10</v>
       </c>
-      <c r="M31" s="17">
-        <v>1</v>
-      </c>
+      <c r="M31" s="17"/>
       <c r="N31" s="17"/>
       <c r="O31" s="10"/>
       <c r="P31" s="10" t="e">
@@ -3568,9 +3546,7 @@
       <c r="L32" s="16">
         <v>10</v>
       </c>
-      <c r="M32" s="17">
-        <v>1</v>
-      </c>
+      <c r="M32" s="17"/>
       <c r="N32" s="17"/>
       <c r="O32" s="10"/>
       <c r="P32" s="10" t="e">
@@ -3609,9 +3585,7 @@
       <c r="L33" s="16">
         <v>10</v>
       </c>
-      <c r="M33" s="17">
-        <v>1</v>
-      </c>
+      <c r="M33" s="17"/>
       <c r="N33" s="17"/>
       <c r="O33" s="10"/>
       <c r="P33" s="10" t="e">
@@ -3650,9 +3624,7 @@
       <c r="L34" s="16">
         <v>10</v>
       </c>
-      <c r="M34" s="17">
-        <v>1</v>
-      </c>
+      <c r="M34" s="17"/>
       <c r="N34" s="17"/>
       <c r="O34" s="10"/>
       <c r="P34" s="10" t="e">
@@ -3691,14 +3663,12 @@
       <c r="L35" s="16">
         <v>10</v>
       </c>
-      <c r="M35" s="17">
-        <v>1</v>
-      </c>
+      <c r="M35" s="17"/>
       <c r="N35" s="17"/>
       <c r="O35" s="10"/>
       <c r="P35" s="10">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
@@ -3736,14 +3706,12 @@
       <c r="L36" s="16">
         <v>10</v>
       </c>
-      <c r="M36" s="17">
-        <v>1</v>
-      </c>
+      <c r="M36" s="17"/>
       <c r="N36" s="17"/>
       <c r="O36" s="10"/>
       <c r="P36" s="60">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="60">
         <f>K36*N36</f>
@@ -3751,7 +3719,7 @@
       </c>
       <c r="R36" s="29"/>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>309</v>
       </c>
@@ -3780,21 +3748,19 @@
       <c r="L37" s="16">
         <v>10</v>
       </c>
-      <c r="M37" s="71">
-        <v>1</v>
-      </c>
+      <c r="M37" s="71"/>
       <c r="N37" s="71">
         <v>1</v>
       </c>
       <c r="O37" s="10"/>
       <c r="P37" s="10">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>309</v>
       </c>
@@ -3843,10 +3809,10 @@
         <v>113</v>
       </c>
       <c r="C39" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="D39" s="13" t="s">
         <v>419</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>420</v>
       </c>
       <c r="E39" s="20">
         <v>0.5</v>
@@ -3866,16 +3832,14 @@
       <c r="L39" s="16">
         <v>10</v>
       </c>
-      <c r="M39" s="71">
-        <v>1</v>
-      </c>
+      <c r="M39" s="71"/>
       <c r="N39" s="71">
         <v>1</v>
       </c>
       <c r="O39" s="10"/>
       <c r="P39" s="10">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
@@ -3909,16 +3873,14 @@
       <c r="L40" s="16">
         <v>10</v>
       </c>
-      <c r="M40" s="71">
-        <v>0.1</v>
-      </c>
+      <c r="M40" s="71"/>
       <c r="N40" s="71">
         <v>0.1</v>
       </c>
       <c r="O40" s="10"/>
       <c r="P40" s="10">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="10">
         <f>K40*N40</f>
@@ -3955,16 +3917,14 @@
       <c r="L41" s="16">
         <v>10</v>
       </c>
-      <c r="M41" s="71">
-        <v>1</v>
-      </c>
+      <c r="M41" s="71"/>
       <c r="N41" s="71">
         <v>1</v>
       </c>
       <c r="O41" s="10"/>
       <c r="P41" s="10">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
@@ -3998,16 +3958,14 @@
       <c r="L42" s="16">
         <v>10</v>
       </c>
-      <c r="M42" s="71">
-        <v>1</v>
-      </c>
+      <c r="M42" s="71"/>
       <c r="N42" s="71">
         <v>1</v>
       </c>
       <c r="O42" s="10"/>
       <c r="P42" s="10">
         <f t="shared" si="2"/>
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
@@ -4041,16 +3999,14 @@
       <c r="L43" s="16">
         <v>10</v>
       </c>
-      <c r="M43" s="17">
-        <v>1</v>
-      </c>
+      <c r="M43" s="17"/>
       <c r="N43" s="17">
         <v>1</v>
       </c>
       <c r="O43" s="10"/>
       <c r="P43" s="10">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
@@ -4084,21 +4040,19 @@
       <c r="L44" s="16">
         <v>10</v>
       </c>
-      <c r="M44" s="17">
-        <v>1</v>
-      </c>
+      <c r="M44" s="17"/>
       <c r="N44" s="17">
         <v>1</v>
       </c>
       <c r="O44" s="10"/>
       <c r="P44" s="10">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -4131,16 +4085,14 @@
       <c r="L45" s="16">
         <v>10</v>
       </c>
-      <c r="M45" s="71">
-        <v>2</v>
-      </c>
+      <c r="M45" s="71"/>
       <c r="N45" s="71">
         <v>1.5</v>
       </c>
       <c r="O45" s="10"/>
       <c r="P45" s="10">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="10">
         <f>K45*N45</f>
@@ -4181,9 +4133,7 @@
       <c r="L46" s="16">
         <v>10</v>
       </c>
-      <c r="M46" s="17">
-        <v>1</v>
-      </c>
+      <c r="M46" s="17"/>
       <c r="N46" s="17">
         <v>1</v>
       </c>
@@ -4309,9 +4259,7 @@
       <c r="L49" s="16">
         <v>10</v>
       </c>
-      <c r="M49" s="71">
-        <v>1.4</v>
-      </c>
+      <c r="M49" s="71"/>
       <c r="N49" s="71">
         <v>1.4</v>
       </c>
@@ -4356,9 +4304,7 @@
       <c r="L50" s="16">
         <v>10</v>
       </c>
-      <c r="M50" s="71">
-        <v>1</v>
-      </c>
+      <c r="M50" s="71"/>
       <c r="N50" s="71">
         <v>1</v>
       </c>
@@ -4378,7 +4324,7 @@
         <v>134</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>151</v>
@@ -4401,9 +4347,7 @@
       <c r="L51" s="16">
         <v>10</v>
       </c>
-      <c r="M51" s="71">
-        <v>1</v>
-      </c>
+      <c r="M51" s="71"/>
       <c r="N51" s="71">
         <v>1</v>
       </c>
@@ -4448,9 +4392,7 @@
       <c r="L52" s="16">
         <v>10</v>
       </c>
-      <c r="M52" s="71">
-        <v>0.8</v>
-      </c>
+      <c r="M52" s="71"/>
       <c r="N52" s="71">
         <v>0.8</v>
       </c>
@@ -4491,9 +4433,7 @@
       <c r="L53" s="16">
         <v>10</v>
       </c>
-      <c r="M53" s="71">
-        <v>2</v>
-      </c>
+      <c r="M53" s="71"/>
       <c r="N53" s="71">
         <v>2</v>
       </c>
@@ -4505,7 +4445,7 @@
       <c r="Q53" s="11"/>
       <c r="R53" s="10">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4663,16 +4603,14 @@
       <c r="L57" s="16">
         <v>10</v>
       </c>
-      <c r="M57" s="17">
-        <v>1</v>
-      </c>
+      <c r="M57" s="17"/>
       <c r="N57" s="17">
         <v>1</v>
       </c>
       <c r="O57" s="10"/>
       <c r="P57" s="10">
         <f>K57*M57</f>
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
@@ -4710,16 +4648,14 @@
       <c r="L58" s="16">
         <v>10</v>
       </c>
-      <c r="M58" s="17">
-        <v>1</v>
-      </c>
+      <c r="M58" s="17"/>
       <c r="N58" s="17">
         <v>1</v>
       </c>
       <c r="O58" s="10"/>
       <c r="P58" s="10">
         <f>K58*M58</f>
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
@@ -4757,9 +4693,7 @@
       <c r="L59" s="16">
         <v>10</v>
       </c>
-      <c r="M59" s="17">
-        <v>1</v>
-      </c>
+      <c r="M59" s="17"/>
       <c r="N59" s="17">
         <v>1</v>
       </c>
@@ -4801,9 +4735,7 @@
       <c r="L60" s="16">
         <v>10</v>
       </c>
-      <c r="M60" s="17">
-        <v>1</v>
-      </c>
+      <c r="M60" s="17"/>
       <c r="N60" s="17"/>
       <c r="O60" s="10"/>
       <c r="P60" s="10"/>
@@ -4843,9 +4775,7 @@
       <c r="L61" s="16">
         <v>10</v>
       </c>
-      <c r="M61" s="17">
-        <v>1</v>
-      </c>
+      <c r="M61" s="17"/>
       <c r="N61" s="17"/>
       <c r="O61" s="10"/>
       <c r="P61" s="10"/>
@@ -4885,16 +4815,14 @@
       <c r="L62" s="16">
         <v>10</v>
       </c>
-      <c r="M62" s="17">
-        <v>1</v>
-      </c>
+      <c r="M62" s="17"/>
       <c r="N62" s="17">
         <v>1</v>
       </c>
       <c r="O62" s="10"/>
       <c r="P62" s="10">
         <f>K62*M62</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="11"/>
       <c r="R62" s="11"/>
@@ -4928,9 +4856,7 @@
       <c r="L63" s="16">
         <v>10</v>
       </c>
-      <c r="M63" s="17">
-        <v>1</v>
-      </c>
+      <c r="M63" s="17"/>
       <c r="N63" s="17">
         <v>1</v>
       </c>
@@ -4972,14 +4898,12 @@
       <c r="L64" s="16">
         <v>10</v>
       </c>
-      <c r="M64" s="17">
-        <v>1</v>
-      </c>
+      <c r="M64" s="17"/>
       <c r="N64" s="17"/>
       <c r="O64" s="10"/>
       <c r="P64" s="10">
         <f t="shared" ref="P64:P69" si="7">K64*M64</f>
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="11"/>
       <c r="R64" s="11"/>
@@ -5013,14 +4937,12 @@
       <c r="L65" s="16">
         <v>10</v>
       </c>
-      <c r="M65" s="17">
-        <v>1</v>
-      </c>
+      <c r="M65" s="17"/>
       <c r="N65" s="17"/>
       <c r="O65" s="10"/>
       <c r="P65" s="10">
         <f t="shared" si="7"/>
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="11"/>
       <c r="R65" s="11"/>
@@ -5054,14 +4976,12 @@
       <c r="L66" s="16">
         <v>10</v>
       </c>
-      <c r="M66" s="17">
-        <v>1</v>
-      </c>
+      <c r="M66" s="17"/>
       <c r="N66" s="17"/>
       <c r="O66" s="10"/>
       <c r="P66" s="10">
         <f t="shared" si="7"/>
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="Q66" s="11"/>
       <c r="R66" s="11"/>
@@ -5099,14 +5019,12 @@
       <c r="L67" s="16">
         <v>10</v>
       </c>
-      <c r="M67" s="17">
-        <v>1</v>
-      </c>
+      <c r="M67" s="17"/>
       <c r="N67" s="17"/>
       <c r="O67" s="10"/>
       <c r="P67" s="10">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="11"/>
       <c r="R67" s="11"/>
@@ -5144,14 +5062,12 @@
       <c r="L68" s="16">
         <v>10</v>
       </c>
-      <c r="M68" s="17">
-        <v>1</v>
-      </c>
+      <c r="M68" s="17"/>
       <c r="N68" s="17"/>
       <c r="O68" s="10"/>
       <c r="P68" s="10">
         <f t="shared" si="7"/>
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="11"/>
       <c r="R68" s="11"/>
@@ -5215,15 +5131,59 @@
   <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="FGTV"/>
-        <filter val="INEN"/>
-        <filter val="IPPU"/>
-        <filter val="PFLO"/>
-        <filter val="TRDE"/>
+        <filter val="ENTC"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="G24">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G39">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G51">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
@@ -5235,7 +5195,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
+  <conditionalFormatting sqref="H28">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -5247,7 +5207,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G39">
+  <conditionalFormatting sqref="H39">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -5259,7 +5219,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G51">
+  <conditionalFormatting sqref="H51">
     <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
@@ -5271,7 +5231,343 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
+  <conditionalFormatting sqref="M1">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M6">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M23:M35">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M47:M56">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M57:M58">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:N2">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:N3">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:N4">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M37:N42 M45:N45 M12:N22 M9:N10">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:N11">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M36:N36">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M43:N43">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M44:N44">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M46:N46">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M59:N59">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M60:N60">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M61:N61">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M62:N62">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M63:N63">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M64:N64">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M65:N65">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M66:N66">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M67:N67">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M68:N68">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M69:N1048576">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N5:N6">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N8">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
@@ -5283,8 +5579,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
-    <cfRule type="colorScale" priority="32">
+  <conditionalFormatting sqref="N23:N35">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5295,8 +5591,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H39">
-    <cfRule type="colorScale" priority="34">
+  <conditionalFormatting sqref="N47:N56">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5307,307 +5603,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H51">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M1">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M6">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M8">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M23:M35">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M47:M56">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M57:M58">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:N2">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3:N3">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4:N4">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N10 M37:N42 M45:N45 M12:N22">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M11:N11">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M36:N36">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M43:N43">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M44:N44">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M46:N46">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M59:N59">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M60:N60">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M61:N61">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M62:N62">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M63:N63">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M64:N64">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M65:N65">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M66:N66">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M67:N67">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M68:N68">
+  <conditionalFormatting sqref="N57:N58">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -5619,80 +5615,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M69:N1048576">
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N6">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N8">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N23:N35">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N47:N56">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N57:N58">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="M8">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6048,13 +5972,13 @@
         <v>70</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6076,13 +6000,13 @@
         <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6118,13 +6042,13 @@
         <v>70</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6272,13 +6196,13 @@
         <v>113</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6426,13 +6350,13 @@
         <v>134</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05619E08-449D-FF4C-891F-FE0DE5089343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813370E0-5228-4045-9021-727423EC5345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-44460" yWindow="1340" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2462,7 +2462,7 @@
         <v>10</v>
       </c>
       <c r="M8" s="17">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N8" s="17">
         <v>1.5</v>
@@ -2470,7 +2470,7 @@
       <c r="O8" s="10"/>
       <c r="P8" s="10">
         <f>0.6*M8</f>
-        <v>0.89999999999999991</v>
+        <v>0.6</v>
       </c>
       <c r="Q8" s="10">
         <f>0.6*N8</f>
@@ -2512,7 +2512,7 @@
         <v>10</v>
       </c>
       <c r="M9" s="71">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="N9" s="71">
         <v>0.5</v>
@@ -2520,7 +2520,7 @@
       <c r="O9" s="10"/>
       <c r="P9" s="10">
         <f t="shared" ref="P9:P15" si="1">K9*M9</f>
-        <v>0.47499999999999998</v>
+        <v>0.23749999999999999</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -5267,6 +5267,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M8">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M23:M35">
     <cfRule type="colorScale" priority="5">
       <colorScale>
@@ -5339,18 +5351,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M37:N42 M45:N45 M12:N22 M9:N10">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="M11:N11">
     <cfRule type="colorScale" priority="42">
       <colorScale>
@@ -5365,6 +5365,18 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="M36:N36">
     <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M37:N42 M45:N45 M12:N22 M9:N10">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5615,18 +5627,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M8">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813370E0-5228-4045-9021-727423EC5345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B60AD20-0A27-0349-A950-1629ACE2F760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-44460" yWindow="1340" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-47180" yWindow="600" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>226</v>
       </c>
@@ -2419,7 +2419,9 @@
         <v>10</v>
       </c>
       <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
+      <c r="N7" s="17">
+        <v>0.3</v>
+      </c>
       <c r="O7" s="10"/>
       <c r="P7" s="10">
         <f t="shared" si="0"/>
@@ -2428,7 +2430,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2478,7 +2480,7 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>226</v>
       </c>
@@ -2525,7 +2527,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>226</v>
       </c>
@@ -2734,7 +2736,7 @@
       </c>
       <c r="M14" s="71"/>
       <c r="N14" s="71">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10">
@@ -2743,7 +2745,7 @@
       </c>
       <c r="Q14" s="10">
         <f>K14*N14</f>
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="R14" s="11"/>
     </row>
@@ -2782,7 +2784,7 @@
       </c>
       <c r="M15" s="71"/>
       <c r="N15" s="71">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10">
@@ -2791,11 +2793,11 @@
       </c>
       <c r="Q15" s="10">
         <f>K15*N15</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="114" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -5131,7 +5133,7 @@
   <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="ENTC"/>
+        <filter val="CCSQ"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B60AD20-0A27-0349-A950-1629ACE2F760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBB6D5F-B69A-5446-A16B-CBEC96FFD04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-47180" yWindow="600" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37720" yWindow="4420" windowWidth="37660" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>226</v>
       </c>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M15" s="71"/>
       <c r="N15" s="71">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Q15" s="10">
         <f>K15*N15</f>
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="R15" s="11"/>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="R22" s="11"/>
     </row>
-    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>212</v>
       </c>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="R23" s="11"/>
     </row>
-    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>212</v>
       </c>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>212</v>
       </c>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="R25" s="11"/>
     </row>
-    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>212</v>
       </c>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="R26" s="11"/>
     </row>
-    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>212</v>
       </c>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="M27" s="17"/>
       <c r="N27" s="17">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10">
@@ -3336,11 +3336,11 @@
       </c>
       <c r="Q27" s="60">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="R27" s="11"/>
     </row>
-    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>212</v>
       </c>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>212</v>
       </c>
@@ -5133,7 +5133,7 @@
   <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="CCSQ"/>
+        <filter val="LNDU"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBB6D5F-B69A-5446-A16B-CBEC96FFD04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9016A1-B107-B04D-8BAE-80DC2376C6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37720" yWindow="4420" windowWidth="37660" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2114,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R70"/>
@@ -2183,7 +2183,7 @@
       <c r="Q1" s="11"/>
       <c r="R1" s="11"/>
     </row>
-    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>212</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
     </row>
-    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>212</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
     </row>
-    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>212</v>
       </c>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="R4" s="11"/>
     </row>
-    <row r="5" spans="1:18" s="4" customFormat="1" ht="153" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" s="4" customFormat="1" ht="153" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>212</v>
       </c>
@@ -2343,7 +2343,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
     </row>
-    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>212</v>
       </c>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>226</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>226</v>
       </c>
@@ -2527,7 +2527,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>226</v>
       </c>
@@ -2574,7 +2574,7 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>226</v>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>226</v>
       </c>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>226</v>
       </c>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="114" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -2835,7 +2835,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="R17" s="57"/>
     </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="R29" s="11"/>
     </row>
-    <row r="30" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>212</v>
       </c>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="R30" s="28"/>
     </row>
-    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>212</v>
       </c>
@@ -3519,7 +3519,7 @@
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
     </row>
-    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>212</v>
       </c>
@@ -3558,7 +3558,7 @@
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
     </row>
-    <row r="33" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>212</v>
       </c>
@@ -3597,7 +3597,7 @@
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
     </row>
-    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>212</v>
       </c>
@@ -3636,7 +3636,7 @@
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
     </row>
-    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>212</v>
       </c>
@@ -3675,7 +3675,7 @@
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
     </row>
-    <row r="36" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>212</v>
       </c>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="R36" s="29"/>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>309</v>
       </c>
@@ -3762,7 +3762,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>309</v>
       </c>
@@ -3803,7 +3803,7 @@
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
     </row>
-    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>226</v>
       </c>
@@ -3846,7 +3846,7 @@
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
     </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>226</v>
       </c>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="R40" s="11"/>
     </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>226</v>
       </c>
@@ -3931,7 +3931,7 @@
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
     </row>
-    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>226</v>
       </c>
@@ -3972,7 +3972,7 @@
       <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
     </row>
-    <row r="43" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>212</v>
       </c>
@@ -4013,7 +4013,7 @@
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
     </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>212</v>
       </c>
@@ -4044,17 +4044,20 @@
       </c>
       <c r="M44" s="17"/>
       <c r="N44" s="17">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="O44" s="10"/>
       <c r="P44" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q44" s="11"/>
+      <c r="Q44" s="10">
+        <f>K44*N44</f>
+        <v>0.25</v>
+      </c>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -4102,7 +4105,7 @@
       </c>
       <c r="R45" s="11"/>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>226</v>
       </c>
@@ -4150,7 +4153,7 @@
       </c>
       <c r="R46" s="11"/>
     </row>
-    <row r="47" spans="1:18" s="4" customFormat="1" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>226</v>
       </c>
@@ -4193,7 +4196,7 @@
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
     </row>
-    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>226</v>
       </c>
@@ -4232,7 +4235,7 @@
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
     </row>
-    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>226</v>
       </c>
@@ -4273,7 +4276,7 @@
       <c r="Q49" s="10"/>
       <c r="R49" s="11"/>
     </row>
-    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>226</v>
       </c>
@@ -4318,7 +4321,7 @@
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
     </row>
-    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>226</v>
       </c>
@@ -4361,7 +4364,7 @@
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>226</v>
       </c>
@@ -4406,7 +4409,7 @@
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
     </row>
-    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>226</v>
       </c>
@@ -4450,7 +4453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>226</v>
       </c>
@@ -4493,7 +4496,7 @@
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
     </row>
-    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>226</v>
       </c>
@@ -4536,7 +4539,7 @@
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
     </row>
-    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>226</v>
       </c>
@@ -4576,7 +4579,7 @@
       <c r="Q56" s="11"/>
       <c r="R56" s="11"/>
     </row>
-    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>51</v>
       </c>
@@ -4617,7 +4620,7 @@
       <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
     </row>
-    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>51</v>
       </c>
@@ -4662,7 +4665,7 @@
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
     </row>
-    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>369</v>
       </c>
@@ -4704,7 +4707,7 @@
       <c r="Q59" s="11"/>
       <c r="R59" s="11"/>
     </row>
-    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>369</v>
       </c>
@@ -4744,7 +4747,7 @@
       <c r="Q60" s="11"/>
       <c r="R60" s="11"/>
     </row>
-    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>369</v>
       </c>
@@ -4784,7 +4787,7 @@
       <c r="Q61" s="11"/>
       <c r="R61" s="11"/>
     </row>
-    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>369</v>
       </c>
@@ -4829,7 +4832,7 @@
       <c r="Q62" s="11"/>
       <c r="R62" s="11"/>
     </row>
-    <row r="63" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>369</v>
       </c>
@@ -4867,7 +4870,7 @@
       <c r="Q63" s="11"/>
       <c r="R63" s="11"/>
     </row>
-    <row r="64" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>369</v>
       </c>
@@ -4910,7 +4913,7 @@
       <c r="Q64" s="11"/>
       <c r="R64" s="11"/>
     </row>
-    <row r="65" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>369</v>
       </c>
@@ -4949,7 +4952,7 @@
       <c r="Q65" s="11"/>
       <c r="R65" s="11"/>
     </row>
-    <row r="66" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>369</v>
       </c>
@@ -4988,7 +4991,7 @@
       <c r="Q66" s="11"/>
       <c r="R66" s="11"/>
     </row>
-    <row r="67" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="40" t="s">
         <v>369</v>
       </c>
@@ -5031,7 +5034,7 @@
       <c r="Q67" s="11"/>
       <c r="R67" s="11"/>
     </row>
-    <row r="68" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="42" t="s">
         <v>369</v>
       </c>
@@ -5074,7 +5077,7 @@
       <c r="Q68" s="11"/>
       <c r="R68" s="11"/>
     </row>
-    <row r="69" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="43" t="s">
         <v>226</v>
       </c>
@@ -5109,7 +5112,7 @@
       <c r="Q69" s="11"/>
       <c r="R69" s="28"/>
     </row>
-    <row r="70" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="31"/>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
@@ -5130,13 +5133,7 @@
       <c r="R70" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="LNDU"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="G24">
     <cfRule type="colorScale" priority="32">
       <colorScale>

--- a/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_morocco_transformation_cw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9016A1-B107-B04D-8BAE-80DC2376C6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C70528-5854-714D-9E94-0EFCF8C3B0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2114,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R70"/>
@@ -2183,7 +2183,7 @@
       <c r="Q1" s="11"/>
       <c r="R1" s="11"/>
     </row>
-    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" s="4" customFormat="1" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>212</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
     </row>
-    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>212</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
     </row>
-    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" s="4" customFormat="1" ht="86" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>212</v>
       </c>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="R4" s="11"/>
     </row>
-    <row r="5" spans="1:18" s="4" customFormat="1" ht="153" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" s="4" customFormat="1" ht="153" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>212</v>
       </c>
@@ -2343,7 +2343,7 @@
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
     </row>
-    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" s="4" customFormat="1" ht="70" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>212</v>
       </c>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="R6" s="11"/>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="4" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
         <v>226</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="55" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>226</v>
       </c>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="R8" s="11"/>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>226</v>
       </c>
@@ -2527,7 +2527,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>226</v>
       </c>
@@ -2574,7 +2574,7 @@
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>226</v>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>226</v>
       </c>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="R12" s="11"/>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>226</v>
       </c>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>226</v>
       </c>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="R14" s="11"/>
     </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>226</v>
       </c>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" s="4" customFormat="1" ht="114" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>226</v>
       </c>
@@ -2835,7 +2835,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
     </row>
-    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" s="58" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="R17" s="57"/>
     </row>
-    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>51</v>
       </c>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="R18" s="11"/>
     </row>
-    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>51</v>
       </c>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="R19" s="11"/>
     </row>
-    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="R20" s="11"/>
     </row>
-    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R21" s="11"/>
     </row>
-    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>51</v>
       </c>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="R22" s="11"/>
     </row>
-    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>212</v>
       </c>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="R23" s="11"/>
     </row>
-    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>212</v>
       </c>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>212</v>
       </c>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="R25" s="11"/>
     </row>
-    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>212</v>
       </c>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="R26" s="11"/>
     </row>
-    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>212</v>
       </c>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="R27" s="11"/>
     </row>
-    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>212</v>
       </c>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="R28" s="11"/>
     </row>
-    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>212</v>
       </c>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="R29" s="11"/>
     </row>
-    <row r="30" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>212</v>
       </c>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="R30" s="28"/>
     </row>
-    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>212</v>
       </c>
@@ -3519,7 +3519,7 @@
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
     </row>
-    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>212</v>
       </c>
@@ -3558,7 +3558,7 @@
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
     </row>
-    <row r="33" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>212</v>
       </c>
@@ -3597,7 +3597,7 @@
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
     </row>
-    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>212</v>
       </c>
@@ -3636,7 +3636,7 @@
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
     </row>
-    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>212</v>
       </c>
@@ -3675,7 +3675,7 @@
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
     </row>
-    <row r="36" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>212</v>
       </c>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="R36" s="29"/>
     </row>
-    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>309</v>
       </c>
@@ -3762,7 +3762,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
     </row>
-    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>309</v>
       </c>
@@ -3803,7 +3803,7 @@
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
     </row>
-    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>226</v>
       </c>
@@ -3846,7 +3846,7 @@
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
     </row>
-    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>226</v>
       </c>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="R40" s="11"/>
     </row>
-    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>226</v>
       </c>
@@ -3931,7 +3931,7 @@
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
     </row>
-    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>226</v>
       </c>
@@ -3962,17 +3962,20 @@
       </c>
       <c r="M42" s="71"/>
       <c r="N42" s="71">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="O42" s="10"/>
       <c r="P42" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q42" s="11"/>
+      <c r="Q42" s="10">
+        <f>K42*N42</f>
+        <v>0.90249999999999997</v>
+      </c>
       <c r="R42" s="11"/>
     </row>
-    <row r="43" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>212</v>
       </c>
@@ -4013,7 +4016,7 @@
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
     </row>
-    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>212</v>
       </c>
@@ -4057,7 +4060,7 @@
       </c>
       <c r="R44" s="11"/>
     </row>
-    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>226</v>
       </c>
@@ -4105,7 +4108,7 @@
       </c>
       <c r="R45" s="11"/>
     </row>
-    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>226</v>
       </c>
@@ -4153,7 +4156,7 @@
       </c>
       <c r="R46" s="11"/>
     </row>
-    <row r="47" spans="1:18" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" s="4" customFormat="1" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>226</v>
       </c>
@@ -4196,7 +4199,7 @@
       <c r="Q47" s="11"/>
       <c r="R47" s="11"/>
     </row>
-    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>226</v>
       </c>
@@ -4235,7 +4238,7 @@
       <c r="Q48" s="11"/>
       <c r="R48" s="11"/>
     </row>
-    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>226</v>
       </c>
@@ -4276,7 +4279,7 @@
       <c r="Q49" s="10"/>
       <c r="R49" s="11"/>
     </row>
-    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>226</v>
       </c>
@@ -4321,7 +4324,7 @@
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
     </row>
-    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>226</v>
       </c>
@@ -4364,7 +4367,7 @@
       <c r="Q51" s="11"/>
       <c r="R51" s="11"/>
     </row>
-    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>226</v>
       </c>
@@ -4409,7 +4412,7 @@
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
     </row>
-    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>226</v>
       </c>
@@ -4453,7 +4456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>226</v>
       </c>
@@ -4496,7 +4499,7 @@
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
     </row>
-    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>226</v>
       </c>
@@ -4539,7 +4542,7 @@
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
     </row>
-    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>226</v>
       </c>
@@ -5077,7 +5080,7 @@
       <c r="Q68" s="11"/>
       <c r="R68" s="11"/>
     </row>
-    <row r="69" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="43" t="s">
         <v>226</v>
       </c>
@@ -5112,7 +5115,7 @@
       <c r="Q69" s="11"/>
       <c r="R69" s="28"/>
     </row>
-    <row r="70" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="31"/>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
@@ -5133,7 +5136,15 @@
       <c r="R70" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R70" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="TRWW"/>
+        <filter val="WALI"/>
+        <filter val="WASO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="G24">
     <cfRule type="colorScale" priority="32">
       <colorScale>
